--- a/eval/data/gt_datasets.xlsx
+++ b/eval/data/gt_datasets.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -721,7 +721,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -770,85 +771,74 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>q001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>실크블렌드 가디건 상품 정보</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>특정 상품명 검색 — 1개 정답</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>products:12800000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>q002</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>시폰 플리츠 롱 스커트</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -856,28 +846,32 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>동일 상품명 여러 시즌 — 복수 정답</t>
+          <t>특정 상품명 검색 — 1개 정답</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>products:12800001
-products:12800007</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>q003</t>
+          <t>q002</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>울 캐시미어 브이넥 니트</t>
+          <t>시폰 플리츠 롱 스커트</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -885,27 +879,34 @@
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>소재+스타일 복합 검색</t>
+          <t>동일 상품명 여러 시즌 — 복수 정답</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>products:12800004</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>[products:12800001] products:12800001  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
+[products:12800007] products:12800007  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800007 | 69900.0 | 20.0 | 2932 | 204946800.0</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>products:12800001
+products:12800007</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>q004</t>
+          <t>q003</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>린넨 와이드 밴딩 슬랙스</t>
+          <t>울 캐시미어 브이넥 니트</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -913,7 +914,7 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>소재+디자인 검색</t>
+          <t>소재+스타일 복합 검색</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -921,19 +922,24 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>products:12800009</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>[products:12800004] products:12800004  ▸  products: 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>products:12800004</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>q005</t>
+          <t>q004</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>모달 레이스 트리밍 블라우스</t>
+          <t>린넨 와이드 밴딩 슬랙스</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -941,7 +947,7 @@
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>소재+디테일 검색</t>
+          <t>소재+디자인 검색</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -949,19 +955,24 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>products:12800005</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>[products:12800009] products:12800009  ▸  products: 24SS 린넨 와이드 밴딩 슬랙스 | LBL 시즌2025 S/S NO.1 | 24SS | 12800009 | 99900.0 | 20.0 | 4416 | 441158400.0</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>products:12800009</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>q006</t>
+          <t>q005</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>소라 색상 옵션</t>
+          <t>모달 레이스 트리밍 블라우스</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -969,7 +980,7 @@
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>색상 마스터 검색</t>
+          <t>소재+디테일 검색</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
@@ -977,19 +988,24 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>colors:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>[products:12800005] products:12800005  ▸  products: 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>products:12800005</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>q007</t>
+          <t>q006</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>네이비 색상</t>
+          <t>소라 색상 옵션</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -997,7 +1013,7 @@
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>색상 검색</t>
+          <t>색상 마스터 검색</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
@@ -1005,19 +1021,24 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>colors:4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>[colors:1] colors:1  ▸  colors: 소라 | 1</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>colors:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>q008</t>
+          <t>q007</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>55 사이즈</t>
+          <t>네이비 색상</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -1025,7 +1046,7 @@
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>사이즈 마스터 검색</t>
+          <t>색상 검색</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
@@ -1033,19 +1054,24 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>sizes:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>[colors:4] colors:4  ▸  colors: 네이비 | 4</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>colors:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>q009</t>
+          <t>q008</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>입으면 날씬해 보여요 핏이 딱 맞아요</t>
+          <t>55 사이즈</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -1053,7 +1079,7 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>리뷰 텍스트 검색</t>
+          <t>사이즈 마스터 검색</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
@@ -1061,19 +1087,24 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>reviews:259000003</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+          <t>[sizes:2] sizes:2  ▸  sizes: 55 | 2</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>sizes:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>q010</t>
+          <t>q009</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>세탁해도 줄지 않고 마감이 깔끔해요</t>
+          <t>입으면 날씬해 보여요 핏이 딱 맞아요</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -1081,7 +1112,7 @@
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>리뷰 내용 직접 검색</t>
+          <t>리뷰 텍스트 검색</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
@@ -1089,19 +1120,24 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>reviews:259000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>[reviews:259000003] reviews:259000003  ▸  reviews: 입으면 날씬해 보여요. 핏이 딱 맞아요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000003 | 12800000 | 약간큼</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>reviews:259000003</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>q011</t>
+          <t>q010</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>엄마 선물로 구매했는데 너무 좋아하세요</t>
+          <t>세탁해도 줄지 않고 마감이 깔끔해요</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1109,7 +1145,7 @@
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>리뷰 내용 자연어 검색</t>
+          <t>리뷰 내용 직접 검색</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
@@ -1117,19 +1153,24 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>reviews:259000004</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>[reviews:259000000] reviews:259000000  ▸  reviews: 세탁해도 줄지 않고 마감이 깔끔해요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 보통이에요 | 착용감 | 아주편해요 | 259000000 | 12800000 | 중</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>reviews:259000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>q012</t>
+          <t>q011</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>LBL코리아 판매 파트너</t>
+          <t>엄마 선물로 구매했는데 너무 좋아하세요</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1137,7 +1178,7 @@
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>판매 파트너사 검색</t>
+          <t>리뷰 내용 자연어 검색</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
@@ -1145,19 +1186,24 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>sales_partners:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>[reviews:259000004] reviews:259000004  ▸  reviews: 엄마 선물로 구매했는데 너무 좋아하세요. 입으면 편안해요 | 사이즈 | 핏 | 넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000004 | 12800000 | 큼</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>reviews:259000004</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>q013</t>
+          <t>q012</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>OneTV MC 방송 채널</t>
+          <t>LBL코리아 판매 파트너</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1165,7 +1211,7 @@
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>판매 채널 검색</t>
+          <t>판매 파트너사 검색</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
@@ -1173,19 +1219,24 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>sales_channels:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>[sales_partners:2] sales_partners:2  ▸  sales_partners: 2 | [NEC]패션사업부 | LBL코리아주식회사</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>sales_partners:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>q014</t>
+          <t>q013</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>pgm_time 23:00-23:50 broadcast 12800000</t>
+          <t>OneTV MC 방송 채널</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -1193,7 +1244,7 @@
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>방송 시간+상품코드 속성 검색</t>
+          <t>판매 채널 검색</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -1201,19 +1252,24 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>broadcasts:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>[sales_channels:1] sales_channels:1  ▸  sales_channels: MC | 1 | EC | MC | OneTV(MC)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>sales_channels:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>q015</t>
+          <t>q014</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>데님 A라인 미디 스커트</t>
+          <t>pgm_time 23:00-23:50 broadcast 12800000</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1221,13 +1277,51 @@
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>소재+디자인 복합 검색</t>
+          <t>방송 시간+상품코드 속성 검색</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>[broadcasts:1] broadcasts:1  ▸  broadcasts: 1 | 12800000 | 2024-11-15 | 23:00-23:50 | 2024-11-20 | 2024-11-28</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>broadcasts:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>q015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>데님 A라인 미디 스커트</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>소재+디자인 복합 검색</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>[products:12800006] products:12800006  ▸  products: 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>products:12800006</t>
         </is>
@@ -1244,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1254,7 +1348,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1303,93 +1398,74 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>a001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>봄 시즌 신상 니트웨어</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>25SS 울 캐시미어 니트를 시즌+카테고리로 패러프레이즈</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>products:12800004</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>a002</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>여름용 가볍고 시원한 하의</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1405,7 +1481,7 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>린넨 와이드 밴딩 슬랙스를 속성으로 검색</t>
+          <t>25SS 울 캐시미어 니트를 시즌+카테고리로 패러프레이즈</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -1413,35 +1489,40 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>products:12800009</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>[products:12800004] products:12800004  ▸  products: 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>products:12800004</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>a003</t>
+          <t>a002</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>가장 많이 팔린 상품의 리뷰</t>
+          <t>여름용 가볍고 시원한 하의</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>cross_table</t>
+          <t>paraphrase</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>products(cumulative_sales) + reviews 교차</t>
+          <t>린넨 와이드 밴딩 슬랙스를 속성으로 검색</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
@@ -1449,19 +1530,24 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>products:12800000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>[products:12800009] products:12800009  ▸  products: 24SS 린넨 와이드 밴딩 슬랙스 | LBL 시즌2025 S/S NO.1 | 24SS | 12800009 | 99900.0 | 20.0 | 4416 | 441158400.0</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>products:12800009</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>a004</t>
+          <t>a003</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>방송 후 주문이 가장 많았던 상품</t>
+          <t>가장 많이 팔린 상품의 리뷰</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1477,7 +1563,7 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>broadcasts + orders 교차</t>
+          <t>products(cumulative_sales) + reviews 교차</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -1485,35 +1571,40 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
+          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
           <t>products:12800000</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>a005</t>
+          <t>a004</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>9만원 이상 고가 상품 목록</t>
+          <t>방송 후 주문이 가장 많았던 상품</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>cross_table</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>selling_price &gt;= 90000 필터</t>
+          <t>broadcasts + orders 교차</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -1521,19 +1612,24 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>products:12800001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>a006</t>
+          <t>a005</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>할인율이 적용된 상품</t>
+          <t>9만원 이상 고가 상품 목록</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1549,7 +1645,7 @@
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>discount_rate &gt; 0 필터</t>
+          <t>selling_price &gt;= 90000 필터</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
@@ -1557,41 +1653,94 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>products:12800000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>[products:12800001] products:12800001  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>products:12800001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>a007</t>
+          <t>a006</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>색상별 상품 변형 개수</t>
+          <t>할인율이 적용된 상품</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>aggregation</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
+          <t>discount_rate &gt; 0 필터</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>a007</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>색상별 상품 변형 개수</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>product_variants GROUP BY color_id → count</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>[colors:1] colors:1  ▸  colors: 소라 | 1
+[colors:4] colors:4  ▸  colors: 네이비 | 4
+[colors:5] colors:5  ▸  colors: 블랙 | 5</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>colors:1
 colors:4
@@ -1599,37 +1748,44 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>a008</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>시즌별 상품 수</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>products GROUP BY season → count (25SS: 29, 24SS: 32, 24FW: 19)</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+[products:12800001] products:12800001  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
+[products:12800005] products:12800005  ▸  products: 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>products:12800000
 products:12800001
@@ -1637,51 +1793,15 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>a009</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>핏이 타이트하다는 불만이 있는 상품</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>review_sentiment</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>attribute_2_value='타이트해요' 리뷰 검색</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>reviews:259000002</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>a010</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>착용감이 좋다는 후기가 많은 제품</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1697,117 +1817,134 @@
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
+          <t>attribute_2_value='타이트해요' 리뷰 검색</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[reviews:259000002] reviews:259000002  ▸  reviews: 촉감도 좋고 핏도 라인이 예뻐요 ^^만족합니다 | 사이즈 | 핏 | 타이트해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000002 | 12800000 | 중</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>reviews:259000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>a010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>착용감이 좋다는 후기가 많은 제품</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>review_sentiment</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>attribute_4_value='아주편해요' 리뷰 검색</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[reviews:259000000] reviews:259000000  ▸  reviews: 세탁해도 줄지 않고 마감이 깔끔해요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 보통이에요 | 착용감 | 아주편해요 | 259000000 | 12800000 | 중
+[reviews:259000004] reviews:259000004  ▸  reviews: 엄마 선물로 구매했는데 너무 좋아하세요. 입으면 편안해요 | 사이즈 | 핏 | 넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000004 | 12800000 | 큼</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>reviews:259000000
 reviews:259000004</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>a011</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>엄마 생일 선물로 괜찮은 옷 추천해줘. 편하고 품질 좋은 걸로</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>conversational</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>L7</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>자연어 대화체 상품 추천</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+[products:12800004] products:12800004  ▸  products: 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>products:12800000
 products:12800004</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>a012</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>사이즈 55인데 이 브랜드 옷 넉넉한 편이야 작은 편이야?</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>conversational</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>L7</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>리뷰 기반 사이즈 감 질문</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>sizes:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>a013</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>LBL코리아 파트너사가 판매하는 상품들</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>cross_table</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>L3</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>sales_partners + orders + products 3-hop 교차</t>
+          <t>리뷰 기반 사이즈 감 질문</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
@@ -1815,35 +1952,40 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>sales_partners:2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>[sizes:2] sizes:2  ▸  sizes: 55 | 2</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>sizes:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>a014</t>
+          <t>a013</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2024년 11월에 방송된 상품</t>
+          <t>LBL코리아 파트너사가 판매하는 상품들</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>temporal</t>
+          <t>cross_table</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>broadcast_date 필터</t>
+          <t>sales_partners + orders + products 3-hop 교차</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -1851,41 +1993,93 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>broadcasts:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>[sales_partners:2] sales_partners:2  ▸  sales_partners: 2 | [NEC]패션사업부 | LBL코리아주식회사</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>sales_partners:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>a015</t>
+          <t>a014</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>24FW 시즌 전체 상품 목록</t>
+          <t>2024년 11월에 방송된 상품</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>exhaustive</t>
+          <t>temporal</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
+          <t>broadcast_date 필터</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>[broadcasts:1] broadcasts:1  ▸  broadcasts: 1 | 12800000 | 2024-11-15 | 23:00-23:50 | 2024-11-20 | 2024-11-28</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>broadcasts:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>a015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>24FW 시즌 전체 상품 목록</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>exhaustive</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
           <t>season=24FW 전수 열거 (19개)</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>[products:12800005] products:12800005  ▸  products: 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0
+[products:12800006] products:12800006  ▸  products: 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>products:12800005
 products:12800006</t>
@@ -1903,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1913,7 +2107,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1958,124 +2153,158 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>q001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>온실가스 감축 및 에너지 절약 계획은 어떻게 되어있나</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>ESG 및 지속가능성</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 온실가스 + 감축</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[8ff32e537262bfa2] 2020년도_(요약) 2020년 온실가스 감축 및 에너지 절약 업무 추진 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-04-08 16:01:49 &lt;/Document-Metadat
+[d986946925263cee] 2020년도_2020년 온실가스 감축 및 에너지 절약 추진 계획(안) #13  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2011-01-14 09:36:36   수정일: 2020-04-09 11:45:30 &lt;/Document-M</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>8ff32e537262bfa2
 d986946925263cee</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>q002</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>재활힐링승마 사업 운영계획</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>복지 및 교육</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 재활힐링승마</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[9293b657686b140c] 2020년도_200214 (요약) 2020년도 재활힐링승마센터 운영계획(안)ver.6 #14  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: Ryu   작성일: 2020-01-04 13:13:33   수정일: 2020-02-14 11:06:37 &lt;/Document-Metadata&gt;
+[4c2beab48a4fa8ba] 2020년도_200304 (보고)2020년도 재활힐링승마 사업 전략적 홍보방안ver.5 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-05 15:19:27 &lt;/Document-M
+[d3ab6e9ee63de321] 2020년도_200304 2020년도 재활힐링승마 사업 전략적 홍보방안ver.3 #34  ▸  &lt;Document-Metadata&gt;   제목: □    작성자: Ryu   마지막 수정자: Ryu   작성일: 2020-02-20 15:14:45   수정일: 2020-03-04 18:17:25 &lt;/Document-
+[75f6189810773545] 2022년도_재활힐링승마 고도화를 위한 시범과정 운영계획(안) #38  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-03-05 12:48:37   수정일: 2023-04-30 16:21:05 &lt;/Document-Metadata&gt;
+[ae69bf434db74361] 2024년도_재활힐링승마 표준 프로그램 개발연구 시행 계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: □ 2023년 재활힐링승마 시범과정 운영에 따른 사례분석 약식 연구결과   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-05 13:45:52
+[e26613430bc0f1b8] 2020년도_200214 2020년도 재활힐링승마센터 운영계획(안)ver.9 #88  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: Ryu   작성일: 2020-01-04 13:13:33   수정일: 2020-02-14 11:06:08 &lt;/Documen
+[844757da66c84d87] 2024년도_(붙임) 2024년 재활힐링승마 운영 계획(안) #35  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-24 10:15:58   수정일: 2024-02-04 17:57:34 &lt;/Documen</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>9293b657686b140c
 4c2beab48a4fa8ba
@@ -2087,82 +2316,96 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>q003</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>인재개발 기본계획</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>규정 및 지침</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 인재개발 + 기본계획</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[790f2015dc65b6e1] 2020년도_(붙임#2) 2020년 인재개발 기본계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 인 사 노 무 처   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-02 10:20:11   수정일: 2020-02-27 16:52:55 &lt;/Do
+[33ad8cb9e391ffb3] 2020년도_(붙임#1) 인재개발 기본계획(안) 요약 #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-27 16:38:24 &lt;/Documen</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>790f2015dc65b6e1
 33ad8cb9e391ffb3</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>q004</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>인권영향평가 결과</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>인권경영</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 인권영향평가</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[0cf478ddca6e92d5] 2023년도_붙임4 2023년 주요사업 인권영향평가 체크리스트(최종) #29  ▸  &lt;Document-Metadata&gt;   작성자: USER   마지막 수정자: KRA   작성일: 2018-09-04 19:31:17   수정일: 2023-12-21 06:44:31 &lt;/Document-Metadata
+[e507dc22077335c1] 2020년도_별첨_2020년 인권영향평가 결과보고 #14  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2020-11-20 14:17:59   수정일: 2021-05-29 15:46:09 &lt;/Documen
+[dd206af597e56188] 2023년도_붙임1 2023년 인권영향평가 결과보고(최종)★_231222 #11  ▸  &lt;Document-Metadata&gt;   제목: 경영관리처   작성자: KRA   마지막 수정자: KRA   작성일: 2023-12-13 14:18:25   수정일: 2023-12-22 10:01:55 &lt;/Docume
+[005599102a43b8f4] 2023년도_붙임3 2023년 기관운영 인권영향평가 체크리스트(최종) #104  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-09-20 01:25:07   수정일: 2023-12-21 06:47:49 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>0cf478ddca6e92d5
 e507dc22077335c1
@@ -2171,41 +2414,54 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>q005</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>교배실적과 교배횟수</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>경마산업관리</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 교배</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>[2b77cb92e3b2e52e] 2020년도_붙임3. 2020년 총 교배횟수(모든교배내역) #144  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:38:42 &lt;/Document-Metadata&gt;
+[6cdb3f17c1eafe48] 2020년도_붙임2. 2020년 총 교배실적(두수) #111  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:36:12 &lt;/Document-Metadata&gt;
+[bbe40d855e6cc165] 2021년도_경주마 교배 및 번식분야 복지 가이드라인 수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-02 15:44:31 &lt;/Document-M
+[72b1245e55ab96fc] 2021년도_경주마 교배 및 번식분야 복지 가이드라인(안) #17  ▸  &lt;Document-Metadata&gt;   제목: 한국마사회 교배 및 번식 말 복지 가이드라인 초안    작성자: User2007   마지막 수정자: KRA   작성일: 2021-08-07 21:34:58   수정일:
+[57ae80a2b693d18f] 2020년도_붙임4. 2020년 유상교배 수익내역 #6  ▸  &lt;Document-Metadata&gt;   작성자: user   마지막 수정자: KRA   작성일: 2013-10-13 05:56:53   수정일: 2020-12-11 01:28:30 &lt;/Document-Metadata
+[43b8261fe9a4b3ca] 2020년도_@ (결재상신) 2020년 경주마 생산 및 교배지원 결과보고 @ #19  ▸  &lt;Document-Metadata&gt;   제목: 2002. 내륙 민간목장 생산 및 교배지원 결과   작성자: 한국마사회 원당목장팀 대리 임진호   키워드: 
+    설명: 
+    마지막 수정자: KRA
+[e39b4656a5219700] 2020년도_@ (요약) 2020년 경주마 생산 및 교배지원 결과보고 @ #3  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-12-17 11:13:23 &lt;/Document-Metadat</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>2b77cb92e3b2e52e
 6cdb3f17c1eafe48
@@ -2217,82 +2473,96 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>q006</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>한국마사회 인권침해 구제절차 매뉴얼</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>인권경영</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 인권침해 + 구제</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>[803aa364d8f1f722] 2021년도_(별첨) 한국마사회 인권침해 구제절차 및 예방활동 매뉴얼(202112) #0  ▸  &lt;Document-Metadata&gt;   제목: 2017   작성자: ROEN11   마지막 수정자: KRA   작성일: 2017-11-20 09:30:38   수정일: 2023-04-13 13:51:00 &lt;/Docu
+[e074f8fc80056924] 2023년도_(별첨) 한국마사회 인권침해 구제절차 및 예방활동 매뉴얼(202112) #0  ▸  &lt;Document-Metadata&gt;   제목: 2017   작성자: ROEN11   마지막 수정자: KRA   작성일: 2017-11-20 09:30:38   수정일: 2023-04-13 13:51:00 &lt;/Docu</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>803aa364d8f1f722
 e074f8fc80056924</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>q007</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>이용자보호 추진계획</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>업무추진 및 실적</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 이용자보호</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>[3b6b26357ad2ce21] 2020년도_(요약) 2020년 이용자보호 추진계획 보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-21 13:18:29 &lt;/Document-M
+[24413d0baba3f505] 2020년도_(붙임)'20 이용자보호 현업과제 운영계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제도 확산   작성자: KRA   마지막 수정자: KRA   작성일: 2020-06-12 15:43:26   수정일: 2020-07-25 17:48:38 &lt;/Docume
+[d4d20ca93dfcd728] 2020년도_(본문) 2020년 이용자보호 추진계획 #15  ▸  &lt;Document-Metadata&gt;   제목: 회의자료    작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-19 16:10:55   수정일: 2020-03-21 10:39:32 &lt;/Docume
+[5d0dd8502b5a0cb8] 2020년도_(본문) 20년 이용자보호 액션플랜 수립계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 제목    작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-16 09:57:57   수정일: 2020-02-09 15:46:56 &lt;/Document</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>3b6b26357ad2ce21
 24413d0baba3f505
@@ -2301,82 +2571,95 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>q008</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>한국 경주마 국제 레이팅 현황</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>listing</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>경마산업관리</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 국제 + 레이팅</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[012dcbe84f52c595] 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Me
+[2df376eb9253a430] 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Me</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>012dcbe84f52c595
 2df376eb9253a430</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>q009</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>윤리경영 기본계획과 사회적가치</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ESG 및 지속가능성</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 윤리경영 + 기본계획</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[d13b5751987d7a60] 2021년도_(본문) 사회적가치 실현을 위한 2021년 윤리경영 기본계획(안) #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-02 16:19:40   수정일: 2021-07-15 10:25:51 &lt;/Document-Metadata&gt;
+[d908c9b95b9e082a] 2021년도_(요약) 2021년 윤리경영 기본계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2021-07-15 10:
+[8c423366bc12e4d4] 2023년도_★(결재) 2023년 윤리경영 기본계획(이사회 의견 반영 후)★ #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-06-11 15:07:02   수정일: 2023-07-01 14:03:33 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>d13b5751987d7a60
 d908c9b95b9e082a
@@ -2384,41 +2667,48 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>q010</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>사업별 조직별 예산 계층구조</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>listing</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>운영계획</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 사업별 + 조직별 + 예산</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[a4ed66c59a820e40] 2020년도_(붙임#14) 사업별 조직별 예산 계층구조 #78  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-11 08:44:57   수정일: 2020-03-13 01:24:08 &lt;/Document-Metadata&gt;
+[da8efb3618249a33] 2022년도_[붙임2] 2023년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-15 02:28:16   수정일: 2023-02-16 04:38:18 &lt;/Document-Metadata&gt;
+[aa6aff98e2caa723] 2023년도_[붙임2] 2024년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-14 07:46:48   수정일: 2024-01-31 07:29:46 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>a4ed66c59a820e40
 da8efb3618249a33
@@ -2426,163 +2716,189 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>q011</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>예산 및 기금운용계획 집행지침</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>규정 및 지침</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 예산 + 기금운용 + 집행지침</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[436d43261922a8da] 2020년도_(기재부) 2020년도 예산 및 기금운용계획집행지침 #120  ▸  &lt;Document-Metadata&gt;   제목: ?    작성자: Owner   키워드: 
+    설명: 
+    마지막 수정자: mafra   작성일: 2005-01-14 10:13:01   수정일: 20
+[4196a8bfffd7ea93] 2024년도_[붙임3] (기재부) 2024년도 예산 및 기금운용계획 집행지침 #282  ▸  &lt;Document-Metadata&gt;   Version Tagetapplication: WORDPROCESSOR   Version Major: 5   Version Minor: 0   Version Micro: 5</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>436d43261922a8da
 4196a8bfffd7ea93</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>q012</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>내부경영평가제도 개선 방안</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>규정 및 지침</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 내부경영평가</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>[27325f8e49d559f4] 2020년도_(본문) 2020년도 내부경영평가제도 개선(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-22 09:53:12 &lt;/Documen
+[06ea8eb0c6498c61] 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-M</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>27325f8e49d559f4
 06ea8eb0c6498c61</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>q013</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>지사 고객입장 및 방역관리 방안</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>규정 및 지침</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 방역</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>[36f5479362d3d864] 2020년도_201020 지사 고객입장 및 방역관리 방안(최종) #25  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-10-16 08:23:47   수정일: 2020-10-20 18:44:49 &lt;/Documen</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>36f5479362d3d864</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>q014</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>스마트 사무환경 구축 및 망분리 개선</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>정보기술 시스템</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 스마트 + 망분리</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>[afd0f60cc9c978c0] 2022년도_붙임 1. 스마트 사무환경 구축 및 망분리 개선 견적서(총괄) #27  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-02 04:07:54   수정일: 2023-08-17 03:33:36 &lt;/Document-Metadata&gt;
+[9d226cce773a4434] 2022년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen
+[993ad9a5e29994fc] 2023년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>afd0f60cc9c978c0
 9d226cce773a4434
@@ -2590,41 +2906,49 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>q015</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>재물조사 결과 내역</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>listing</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>조사 및 평가</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 재물조사</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>[c8ed7811592eac64] 2022년도_(붙임2)재물조사결과내역(전체) #393  ▸  &lt;Document-Metadata&gt;   작성일: 2025-12-05 08:14:00   수정일: 2025-12-05 08:14:00 &lt;/Document-Metadata&gt;  [Page Number: 394]  &lt;tab
+[59854a9e60c7d3ab] 2022년도_(붙임2)재물조사결과내역(전체) #106  ▸  &lt;Document-Metadata&gt;   작성자: KA B &lt;/Document-Metadata&gt;  [Sheet: 전체] [Table Chunk 107/107] | 자산번호 | SAP자산번호 | 자산구분 | 세분류 |
+[6a278de5a7f63982] 2022년도_(붙임1)2022년 정기 재물조사 실시 결과보고 #9  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-23 10:36:27   수정일: 2023-01-19 14:22:42 &lt;/Documen
+[95765c577ef9e336] 2024년도_(붙임1) 2024년 재물조사 시행 결과보고_241227 #15  ▸  &lt;Document-Metadata&gt;   제목: 재물조정   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-12 16:02:40   수정일: 2024-12-27 09:49:24 &lt;/Documen</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>c8ed7811592eac64
 59854a9e60c7d3ab
@@ -2633,164 +2957,207 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>q016</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>2024년 정보화기기 교체 계획</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>정보기술 시스템</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 정보화기기 + 교체</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>[e4f72caaf5619284] 2023년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;
+[7d016a8eb300196a] 2024년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>e4f72caaf5619284
 7d016a8eb300196a</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>q017</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>도심승마체험 시행계획</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>승마 행사 및 대회</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 도심승마</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>[1dd7a41b6d49067a] 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-M
+[68c173524cf22c47] 2020년도_붙임_1_2020년 도심승마체험 시행계획(요약, 최종) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-03-07 18:01:46 &lt;/Document-Metadat</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>1dd7a41b6d49067a
 68c173524cf22c47</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>q018</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>KPC 개최계획</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>factoid</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>승마 행사 및 대회</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: KPC</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>[a5a7f37b741bdeee] 2020년도_제2차 KPC 개최계획(안) 최종 #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-21 09:21:54   수정일: 2020-08-21 17:42:45 &lt;/Document-Metadata&gt;
+[33640ab36a7a2b8c] 2024년도_2024년 제 2차 KPC 개최 심의 안건 #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-18 12:53:46 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>a5a7f37b741bdeee
 33640ab36a7a2b8c</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>q019</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>말산업 연구사업 과제 목록</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>listing</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>경마산업관리</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 말산업 + 연구</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>[dd534b8aff2c0b47] 2023년도_(별첨2)말산업 연구사업 과제목록(13-23) #23  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2024-03-30 11:46:30 &lt;/Document-Metadata&gt;
+[858311a17598e098] 2024년도_(별첨2)말산업 연구사업 과제목록(13-23) #23  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2024-03-30 11:46:30 &lt;/Document-Metadata&gt;
+[37d0fe4807f770c9] 2020년도_2020년 말산업 연구사업 추진계획(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2020-05-30 14:55:48 &lt;/Document-M
+[665c95e2452936a4] 2021년도_2021년 말산업 연구사업 추진계획(요약,결재용) #3  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-05-08 09:19:09 &lt;/Documen
+[6498c34e04755c85] 2021년도_[붙임2] 2021년 말산업 분야 기술상용화 연구 추진계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-06-20 11:32:59 &lt;/Documen
+[ca05784c3e5aac4f] 2023년도_2023년 말산업 연구사업 추진계획(요약) #2  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2023-04-05 15:06:47 &lt;/Documen
+[9ef0a8ba81ba8b76] 2024년도_2024년 말산업연구소 주요사업 추진계획(본문)  ▸  2024년도_2024년 말산업연구소 주요사업 추진계획(본문)
+[5751364a07bd6432] 2022년도_(별첨2)말산업연구소 연구과제 목록('13_'22) #22  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2023-04-05 01:26:43 &lt;/Document-Metadata&gt;
+[a327f99bb35ec842] 2020년도_2020년 말산업 연구사업 추진계획(요약) #2  ▸  &lt;Document-Metadata&gt;   작성자: 류성훈   마지막 수정자: KRA   작성일: 2014-07-03 13:36:03   수정일: 2020-05-30 15:39:20 &lt;/Document-Metadata&gt;
+[72abd3a0e6e49e3b] 2020년도_[붙임1] 2020년 말산업 분야 위탁연구과제 추진 계획(안) #7  ▸  &lt;Document-Metadata&gt;   제목: 2016   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-25 11:04:51   수정일: 2020-06-24 16:38:49 &lt;/Documen
+[7391433818c2aa29] 2021년도_2021년 말산업 연구사업 추진계획(안,결재용) #10  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2021-05-09 17:06:29 &lt;/Document-M
+[fd1f3b6cb4f3c808] 2021년도_[붙임1] 2021년 말산업 분야 기술상용화 연구 추진계획(요약) #4  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-06-20 11:32:44 &lt;/Documen
+[69aa111c4c3c9c4e] 2023년도_2023년 말산업 연구사업 변경 및 신규과제 추진계획(요약) #3  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2023-12-21 10:35:31 &lt;/Documen
+[425d5a095aa05d99] 2023년도_2023년 말산업 연구사업 추진계획(본문) #16  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2023-04-05 15:01:17 &lt;/Document-M
+[530eee4771fc7f6a] 2023년도_2023년 말산업연구소 주요사업 추진계획(본문)  ▸  2023년도_2023년 말산업연구소 주요사업 추진계획(본문)
+[3069278768910766] 2023년도_2023년 말산업연구소 주요사업 추진계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2023-03-09 15:45:08 &lt;/Documen
+[dce393b4643910d6] 2023년도_23년_말산업_R&amp;D_연구과제_변경_및 _추진계획(안)) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-12-21 09:45:12 &lt;/Document-M
+[7b6883061d74991f] 2024년도_2024년 말산업 연구사업 추진계획(본문) #25  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2024-03-31 10:52:49 &lt;/Document-M
+[c7acbf436686b08b] 2024년도_2024년 말산업 연구사업 추진계획(요약) #12  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2024-03-31 11:13:34 &lt;/Documen
+[f7f1618283b6dd00] 2024년도_2024년 말산업연구소 주요사업 추진계획(본문)  ▸  2024년도_2024년 말산업연구소 주요사업 추진계획(본문)
+... +2 more</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>dd534b8aff2c0b47
 858311a17598e098
@@ -2817,41 +3184,46 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>q020</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>마주 경제적기준 연도별 현황</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>listing</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>경마산업관리</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Keyword seed: 마주 + 경제적기준</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>[157016074626f25d] 2021년도_(별첨1) 연도별 마주 경제적기준(2007_2021) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-20 01:23:19   수정일: 2021-11-26 04:01:22 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>157016074626f25d</t>
         </is>
@@ -2868,7 +3240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2878,7 +3250,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2923,81 +3296,74 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>g001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2020년부터 2024년까지 '인권영향평가'를 주제로 다루는 '규정 및 지침' 카테고리 문서는 연도별로 몇 개씩 있는가?</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>A_aggregation</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>g002</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>KRA의 예산 관련 문서('예산', '집행지침', '전용', '세부내역' 키워드 포함) 총 개수와 카테고리별 분포</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -3012,16 +3378,17 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>g003</t>
+          <t>g002</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>전체 1,110개 문서 중 '평가' 개념이 포함된 문서(내부경영평가, 인권영향평가, 재물조사평가, ESG경영진단 등)의 비율은 얼마인가?</t>
+          <t>KRA의 예산 관련 문서('예산', '집행지침', '전용', '세부내역' 키워드 포함) 총 개수와 카테고리별 분포</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -3036,23 +3403,24 @@
         <v>0</v>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>g004</t>
+          <t>g003</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>'2021년 윤리경영 기본계획'과 '인권경영 실행지침 일부 개정(안)'에서 공통으로 언급되는 위원회 또는 조직명은 무엇인가?</t>
+          <t>전체 1,110개 문서 중 '평가' 개념이 포함된 문서(내부경영평가, 인권영향평가, 재물조사평가, ESG경영진단 등)의 비율은 얼마인가?</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>B_set_ops</t>
+          <t>A_aggregation</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -3060,16 +3428,17 @@
         <v>0</v>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>g005</t>
+          <t>g004</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>'사업별 조직별 예산 계층구조' 2020년 문서와 2023년 문서를 비교했을 때, 2020년에는 있었으나 2023년에 사라진 사업/조직은?</t>
+          <t>'2021년 윤리경영 기본계획'과 '인권경영 실행지침 일부 개정(안)'에서 공통으로 언급되는 위원회 또는 조직명은 무엇인가?</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -3084,16 +3453,17 @@
         <v>0</v>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>g006</t>
+          <t>g005</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>'경주마 국제 레이팅' 관련 문서들이 참조하는 등급 체계와 '대상경주 레이스 레이팅' 문서들이 참조하는 등급 체계의 합집합</t>
+          <t>'사업별 조직별 예산 계층구조' 2020년 문서와 2023년 문서를 비교했을 때, 2020년에는 있었으나 2023년에 사라진 사업/조직은?</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -3108,23 +3478,24 @@
         <v>0</v>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>g007</t>
+          <t>g006</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2020년 '지사 고객입장 및 방역관리 방안'(코로나 대응)이 2021~2024년 어떤 규정/계획 문서로 반영되거나 대체됐는가?</t>
+          <t>'경주마 국제 레이팅' 관련 문서들이 참조하는 등급 체계와 '대상경주 레이스 레이팅' 문서들이 참조하는 등급 체계의 합집합</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>C_temporal</t>
+          <t>B_set_ops</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
@@ -3132,16 +3503,17 @@
         <v>0</v>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>g008</t>
+          <t>g007</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2020~2024년 '인재개발 기본계획' 연차별 문서 비교 — 매년 새로 추가된 교육 프로그램과 중단된 프로그램</t>
+          <t>2020년 '지사 고객입장 및 방역관리 방안'(코로나 대응)이 2021~2024년 어떤 규정/계획 문서로 반영되거나 대체됐는가?</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -3156,16 +3528,17 @@
         <v>0</v>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="I14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="80" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>g009</t>
+          <t>g008</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>'내부경영평가제도'가 2020년 개선(안) 이후 몇 번 개정됐고 주요 변화점은 무엇인가?</t>
+          <t>2020~2024년 '인재개발 기본계획' 연차별 문서 비교 — 매년 새로 추가된 교육 프로그램과 중단된 프로그램</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -3180,23 +3553,24 @@
         <v>0</v>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>g010</t>
+          <t>g009</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>KPC 개최계획에 등장하는 '부서' 중에서, 같은 해 인권영향평가 대상 부서 목록에 포함된 부서는?</t>
+          <t>'내부경영평가제도'가 2020년 개선(안) 이후 몇 번 개정됐고 주요 변화점은 무엇인가?</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>D_multi_hop</t>
+          <t>C_temporal</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -3204,16 +3578,17 @@
         <v>0</v>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="80" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>g011</t>
+          <t>g010</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2020년 '내부경영평가제도 개선(안)'에서 제안된 평가 항목 중, 실제로 이후 연도의 경영실적 보고서에 반영된 항목은 무엇인가?</t>
+          <t>KPC 개최계획에 등장하는 '부서' 중에서, 같은 해 인권영향평가 대상 부서 목록에 포함된 부서는?</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -3228,16 +3603,17 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="80" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>g012</t>
+          <t>g011</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024년 '정보화기기 교체 계획'이 참조하거나 근거로 삼은 예산 규정 및 집행지침은 무엇이며, 그 지침들의 상위 법적 근거 문서는?</t>
+          <t>2020년 '내부경영평가제도 개선(안)'에서 제안된 평가 항목 중, 실제로 이후 연도의 경영실적 보고서에 반영된 항목은 무엇인가?</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -3252,23 +3628,24 @@
         <v>0</v>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="80" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>g013</t>
+          <t>g012</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>KRRA 문서 네트워크에서 '다른 문서들이 가장 많이 참조하는 핵심 규정' top 5 (in-degree 기준)</t>
+          <t>2024년 '정보화기기 교체 계획'이 참조하거나 근거로 삼은 예산 규정 및 집행지침은 무엇이며, 그 지침들의 상위 법적 근거 문서는?</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>E_structural</t>
+          <t>D_multi_hop</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -3276,16 +3653,17 @@
         <v>0</v>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="I19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="80" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>g014</t>
+          <t>g013</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>'규정 및 지침' 카테고리 내에서 상호 참조가 가장 밀집된 규정 묶음(community) 1개와 그에 속한 문서 목록</t>
+          <t>KRRA 문서 네트워크에서 '다른 문서들이 가장 많이 참조하는 핵심 규정' top 5 (in-degree 기준)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -3300,23 +3678,24 @@
         <v>0</v>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="I20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="80" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>g015</t>
+          <t>g014</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2022년 이후 발간된 '인권경영' 카테고리 문서 중, 본문에 '위원회'가 3회 이상 등장하고 제목에 '개정' 또는 '지침'이 포함된 문서</t>
+          <t>'규정 및 지침' 카테고리 내에서 상호 참조가 가장 밀집된 규정 묶음(community) 1개와 그에 속한 문서 목록</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>F_constraint</t>
+          <t>E_structural</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -3324,6 +3703,32 @@
         <v>0</v>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>g015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2022년 이후 발간된 '인권경영' 카테고리 문서 중, 본문에 '위원회'가 3회 이상 등장하고 제목에 '개정' 또는 '지침'이 포함된 문서</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>F_constraint</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3336,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3346,7 +3751,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3395,79 +3801,121 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>h001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>말 복지 향상을 위한 프로그램</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>재활힐링승마를 직접 언급하지 않고 의미로 검색</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[0346542e0be2b2ab] 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Documen
+[123f03df3479517e] 2022년도_[별첨1] KRA-ESG경영 진단모델(세부 진단기준)_최종 #43  ▸  &lt;Document-Metadata&gt;   제목: 《 KRA   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-04 14:33:57   수정일: 2023-05-27 10:21:04 &lt;/Docume
+[156fec294ba67ae4] 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-M
+[210e0e2db641965a] 2020년도_[붙임 1] 2020년 재활승마 활성화 지원 시범사업 계획(안_요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 말산업육성본부   작성자: KRA   마지막 수정자: KRA   작성일: 2017-05-24 17:59:41   수정일: 2020-08-07 15:31:04 &lt;/Docu
+[2212a005847a8f98] 2023년도_2023년 힐링승마 지원사업 추진 계획(안)_220308_2 #43  ▸  &lt;Document-Metadata&gt;   제목: 목 적   작성자: KRA   설명: |Fasoo_Trace_ID:eyJub2RlMSI6eyJkc2QiOiIwMTAwMDAwMDAwMDAxODMwIiwibG9nVGltZ
+[27dcbb61e82d6f82] 2024년도_과제 및 사업별 담당부서 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-08 02:27:01   수정일: 2024-06-13 05:02:20 &lt;/Document-Metadata&gt;
+[2a67e1073fe83029] 2022년도_2022 힐링승마 지원사업 운영 결과보고_221222 #25  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-08-06 09:18:55   수정일: 2022-12-22 18:09:26 &lt;/Document-Metadata&gt;
+[2d94f6c769030bda] 2020년도_경주마 통합 건강관리시스템 추진계획(안) #19  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2020-05-27 10:31:20 &lt;/Document-M
+[33882770624ec69f] 2022년도_「말의 인도적인 처리 가이드라인」수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2022-12-21 14:48:38 &lt;/Document-M
+[345beb807d95ba70] 2020년도_★(결재) 2020 사회공익힐링 승마 사업 기본 운영 계획 #5  ▸  &lt;Document-Metadata&gt;   제목: 2019 전국민 승마체험 사업 기본계획   작성자: user   마지막 수정자: KRA   작성일: 2019-02-15 13:56:48   수정일: 2020-02-26
+[386c3d238d9e12b0] 2021년도_(요약) 2021 사회공익 힐링승마 사업 결과보고 #4  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-23 17:48:23 &lt;/Document-M
+[3b4dc85349de4eae] 2023년도_(요약) 말등록부 연간 업무 추진계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-21 11:12:57 &lt;/Document-M
+[3fe2d89ca01994f0] 2023년도_[붙임1] 해외종축개발운영위원회규정 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: 2170058   작성일: 2014-08-15 11:42:18   수정일: 2024-05-26 10:50:28 &lt;/Docume
+[40122ffcb05effea] 2020년도_★(요약) 2020 사회공익힐링 승마 사업 기본 운영 계획 #10  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-04 13:13:33   수정일: 2020-02-26 16:19:50 &lt;/Document-Metadata&gt;
+[4c2beab48a4fa8ba] 2020년도_200304 (보고)2020년도 재활힐링승마 사업 전략적 홍보방안ver.5 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-05 15:19:27 &lt;/Document-M
+[4cb0ece55fc920e7] 2023년도_(요약) 2023년 말복지센터 업무 추진계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 2022   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-18 10:11:25   수정일: 2023-02-09 09:59:44 &lt;/Documen
+[4f2b02c85a84bf0f] 2024년도_2. 2024년 경주마 토탈 케어시스템 운영 계획(안) 1부 #23  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-02-04 09:56:05 &lt;/Document-Met
+[4f5b39b0938daff2] 2024년도_(붙임 1) 말용도 다각화 추진계획_요약 #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-06-01 17:40:16 &lt;/Document-M
+[54275dff6b495fb6] 2024년도_1. 2024년 경주마 토탈 케어시스템 운영 계획(안) 1부(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 2022   작성자: KRA   마지막 수정자: KRA   작성일: 2022-04-17 09:56:03   수정일: 2024-02-03 17:32:13 &lt;/Documen
+[551eb387c7145222] 2024년도_[붙임1] 해외종축개발운영위원회규정 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: 2170058   작성일: 2014-08-15 11:42:18   수정일: 2024-05-26 10:50:28 &lt;/Docume
+... +47 more</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>0346542e0be2b2ab
 123f03df3479517e
@@ -3539,37 +3987,53 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>h002</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>직원들의 역량 강화 교육 방안</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>인재개발 기본계획을 다른 표현으로</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[1c2e14b3e46641c4] 2023년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-M
+[33ad8cb9e391ffb3] 2020년도_(붙임#1) 인재개발 기본계획(안) 요약 #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-27 16:38:24 &lt;/Documen
+[34ee099eaee5f3ae] 2022년도_(본문) 경주마관계자 임시조치 개선계획(안) #34  ▸  &lt;Document-Metadata&gt;   제목: 2022년 교육훈련 기본계획   작성자: KRA   마지막 수정자: KRA   작성일: 2022-03-04 14:47:46   수정일: 2022-11-11 16:14:3
+[3c78d27b62aca0f0] 2022년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-M
+[5cf871e3bcad9e3b] 2025년도_(붙임3) 2025년 한국마사회 수입 및 지출계획서 #12  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2024-12-19 17:06:39 &lt;/Documen
+[6348ecdf3dc5e21e] 2024년도_[요약] 24년 데이터기반행정 활성화 추진계획_240504 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-05-04 09:27:45 &lt;/Document-M
+[7397f4cf3cd4bcb4] 2022년도_(붙임4) 2023년 경마분야 지원 R&amp;D 추진계획(최종) #14  ▸  &lt;Document-Metadata&gt;   제목: 시험시행 종합계획   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-27 11:07:39   수정일: 2023-06-17 13:39:57 &lt;/Do
+[750220b64c1d0833] 2022년도_(경마본부) 2022년 핵심과제 추진실적 #4  ▸  &lt;Document-Metadata&gt;   제목: 감사원 지적사항 조치실적   마지막 수정자: KRA   작성일: 2007-12-13 21:52:10   수정일: 2022-12-20 10:42:23 &lt;/Document-
+[790f2015dc65b6e1] 2020년도_(붙임#2) 2020년 인재개발 기본계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 인 사 노 무 처   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-02 10:20:11   수정일: 2020-02-27 16:52:55 &lt;/Do
+[811aee113d51f0a0] 2023년도_(붙임4) 2023년 경마분야 지원 R&amp;D 추진계획(최종) #14  ▸  &lt;Document-Metadata&gt;   제목: 시험시행 종합계획   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-27 11:07:39   수정일: 2023-06-17 13:39:57 &lt;/Do
+[c13ca063e2675d57] 2022년도_1. 경마안정성 강화 대책 수립 계획(안) #5  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-18 19:10:02   수정일: 2023-02-04 17:46:47 &lt;/Documen
+[d91964b859494daf] 2021년도_(붙임3)_2021년도 수입 및 지출 계획서 #14  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2020-12-18 18:13:07 &lt;/Documen</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>1c2e14b3e46641c4
 33ad8cb9e391ffb3
@@ -3586,37 +4050,62 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>h003</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>공공기관 탄소 배출 줄이기 전략</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>온실가스 감축을 paraphrase</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[0346542e0be2b2ab] 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Documen
+[0370e8a4dce03ce3] 2020년도_경마실황 무선중계시스템 도입 계획(안) #9  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-20 12:54:03   수정일: 2020-08-08 11:33:53 &lt;/Document-Metadata&gt;
+[08712ddb117bedbb] 2023년도_2023 온라인 방송 추진 계획(안)_최종 #12  ▸  &lt;Document-Metadata&gt;   제목: 미래비전의 초석   작성자: KRA   마지막 수정자: KRA   작성일: 2022-05-28 14:52:15   수정일: 2023-07-23 09:58:23 &lt;/Doc
+[123f03df3479517e] 2022년도_[별첨1] KRA-ESG경영 진단모델(세부 진단기준)_최종 #43  ▸  &lt;Document-Metadata&gt;   제목: 《 KRA   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-04 14:33:57   수정일: 2023-05-27 10:21:04 &lt;/Docume
+[133dd2fda4f7c41d] 2024년도_(붙임 1) 제1회 국산마 품평회 개최계획 #18  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-15 17:31:04   수정일: 2024-06-19 17:49:01 &lt;/Documen
+[156fec294ba67ae4] 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-M
+[17a6323f30b615ff] 2024년도_(요약) 보고서(2024년 부경본부 후반기 입장인원 증대계획) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2024-07-24 17:56:30 &lt;/Document-Metadat
+[1e7df0e389317f02] 2024년도_2024년 봄 야간경마 시즌 드라이브 스루 베팅존 운영계획(안) 240225 결재 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:54:36   수정일: 2024-02-25 16:31:26 &lt;/Document-M
+[24fa325d76c7cd8a] 2024년도_2024년 서울경마공원 발매사업 운영계획(안)_최종 #0  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2024-03-22 09:44:13 &lt;/Docume
+[2965f2e46bcfa371] 2024년도_(붙임1) 제주 경마방송 노후 동기 신호 발생기 교체 계획(안)_V2 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-18 09:43:45   수정일: 2024-05-12 16:07:00 &lt;/Document-M
+[2e907c84c2a15612] 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-M
+[30e5c01f74f2a2b2] 2024년도_2024년 발매사업 운영계획(안)_ver3.0 #16  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2024-03-03 16:48:21 &lt;/Docume
+[329af5c7de78350a] 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Documen
+[3899cc22b412106f] 2022년도_(친환경탄소중립) 2022 보고서 작성_환경_5차 워크숍_컨설팅_최종 #40  ▸  &lt;Document-Metadata&gt;   제목: 1. 전략기획 및 사회적책임   마지막 수정자: KRA   작성일: 2015-01-15 14:27:57   수정일: 2023-02-19 14:55:17 &lt;/Documen
+[38bd220368aba4ab] 2023년도_[붙임 1] (요약) 말산업 R&amp;D 중장기 로드맵 구축 연구 #10  ▸  &lt;Document-Metadata&gt;   제목: 사업개요   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-19 15:06:14   수정일: 2024-03-03 16:48:29 &lt;/Documen
+[3d8c8292183997c8] 2023년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
+[3e1e3c7c7c6dbc28] 2024년도_[붙임2] 개정 「내부통제규정」전문 #10  ▸  &lt;Document-Metadata&gt;   제목: 제1장  총칙                                      작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-28 17:38:1
+[3f4afc51b550193f] 2023년도_2. [본문] 2023년 영향평가 시행 계획(안) #15  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2023-05-18 09:24:05 &lt;/Document-Met
+[3fb6428d743036ee] 2022년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
+[419a0013fb52efe2] 2024년도_(요약)'24년 안전보건경영시스템 경영자 검토보고 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-28 16:47:06   수정일: 2024-12-27 09:58:43 &lt;/Document-Metadata&gt;
+... +67 more</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>0346542e0be2b2ab
 0370e8a4dce03ce3
@@ -3708,37 +4197,64 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>h004</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>인권경영 지침이 예산 편성에 어떻게 반영되나</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>cross_document</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>인권경영(RULE) + 예산집행지침(DECISION) 교차</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>133</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[030292b5e5db1492] 2023년도_(요약본) 2023년 기록관리 기본계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-03-30 09:55:50 &lt;/Document-M
+[06b38c6a346a2385] 2023년도_2023년 바로마켓 운영 계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2011-01-14 09:36:36   수정일: 2023-02-05 17:18:03 &lt;/Document-M
+[06ea8eb0c6498c61] 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-M
+[0f9e1947b0221b27] 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-M
+[1002c0855b631621] 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document
+[10f09627fe81dec0] 2024년도_2024 마권 용지 및 구매표 구매 계획 요약 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-22 11:16:41 &lt;/Document-M
+[1288cb8b3a80b7a4] 2025년도_[요약] 2025년 학교체육 승마 지원사업 운영계획(안) 241201 #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-12-01 14:34:19 &lt;/Document-M
+[19fa870b8e483f1c] 2024년도_512.기부금관리규정(전문) #31  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-03-14 14:40:25   수정일: 2024-12-05 18:
+[1a1522e81a560fbf] 2020년도_(본문)20년 말산업 컨설팅 추진계획(안) #32  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2015-02-08 08:46:52   수정일: 2020-03-25 11:26:26 &lt;/Document-Metadata&gt;
+[1c82399b98aebbba] 2024년도_(양식) 상반기 자본예산 집행실적 #21  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-05 10:21:26   수정일: 2024-06-13 06:23:29 &lt;/Document-Metadata&gt;
+[1d6b0fc02595dbd7] 2020년도_(요약) 2020 한국경마 대국민 인식조사 결과보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-01-28 13:35:00 &lt;/Document-M
+[2170040846621df2] 2020년도_붙임 2.  2020 박람회추진계획(안)(요약) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-27 10:42:10 &lt;/Document-M
+[21a9f52b725a25b7] 2021년도_20210327 2021년 바로마켓 운영 계획(안) 요약보고 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-03-27 17:30:56 &lt;/Document-M
+[23f259fe9f9c25d9] 2020년도_200828_언택트발매추진단 하반기 사업계획 및 예산 #4  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-21 12:13:34   수정일: 2020-08-28 13:15:23 &lt;/Document-M
+[2520e4f72ad580ae] 2022년도_(제23-11호) 인권경영 실행지침 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-04 09:10:19   수정일: 2023-04-23 10:51:13 &lt;/Do
+[257c21115efd0262] 2022년도_2022년도 기관경영평가 재무예산관리 지표 경영실적보고서(수정, 02.18) #96  ▸  &lt;Document-Metadata&gt;   제목: 1. 전략기획 및 사회적책임   마지막 수정자: KRA   작성일: 2015-01-15 14:27:57   수정일: 2023-02-18 17:30:08 &lt;/Documen
+[26804b9bb678ce82] 2020년도_('20.08.06) 공공기관 자회사 운영실태 평가 계획(비대면) #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-08-09 15:07:56 &lt;/Document-M
+[2a3a0e1ad3162f25] 2024년도_(붙임2) '24년 마권용지 및 구매표 구매계획(안)_최종 #24  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2011-03-04 12:47:46   수정일: 2024-02-22 11:20:58 &lt;/Document-M
+[2e907c84c2a15612] 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-M
+[2ffc5467d8f17d86] 2020년도_(본문) 2020년 한국마사회 지식경영 운영계획(안)(200417) #19  ▸  &lt;Document-Metadata&gt;   제목: 2017년 지식경영 운영계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-13 15:38:51   수정일: 2020-04-17 10:22:3
+... +113 more</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>030292b5e5db1492
 06b38c6a346a2385
@@ -3876,37 +4392,52 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>h005</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>경주마 교배 실적과 생산 현황의 관계</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>cross_document</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>교배실적 + 생산실적 두 문서 교차</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>[08dbb848822964aa] 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:
+[2b77cb92e3b2e52e] 2020년도_붙임3. 2020년 총 교배횟수(모든교배내역) #144  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:38:42 &lt;/Document-Metadata&gt;
+[43b8261fe9a4b3ca] 2020년도_@ (결재상신) 2020년 경주마 생산 및 교배지원 결과보고 @ #19  ▸  &lt;Document-Metadata&gt;   제목: 2002. 내륙 민간목장 생산 및 교배지원 결과   작성자: 한국마사회 원당목장팀 대리 임진호   키워드: 
+    설명: 
+    마지막 수정자: KRA
+[481cdea45e2aa69d] 2020년도_붙임1. 2020년 경주마 생산실적 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:32:35 &lt;/Document-Metadata&gt;
+[57ae80a2b693d18f] 2020년도_붙임4. 2020년 유상교배 수익내역 #6  ▸  &lt;Document-Metadata&gt;   작성자: user   마지막 수정자: KRA   작성일: 2013-10-13 05:56:53   수정일: 2020-12-11 01:28:30 &lt;/Document-Metadata
+[6cdb3f17c1eafe48] 2020년도_붙임2. 2020년 총 교배실적(두수) #111  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:36:12 &lt;/Document-Metadata&gt;
+[72b1245e55ab96fc] 2021년도_경주마 교배 및 번식분야 복지 가이드라인(안) #17  ▸  &lt;Document-Metadata&gt;   제목: 한국마사회 교배 및 번식 말 복지 가이드라인 초안    작성자: User2007   마지막 수정자: KRA   작성일: 2021-08-07 21:34:58   수정일:
+[bbe40d855e6cc165] 2021년도_경주마 교배 및 번식분야 복지 가이드라인 수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-02 15:44:31 &lt;/Document-M
+[e39b4656a5219700] 2020년도_@ (요약) 2020년 경주마 생산 및 교배지원 결과보고 @ #3  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-12-17 11:13:23 &lt;/Document-Metadat</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>08dbb848822964aa
 2b77cb92e3b2e52e
@@ -3920,37 +4451,54 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>h006</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>스마트 사무환경 구축에 필요한 정보화기기 목록</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>cross_document</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>망분리 개선 + 정보화기기 교체 교차</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>[0f9e1947b0221b27] 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-M
+[19fe4e04b9ae46af] 2023년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Met
+[3d8c8292183997c8] 2023년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
+[3fb6428d743036ee] 2022년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
+[53036042c659a508] 2024년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-M
+[5b4cfb9e5eb0817f] 2024년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Met
+[7d016a8eb300196a] 2024년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;
+[8c8f02475898d6e9] 2024년도_(요약)스마트 사무환경 고도화 추진 계획 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-21 11:12:09 &lt;/Document-M
+[993ad9a5e29994fc] 2023년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen
+[9d226cce773a4434] 2022년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen
+[a869fa35476990c2] 2023년도_서울경마공원 콜센터 설비 이중화 및 망분리 계획(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-09 11:14:17   수정일: 2024-04-06 17:02:38 &lt;/Document-Metadata&gt;
+[afd0f60cc9c978c0] 2022년도_붙임 1. 스마트 사무환경 구축 및 망분리 개선 견적서(총괄) #27  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-02 04:07:54   수정일: 2023-08-17 03:33:36 &lt;/Document-Metadata&gt;
+[e4f72caaf5619284] 2023년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>0f9e1947b0221b27
 19fe4e04b9ae46af
@@ -3968,37 +4516,64 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>h007</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>2022년과 2023년 경주마 레이팅 변화</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>temporal</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>L4</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>연도별 비교 — 두 연도 문서 모두 찾아야</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>[012dcbe84f52c595] 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Me
+[05dbe5ea6c8d03fe] 2024년도_(붙임3) 2024년 제주방송 프로그램 연간 제작계획 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-02-02 04:18:57   수정일: 2024-01-26 05:46:09 &lt;/Document-Metadata&gt;
+[0787b40b4734cb4b] 2023년도_[붙임2] (본문) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #9  ▸  &lt;Document-Metadata&gt;   제목: 2019   작성자: KRA   마지막 수정자: KRA   작성일: 2019-07-24 15:06:06   수정일: 2024-05-25 09:18:53 &lt;/Documen
+[110f8ff7eb5dbdc1] 2022년도_첨부1_2022년 한국 대상경주 레이스 레이팅 총괄(연말최종) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-12-28 05:32:05   수정일: 2022-12-16 01:40:34 &lt;/Document-Metadata&gt;
+[134ceaf0ae1ba751] 2023년도_(요약) 23년 국제경주(코리아컵 코리아스프린트) 시행계획 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-04-28 10:50:47 &lt;/Document-M
+[22bf2d7e00a0f6d9] 2024년도_2024년 시리즈 경주 시행 결과보고 #25  ▸  &lt;Document-Metadata&gt;   제목: 대상경주 시리즈 선발체계 홍보   작성자: KRA   마지막 수정자: KRA   작성일: 2024-12-12 09:56:21   수정일: 2024-12-13 18:21:
+[2df376eb9253a430] 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Me
+[33640ab36a7a2b8c] 2024년도_2024년 제 2차 KPC 개최 심의 안건 #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-18 12:53:46 &lt;/Document-Metadata&gt;
+[517703ddbb49e0f6] 2024년도_붙임  (요약)야간경마 행사 추진계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-11 16:38:58 &lt;/Document-M
+[5d259d9a09f37c29] 2024년도_[붙임2] (본문) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #9  ▸  &lt;Document-Metadata&gt;   제목: 2019   작성자: KRA   마지막 수정자: KRA   작성일: 2019-07-24 15:06:06   수정일: 2024-05-25 09:18:53 &lt;/Documen
+[606afb85836eff9c] 2024년도_붙임2) (경주분류위원회)부의안건 #17  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-28 09:41:41 &lt;/Document-Metadata&gt;
+[6f3bfd6f2d2b9b04] 2022년도_(211230)2022_제주경마계획_책자원고(최종수정) #141  ▸  &lt;Document-Metadata&gt;   제목: Ⅱ. 경마 시행 개요   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2005-01-06 17:05:55   수정일: 2021-12-
+[788bbf4ba82b5320] 2022년도_첨부2_2022년 대상경주별 레이스 레이팅 세부 현황(연말 최종) #37  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-14 00:44:46   수정일: 2022-12-16 01:40:17 &lt;/Document-Me
+[83680adc07f09d42] 2022년도_연말연시 대고객 무료입장 행사 시행 결과보고 #7  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-26 11:21:25   수정일: 2022-12-23 09:30:05 &lt;/Document-M
+[929899bce4b8ff3e] 2023년도_첨부2_2023년 대상경주별 레이스 레이팅 세부 현황(연말 최종) #37  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-22 01:15:23   수정일: 2023-12-28 05:16:45 &lt;/Document-Me
+[9e0b5f9c2ae462c6] 2023년도_1등급 경주마 레이팅 현실화_최종 #15  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: user   마지막 수정자: KRA   작성일: 2018-04-17 13:51:47   수정일: 2023-11-26 14:39:29 &lt;/Document-
+[b0fc75f5da7a1c86] 2024년도_(붙임1) 2024년 제주경마방송 운영 계획(안)_요약 (최종) #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-07 09:19:14 &lt;/Document-M
+[b693b284424819ba] 2023년도_붙임_2023년 대상경주 레이스 레이팅 부여결과 보고 #11  ▸  &lt;Document-Metadata&gt;   제목: 2016년 주요 대상경주 Race Rating 부여결과 보고   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-06 09:42:57   수정일:
+[b990e68b5d5d78da] 2023년도_[붙임1] (요약) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2023-11-03 09:16:57   수정일: 2024-05-24 19:48:59 &lt;/Document-M
+[be51e42247813522] 2022년도_시리즈 경주 시행 결과보고 #25  ▸  &lt;Document-Metadata&gt;   제목: 2021년 시리즈 경주 시행 결과보고   작성자: KRA   마지막 수정자: KRA   작성일: 2021-12-15 13:12:50   수정일: 2022-12-17 11
+... +8 more</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>012dcbe84f52c595
 05dbe5ea6c8d03fe
@@ -4031,37 +4606,45 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>h008</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>가장 최근 연도의 재물조사 결과</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>temporal</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>L4</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>최신 버전 찾기</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[59854a9e60c7d3ab] 2022년도_(붙임2)재물조사결과내역(전체) #106  ▸  &lt;Document-Metadata&gt;   작성자: KA B &lt;/Document-Metadata&gt;  [Sheet: 전체] [Table Chunk 107/107] | 자산번호 | SAP자산번호 | 자산구분 | 세분류 |
+[6a278de5a7f63982] 2022년도_(붙임1)2022년 정기 재물조사 실시 결과보고 #9  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-23 10:36:27   수정일: 2023-01-19 14:22:42 &lt;/Documen
+[95765c577ef9e336] 2024년도_(붙임1) 2024년 재물조사 시행 결과보고_241227 #15  ▸  &lt;Document-Metadata&gt;   제목: 재물조정   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-12 16:02:40   수정일: 2024-12-27 09:49:24 &lt;/Documen
+[c8ed7811592eac64] 2022년도_(붙임2)재물조사결과내역(전체) #393  ▸  &lt;Document-Metadata&gt;   작성일: 2025-12-05 08:14:00   수정일: 2025-12-05 08:14:00 &lt;/Document-Metadata&gt;  [Page Number: 394]  &lt;tab</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>59854a9e60c7d3ab
 6a278de5a7f63982
@@ -4070,74 +4653,90 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>h009</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>예산전용 세부내역</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>specific_clause</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>붙임 문서의 구체적 내용</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[8390d154aeb39727] 2022년도_붙임 3. 예산전용 세부내역 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-13 05:10:41   수정일: 2023-08-18 04:08:23 &lt;/Document-Metadata&gt;
+[e9e64a316174aed5] 2022년도_[붙임]출전준비소 바닥면 탄성포장 추진안 #1  ▸  &lt;Document-Metadata&gt;   제목: 조명탑 및 감시카메라    작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-26 15:45:00   수정일: 2022-10-15 15:21:52 &lt;</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>8390d154aeb39727
 e9e64a316174aed5</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>h010</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>사업별 조직별 예산 구조 상세</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>specific_clause</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>붙임 별첨 문서 정밀 검색</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[17bd81589a0131cf] 2024년도_[붙임2] (제24-63호) 직제규정시행세칙 일부 개정(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-15 13:06:07   수정일: 2024-12-13 17:50:27 &lt;/Document-M
+[27dcbb61e82d6f82] 2024년도_과제 및 사업별 담당부서 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-08 02:27:01   수정일: 2024-06-13 05:02:20 &lt;/Document-Metadata&gt;
+[4fbf4a8a7bd53b63] 2023년도_(붙임) D-공원레저 및 지역상생(230222) #50  ▸  &lt;Document-Metadata&gt;   제목: 3   작성자: KRA   마지막 수정자: KRA   작성일: 2021-11-28 15:41:36   수정일: 2023-02-22 14:37:47 &lt;/Document-M
+[a4ed66c59a820e40] 2020년도_(붙임#14) 사업별 조직별 예산 계층구조 #78  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-11 08:44:57   수정일: 2020-03-13 01:24:08 &lt;/Document-Metadata&gt;
+[aa6aff98e2caa723] 2023년도_[붙임2] 2024년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-14 07:46:48   수정일: 2024-01-31 07:29:46 &lt;/Document-Metadata&gt;
+[da8efb3618249a33] 2022년도_[붙임2] 2023년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-15 02:28:16   수정일: 2023-02-16 04:38:18 &lt;/Document-Metadata&gt;</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>17bd81589a0131cf
 27dcbb61e82d6f82
@@ -4148,37 +4747,60 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>h011</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>마주 경제적기준에 2020년 이전 데이터가 포함되어 있는가</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>absence</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>특정 연도 범위 존재 여부 확인</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[012dcbe84f52c595] 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Me
+[0cc573d6922d1cfd] 2024년도_★ 2024년 공정관리 업무추진 계획(안) #5  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-03 15:15:28 &lt;/Document-M
+[157016074626f25d] 2021년도_(별첨1) 연도별 마주 경제적기준(2007_2021) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-20 01:23:19   수정일: 2021-11-26 04:01:22 &lt;/Document-Metadata&gt;
+[1ff851c7c3ee9eb5] 2021년도_(2021) 제 99주년 경마의 날 기념식 시행계획(안)_요약보고 #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2021-05-08 14:10:03 &lt;/Document-Metadat
+[2df376eb9253a430] 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Me
+[5cf871e3bcad9e3b] 2025년도_(붙임3) 2025년 한국마사회 수입 및 지출계획서 #12  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2024-12-19 17:06:39 &lt;/Documen
+[6e8edf545decf5bf] 2021년도_(붙임1) 2021년 더러브렛 마주 운영 개선(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 2021년 마주제도 개선 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-11 15:25:28   수정일: 2021-11-28 09:56:
+[7744ef805224b82a] 2022년도_(제23-14호) 더러브렛등록규정 시행세칙 일부 개정(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2020-05-24 10:48:12   수정일: 2023-04-21 16:37:04 &lt;/Do
+[864c7ea3086114e0] 2021년도_(제21-31호) 경마비위 신고포상금 지급규정 개정_결재(최종)★ #1  ▸  &lt;Document-Metadata&gt;   제목: 임원 징계 규정 제정   작성자: sinyoungpark   마지막 수정자: KRA   작성일: 2020-07-14 15:57:47   수정일: 2021-07-23 17
+[bd4e6e178c18810b] 2022년도_경마시행규정 시행세칙 등 개정(안) #37  ▸  &lt;Document-Metadata&gt;   제목: kjhll   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-20 14:28:49   수정일: 2023-02-25 17:
+[c142c30f937d4868] 2020년도_[붙임1] (요약) 2020년 K-Nicks를 활용한 국내산마 미국 수출 지원계획(안) #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-04-13 11:03:16   수정일: 2020-06-04 16:21:38 &lt;/Document-Metadata&gt;
+[c1ebd6c13900514d] 2021년도_(붙임2) 경주퇴역마 복지 가이드라인(최종안) #3  ▸  &lt;Document-Metadata&gt;   제목: 경주퇴역마 가이드라인 제정 관련   작성자: KRA   마지막 수정자: KRA   작성일: 2021-08-13 09:51:05   수정일: 2021-12-04 10:33
+[d91964b859494daf] 2021년도_(붙임3)_2021년도 수입 및 지출 계획서 #14  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2020-12-18 18:13:07 &lt;/Documen
+[da80398d5e7b1d5b] 2021년도_2020 한국경마 대국민 인식조사 설문지 #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-02-26 15:05:29   수정일: 2021-02-26 15:06:19 &lt;/Document-Metadata&gt;
+[de08827cf2920b82] 2024년도_(요약) 2024년 서울경마공원 경주마 재활지원 프로그램 운영계획 #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-23 17:05:09 &lt;/Document-M
+[f960b0c32b20eee5] 2024년도_(요약) 2024년 서울경마공원 경주마 재활지원 프로그램 운영계획 #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-23 17:05:09 &lt;/Document-M
+[fe8f39c7158239fe] 2023년도_2023 가을승마주간 시행 기본계획(안) #20  ▸  &lt;Document-Metadata&gt;   제목: 서울 경마공원에서    작성자: KRA   마지막 수정자: KRA   작성일: 2023-10-06 08:45:07   수정일: 2023-10-14 18:38:53 &lt;/D</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>012dcbe84f52c595
 0cc573d6922d1cfd
@@ -4200,37 +4822,53 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>h012</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>이용자보호와 관련된 모든 문서 목록</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>exhaustive</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>관련 문서 전수 열거</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>[23f259fe9f9c25d9] 2020년도_200828_언택트발매추진단 하반기 사업계획 및 예산 #4  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-21 12:13:34   수정일: 2020-08-28 13:15:23 &lt;/Document-M
+[24413d0baba3f505] 2020년도_(붙임)'20 이용자보호 현업과제 운영계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제도 확산   작성자: KRA   마지막 수정자: KRA   작성일: 2020-06-12 15:43:26   수정일: 2020-07-25 17:48:38 &lt;/Docume
+[3b6b26357ad2ce21] 2020년도_(요약) 2020년 이용자보호 추진계획 보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-21 13:18:29 &lt;/Document-M
+[594cc15f51062da3] 2023년도_[붙임] 2023년 ESG경영 추진계획(안)_최종 #37  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-05-27 10:36:47 &lt;/Document-Metadata&gt;
+[5d0dd8502b5a0cb8] 2020년도_(본문) 20년 이용자보호 액션플랜 수립계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 제목    작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-16 09:57:57   수정일: 2020-02-09 15:46:56 &lt;/Document
+[853bed249201f55c] 2020년도_[붙임1](요약)온라인 고도화 및 미래대응체계구축 기본계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-15 09:26:37   수정일: 2020-03-28 14:50:47 &lt;/Documen
+[93494a02861846af] 2023년도_붙임_2023년 사감위 건전화평가 관리계획(안)_230617_결재 #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-08 17:12:29   수정일: 2023-06-17 15:12:03 &lt;/Document-Metadata&gt;
+[957fa34075bbf580] 2021년도_(요약) `21년경마 건전화 추진 계획(안) #4  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2021-07-23 14:
+[9c30b7128e4e1947] 2020년도_(별첨) 참고_과제별중장기실행계획('19년) #0  ▸  &lt;Document-Metadata&gt;   제목: □ 과제개요   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-09 14:11:10   수정일: 2020-02-09 14:46:38 &lt;/Docum
+[c1967d59910a20e6] 2021년도_(본문) `21년 경마 건전화 추진 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2015-11-06 10:21:54   수정일: 2021-07-23 14:20:18 &lt;/Document-Metadata&gt;
+[cc2b1d26273fcdab] 2024년도_붙임_2024년 사행산업사업자 건전화평가 관리계획(안)_240518_결재 #24  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-08 17:12:29   수정일: 2024-05-18 17:43:16 &lt;/Document-Metadata&gt;
+[d4d20ca93dfcd728] 2020년도_(본문) 2020년 이용자보호 추진계획 #15  ▸  &lt;Document-Metadata&gt;   제목: 회의자료    작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-19 16:10:55   수정일: 2020-03-21 10:39:32 &lt;/Docume</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>23f259fe9f9c25d9
 24413d0baba3f505
@@ -4247,37 +4885,66 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>h013</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>경마장에서 일하다가 인권 침해를 당하면 어디에 신고해야 하나요?</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>conversational</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>L7</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>자연어 대화체, 인권침해 구제절차 매뉴얼 찾아야</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>[03e46e426c5e0a40] 2022년도_(붙임1) 인사규정시행세칙 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:10:39 &lt;/Document-Metadata&gt;
+[0fdd2b845b06532f] 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-M
+[1002c0855b631621] 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document
+[2520e4f72ad580ae] 2022년도_(제23-11호) 인권경영 실행지침 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-04 09:10:19   수정일: 2023-04-23 10:51:13 &lt;/Do
+[27e3f288a3dda838] 2024년도_지사, 문화센터 홈페이지 개편 계획(안)_240526(수정) #11  ▸  &lt;Document-Metadata&gt;   제목: □ 통합신고센터 운영개선을 통해 불법경마 신고접수 전문인력 양성   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-24 13:51:43   수정일
+[320953785300baf0] 2023년도_(붙임4) 위촉직관리지침 일부 개정(안) #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:09 &lt;/Document-Metadata&gt;
+[329af5c7de78350a] 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Documen
+[3a729c75753c7cf2] 2024년도_붙임1. 인권경영위원회 회의자료 #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-10-13 14:35:36   수정일: 2024-11-27 13:38:05 &lt;/Document-Metadata&gt;
+[3b38d7e7d3da74e2] 2024년도_(요약) 2024년 인권경영 기본계획(안)  ▸  2024년도_(요약) 2024년 인권경영 기본계획(안)
+[455c41ea7d950aff] 2020년도_불법경마사이트 신고 활성화를 위한 고객신고 제도 분석 및 운영 개선(안) #9  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-04 16:43:55   수정일: 2020-01-19 13:58:22 &lt;/Document-M
+[475035a5d7c43233] 2023년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;
+[499f2103edc5d6e1] 2021년도_(본문) 2021년 인권경영 기본계획 #30  ▸  &lt;Document-Metadata&gt;   제목: 2021년도 인권경영 추진계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-05-14 10:44:55   수정일: 2021-05-29 15:39:
+[4cab49368cf80ad5] 2023년도_(결재) 2023년 인권경영 기본계획(최종) #1  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2023-04-13 17:11:11 &lt;/Documen
+[4e67027b23247ea7] 2022년도_[붙임] 「불법경마 신고포상금 지급 등에 관한 규정」 일부 개정안 #0  ▸  &lt;Document-Metadata&gt;   제목: 경주정보 불법 송출   작성자: KRA   마지막 수정자: KRA   작성일: 2022-07-09 19:23:20   수정일: 2022-12-04 15:24:16 &lt;/D
+[55ab962e1bccc09b] 2022년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;
+[6c8917aa77bbade5] 2021년도_(요약) 2021년 인권경영 기본계획 #8  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2021-05-29 15:
+[7137b1d9495ea540] 2024년도_붙임1. 인권경영실행지침 일부 개정(안)_수정(241012) #15  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2023-11-01 14:09:00   수정일: 2024-10-12 16:56:29 &lt;/Document-M
+[722ac78a66cc46c2] 2024년도_[붙임1] 601. 취업규칙 전문(20241214)-제36차 개정 #34  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-03-14 16:07:44   수정일: 2024-12-15 09:
+[725ae7e3f94266ed] 2024년도_붙임1. ‘24년 제1차 인권경영위원회 개최계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: 개최개요   작성자: KRA   마지막 수정자: KRA   작성일: 2023-12-06 16:00:46   수정일: 2024-08-10 14:26:38 &lt;/Documen
+[7610ecb82f1d71e2] 2024년도_(전문)성희롱·성폭력_ 직장내 괴롭힘 및 스토킹 예방지침(241228)최종 #22  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-03-14 16:07:44   수정일: 2024-12-28 09:
+... +30 more</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>03e46e426c5e0a40
 0fdd2b845b06532f
@@ -4332,37 +4999,54 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>h014</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>올해 승마 체험 행사를 기획하려는데 작년에 어떻게 했는지 참고할 자료 있나요?</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>conversational</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>L7</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>도심승마체험 시행계획을 자연어로</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>[1dd7a41b6d49067a] 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-M
+[230b3c89a0f6cfdc] 2023년도_붙임 1. 2023년 학교체육 승마 시범사업 운영계획(안) #35  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-11-04 14:57:12   수정일: 2022-12-02 16:28:09 &lt;/Document-Metadata&gt;
+[2cbdb440161c0502] 2024년도_2024년 제주경마공원 승마체험장 및 관상마체험장 운영계획 #17  ▸  &lt;Document-Metadata&gt;   제목: 2014   마지막 수정자: KRA   작성일: 2014-02-07 09:49:57   수정일: 2024-02-28 11:03:22 &lt;/Document-Metadata&gt;
+[345beb807d95ba70] 2020년도_★(결재) 2020 사회공익힐링 승마 사업 기본 운영 계획 #5  ▸  &lt;Document-Metadata&gt;   제목: 2019 전국민 승마체험 사업 기본계획   작성자: user   마지막 수정자: KRA   작성일: 2019-02-15 13:56:48   수정일: 2020-02-26
+[3811d5c616420fc2] 2024년도_240307 2024 유소년 승마지원 기본계획(요약)(최최종) #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-17 13:38:28   수정일: 2024-03-08 14:41:05 &lt;/Document-M
+[49833f0ed56ba434] 2023년도_제18회 제주마 축제 공고문 및 제안서 #37  ▸  &lt;Document-Metadata&gt;   제목: g   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-01 15:17:22   수정일: 2023-08-20 16:04:43 &lt;/Document-M
+[5619e37e7ee1470d] 2024년도_(양식) 말산업육성지원사업 추진실적 #2  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-28 14:58:32   수정일: 2024-06-13 14:38:26 &lt;/Document-Metadata&gt;
+[68c173524cf22c47] 2020년도_붙임_1_2020년 도심승마체험 시행계획(요약, 최종) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-03-07 18:01:46 &lt;/Document-Metadat
+[7b5af8d8a80073c5] 2023년도_[요약] 2023년 힐링승마 지원사업 추진 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-03-09 14:06:41 &lt;/Document-M
+[affde3091ecbe443] 2024년도_제주마축제 홍보 계획_최종 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-31 19:39:40 &lt;/Document-M
+[c3b5928050f2e9aa] 2024년도_(붙임1) 2024년 도심공원 승마체험 운영계획 변경(안) #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-07 14:26:11   수정일: 2024-06-07 17:52:12 &lt;/Document-M
+[c4f8c5320a9a943c] 2023년도_제18회 제주마 축제 시행계획(안) #26  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2023-08-20 16:19:01 &lt;/Docume
+[edf8fe17a083f95c] 2024년도_[붙임#1] (요약본) 2024년 힐링승마 지원사업 추진 계획(안)_ver2 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-02-22 19:09:53 &lt;/Document-M</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>1dd7a41b6d49067a
 230b3c89a0f6cfdc
@@ -4380,37 +5064,62 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>h015</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>우리 회사 윤리경영 점수가 어떻게 되는지 보고서 좀 찾아줘</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>conversational</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>L7</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>윤리경영 기본계획을 비공식 표현으로</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>[03e46e426c5e0a40] 2022년도_(붙임1) 인사규정시행세칙 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:10:39 &lt;/Document-Metadata&gt;
+[06ea8eb0c6498c61] 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-M
+[0cc6e308b2160025] 2024년도_(요약) 2024년 선수단(유도탁구) 운영 계획_240427 #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-19 14:09:35   수정일: 2024-04-27 10:24:26 &lt;/Document-Metadata&gt;
+[0fdd2b845b06532f] 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-M
+[1ab7e770624479a7] 2024년도_(입찰공고문) 스마트 조교정보시스템 구축 #9  ▸  &lt;Document-Metadata&gt;   제목: 입찰공고문   마지막 수정자: KRA   작성일: 2007-05-20 11:05:36   수정일: 2024-05-10 17:36:20 &lt;/Document-Metadata
+[210e0e2db641965a] 2020년도_[붙임 1] 2020년 재활승마 활성화 지원 시범사업 계획(안_요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 말산업육성본부   작성자: KRA   마지막 수정자: KRA   작성일: 2017-05-24 17:59:41   수정일: 2020-08-07 15:31:04 &lt;/Docu
+[27325f8e49d559f4] 2020년도_(본문) 2020년도 내부경영평가제도 개선(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-22 09:53:12 &lt;/Documen
+[2a67e1073fe83029] 2022년도_2022 힐링승마 지원사업 운영 결과보고_221222 #25  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-08-06 09:18:55   수정일: 2022-12-22 18:09:26 &lt;/Document-Metadata&gt;
+[2c473c597114e075] 2024년도_(요약) 2024년 윤리경영 추진계획(안) (1) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-05-30 11:08:03 &lt;/Document-M
+[2ffc5467d8f17d86] 2020년도_(본문) 2020년 한국마사회 지식경영 운영계획(안)(200417) #19  ▸  &lt;Document-Metadata&gt;   제목: 2017년 지식경영 운영계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-13 15:38:51   수정일: 2020-04-17 10:22:3
+[320953785300baf0] 2023년도_(붙임4) 위촉직관리지침 일부 개정(안) #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:09 &lt;/Document-Metadata&gt;
+[363c897a38703bf5] 2023년도_[요약]한국마사회 CEO·임차인 「청·심·환 간담회」 결과보고 #2  ▸  &lt;Document-Metadata&gt;   제목: □ 편의점 물건   작성자: KRA   마지막 수정자: KRA   작성일: 2022-12-27 14:49:26   수정일: 2023-09-07 14:18:28 &lt;/Doc
+[386c3d238d9e12b0] 2021년도_(요약) 2021 사회공익 힐링승마 사업 결과보고 #4  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-23 17:48:23 &lt;/Document-M
+[40122ffcb05effea] 2020년도_★(요약) 2020 사회공익힐링 승마 사업 기본 운영 계획 #10  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-04 13:13:33   수정일: 2020-02-26 16:19:50 &lt;/Document-Metadata&gt;
+[470d301f2c963cc9] 2020년도_(요약) 2020년 한국마사회 지식경영 운영계획(안)(200417) #1  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2020-04-17 09:
+[475035a5d7c43233] 2023년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;
+[49833f0ed56ba434] 2023년도_제18회 제주마 축제 공고문 및 제안서 #37  ▸  &lt;Document-Metadata&gt;   제목: g   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-01 15:17:22   수정일: 2023-08-20 16:04:43 &lt;/Document-M
+[499f2103edc5d6e1] 2021년도_(본문) 2021년 인권경영 기본계획 #30  ▸  &lt;Document-Metadata&gt;   제목: 2021년도 인권경영 추진계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-05-14 10:44:55   수정일: 2021-05-29 15:39:
+[4b93e74ded9f99c1] 2020년도_2020년 지사 맞춤형 사회적가치 실현  추진 계획(안)) #39  ▸  &lt;Document-Metadata&gt;   제목: 일자리 창출 중장기 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-09-12 12:21:29   수정일: 2020-03-15 17:49:55
+[4bd81a5d3f7d0759] 2024년도_2024년 청심환 간담회 시행 계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: □    작성자: KRA   마지막 수정자: KRA   작성일: 2023-07-13 17:49:14   수정일: 2024-07-20 15:25:58 &lt;/Document-
+... +39 more</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>03e46e426c5e0a40
 06ea8eb0c6498c61
@@ -4485,7 +5194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4495,7 +5204,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4544,86 +5254,74 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>m001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>인권경영 기본계획과 인권영향평가 결과를 종합하면 어떤 조치가 필요한가</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>인권 계획(DECISION) + 영향평가(OBSERVATION) 교차</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>7b891a6e2bfdb9a0
-d4e8e7e0de0bee24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>m002</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>경마산업 운영계획 수립에서 윤리경영 기준이 어떻게 반영되는지</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -4631,7 +5329,7 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>운영계획(DECISION) + 윤리경영(RULE) 교차</t>
+          <t>인권 계획(DECISION) + 영향평가(OBSERVATION) 교차</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -4639,20 +5337,26 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>abf6b885cc56106c
-1d7a8c5b7cde9f12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>[7b891a6e2bfdb9a0] (not found in graph)
+[d4e8e7e0de0bee24] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>7b891a6e2bfdb9a0
+d4e8e7e0de0bee24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>m003</t>
+          <t>m002</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>정보기술 시스템 구축과 관련된 예산 편성 및 집행지침</t>
+          <t>경마산업 운영계획 수립에서 윤리경영 기준이 어떻게 반영되는지</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -4660,27 +5364,34 @@
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>정보기술(ARTIFACT) + 예산 지침(DECISION) 교차</t>
+          <t>운영계획(DECISION) + 윤리경영(RULE) 교차</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>a3e51e3ccd5f7a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>[abf6b885cc56106c] (not found in graph)
+[1d7a8c5b7cde9f12] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>abf6b885cc56106c
+1d7a8c5b7cde9f12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>m004</t>
+          <t>m003</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>교배실적 현황과 경주마 국제 레이팅의 상관관계</t>
+          <t>정보기술 시스템 구축과 관련된 예산 편성 및 집행지침</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -4688,7 +5399,7 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>교배(OBSERVATION) + 레이팅(OBSERVATION) 동일 도메인 복합</t>
+          <t>정보기술(ARTIFACT) + 예산 지침(DECISION) 교차</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -4696,19 +5407,24 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>b5c2f8e7a11b3290</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>[a3e51e3ccd5f7a45] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>a3e51e3ccd5f7a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>m005</t>
+          <t>m004</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>지사 방역관리와 고객입장 정책 개선 방안</t>
+          <t>교배실적 현황과 경주마 국제 레이팅의 상관관계</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -4716,7 +5432,7 @@
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>방역(RULE) + 고객 정책(DECISION) 교차</t>
+          <t>교배(OBSERVATION) + 레이팅(OBSERVATION) 동일 도메인 복합</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -4724,19 +5440,24 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>e2b4c1d7f5a3a908</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>[b5c2f8e7a11b3290] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>b5c2f8e7a11b3290</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>m006</t>
+          <t>m005</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>재활힐링승마 사업과 도심승마체험 시행계획의 공통점</t>
+          <t>지사 방역관리와 고객입장 정책 개선 방안</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -4744,28 +5465,32 @@
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>복수 사업 계획 비교</t>
+          <t>방역(RULE) + 고객 정책(DECISION) 교차</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>f6a42e8c3b1d2f47
-9c3e7a1b5d6f8290</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>[e2b4c1d7f5a3a908] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>e2b4c1d7f5a3a908</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>m007</t>
+          <t>m006</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>인재개발 기본계획과 복지 교육 추진 현황을 연계한 방향</t>
+          <t>재활힐링승마 사업과 도심승마체험 시행계획의 공통점</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -4773,27 +5498,34 @@
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>인재(DECISION) + 복지교육(DECISION) 교차</t>
+          <t>복수 사업 계획 비교</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>c8f4e2d1a7b5c390</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>[f6a42e8c3b1d2f47] (not found in graph)
+[9c3e7a1b5d6f8290] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>f6a42e8c3b1d2f47
+9c3e7a1b5d6f8290</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>m008</t>
+          <t>m007</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>내부경영평가제도 개선 방안과 ESG 지속가능성 보고</t>
+          <t>인재개발 기본계획과 복지 교육 추진 현황을 연계한 방향</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -4801,7 +5533,7 @@
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>내부평가(OBSERVATION) + ESG(RULE) 교차</t>
+          <t>인재(DECISION) + 복지교육(DECISION) 교차</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
@@ -4809,19 +5541,24 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>a1b2c3d4e5f67890</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>[c8f4e2d1a7b5c390] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>c8f4e2d1a7b5c390</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>m009</t>
+          <t>m008</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>예산 및 기금운용계획 집행지침에서 말산업 연구사업 지원 원칙</t>
+          <t>내부경영평가제도 개선 방안과 ESG 지속가능성 보고</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -4829,7 +5566,7 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>예산지침(DECISION) + 말산업 연구(OBSERVATION) 교차</t>
+          <t>내부평가(OBSERVATION) + ESG(RULE) 교차</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
@@ -4837,19 +5574,24 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>d7e9f1a3b5c79024</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+          <t>[a1b2c3d4e5f67890] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>a1b2c3d4e5f67890</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>m010</t>
+          <t>m009</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>KPC 개최계획과 관련된 인권경영 가이드 준수 사항</t>
+          <t>예산 및 기금운용계획 집행지침에서 말산업 연구사업 지원 원칙</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -4857,13 +5599,51 @@
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>KPC 계획(DECISION) + 인권 규정(RULE) 교차</t>
+          <t>예산지침(DECISION) + 말산업 연구(OBSERVATION) 교차</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[d7e9f1a3b5c79024] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>d7e9f1a3b5c79024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>m010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>KPC 개최계획과 관련된 인권경영 가이드 준수 사항</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>KPC 계획(DECISION) + 인권 규정(RULE) 교차</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[b8c2d4e6f8a1b024] (not found in graph)</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>b8c2d4e6f8a1b024</t>
         </is>
@@ -4880,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4890,7 +5670,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4939,85 +5720,74 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>e001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>iPhone 15 Pro 512GB</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>상품명 정확 검색</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>e002</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Shin Ramyun</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -5033,19 +5803,24 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00005</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>e003</t>
+          <t>e002</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Galaxy Book</t>
+          <t>Shin Ramyun</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -5061,19 +5836,24 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00003</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>e004</t>
+          <t>e003</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Dried Beef</t>
+          <t>Galaxy Book</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -5081,7 +5861,7 @@
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>상품명 정확 검색 — 동명 상품 가능</t>
+          <t>상품명 정확 검색</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -5089,19 +5869,24 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>[pr_goods_base:G00003] pr_goods_base:G00003  ▸  pr_goods_base: Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>e005</t>
+          <t>e004</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CLA Mask</t>
+          <t>Dried Beef</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -5109,7 +5894,7 @@
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>상품명 정확 검색</t>
+          <t>상품명 정확 검색 — 동명 상품 가능</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -5117,19 +5902,24 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00002</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>e006</t>
+          <t>e005</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Volume Lip plumper maxi</t>
+          <t>CLA Mask</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -5137,7 +5927,7 @@
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>상품명 정확 검색 (화장품)</t>
+          <t>상품명 정확 검색</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
@@ -5145,19 +5935,24 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00006</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>[pr_goods_base:G00002] pr_goods_base:G00002  ▸  pr_goods_base: CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>e007</t>
+          <t>e006</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cheese Boursin Garlic Herbs</t>
+          <t>Volume Lip plumper maxi</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -5165,7 +5960,7 @@
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>상품명 부분 검색</t>
+          <t>상품명 정확 검색 (화장품)</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
@@ -5173,19 +5968,24 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G01006</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>[pr_goods_base:G00006] pr_goods_base:G00006  ▸  pr_goods_base: Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00006</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>e008</t>
+          <t>e007</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Wine Niagara Reisling</t>
+          <t>Cheese Boursin Garlic Herbs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -5193,28 +5993,32 @@
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>와인 상품 검색</t>
+          <t>상품명 부분 검색</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00010
-pr_goods_base:G00462</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>[pr_goods_base:G01006] pr_goods_base:G01006  ▸  pr_goods_base: Cheese - Boursin, Garlic / Herbs | G01006 | 2023-12-18 | Y | 9999.0 | 77000.0 | 2023-12-19 00:00:00 | 202</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G01006</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>e009</t>
+          <t>e008</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chicken Soup Base</t>
+          <t>Wine Niagara Reisling</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -5222,27 +6026,34 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>상품명 검색</t>
+          <t>와인 상품 검색</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G01004</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+          <t>[pr_goods_base:G00010] pr_goods_base:G00010  ▸  pr_goods_base: Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024
+[pr_goods_base:G00462] pr_goods_base:G00462  ▸  pr_goods_base: Wine - Niagara Peninsula Vqa | G00462 | 2023-12-18 | Y | 9999.0 | 22000.0 | 2023-12-19 00:00:00 | 2024-12</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00010
+pr_goods_base:G00462</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>e010</t>
+          <t>e009</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Pastry Banana Muffin</t>
+          <t>Chicken Soup Base</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -5250,7 +6061,7 @@
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>복합 상품명 검색</t>
+          <t>상품명 검색</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
@@ -5258,19 +6069,24 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00992</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>[pr_goods_base:G01004] pr_goods_base:G01004  ▸  pr_goods_base: Chicken - Soup Base | G01004 | 2023-12-18 | Y | 9999.0 | 52000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G01004</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>e011</t>
+          <t>e010</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Jameson Irish Whiskey</t>
+          <t>Pastry Banana Muffin</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -5278,28 +6094,32 @@
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>주류 상품 검색 — 동명 상품 2개 (dash 유무 차이)</t>
+          <t>복합 상품명 검색</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00082
-pr_goods_base:G00968</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>[pr_goods_base:G00992] pr_goods_base:G00992  ▸  pr_goods_base: Pastry - Banana Muffin - Mini | G00992 | 2023-12-18 | Y | 9999.0 | 24000.0 | 2023-12-19 00:00:00 | 2024-1</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00992</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>e012</t>
+          <t>e011</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Lamb Shoulder Boneless</t>
+          <t>Jameson Irish Whiskey</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -5307,7 +6127,7 @@
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>식재료 검색 — 유사 상품 다수</t>
+          <t>주류 상품 검색 — 동명 상품 2개 (dash 유무 차이)</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
@@ -5315,20 +6135,26 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00470
-pr_goods_base:G00736</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>[pr_goods_base:G00082] pr_goods_base:G00082  ▸  pr_goods_base: Jameson - Irish Whiskey | G00082 | 2023-12-18 | Y | 9999.0 | 58000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
+[pr_goods_base:G00968] pr_goods_base:G00968  ▸  pr_goods_base: Jameson Irish Whiskey | G00968 | 2023-12-18 | Y | 9999.0 | 15000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00082
+pr_goods_base:G00968</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>e013</t>
+          <t>e012</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>English Muffin</t>
+          <t>Lamb Shoulder Boneless</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -5336,7 +6162,7 @@
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>동명 상품 2개</t>
+          <t>식재료 검색 — 유사 상품 다수</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
@@ -5344,20 +6170,26 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00467
-pr_goods_base:G00569</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>[pr_goods_base:G00470] pr_goods_base:G00470  ▸  pr_goods_base: Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18
+[pr_goods_base:G00736] pr_goods_base:G00736  ▸  pr_goods_base: Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00470
+pr_goods_base:G00736</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>e014</t>
+          <t>e013</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Beer Alexander Kieths Pale Ale</t>
+          <t>English Muffin</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -5365,27 +6197,34 @@
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>맥주 상품 검색</t>
+          <t>동명 상품 2개</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00974</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>[pr_goods_base:G00467] pr_goods_base:G00467  ▸  pr_goods_base: English Muffin | G00467 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
+[pr_goods_base:G00569] pr_goods_base:G00569  ▸  pr_goods_base: English Muffin | G00569 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00467
+pr_goods_base:G00569</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>e015</t>
+          <t>e014</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Wiberg Super Cure</t>
+          <t>Beer Alexander Kieths Pale Ale</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -5393,7 +6232,7 @@
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>리뷰가 가장 많은 상품 (29건)</t>
+          <t>맥주 상품 검색</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
@@ -5401,19 +6240,24 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00751</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>[pr_goods_base:G00974] pr_goods_base:G00974  ▸  pr_goods_base: Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 20</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00974</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>e016</t>
+          <t>e015</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Ice Wine</t>
+          <t>Wiberg Super Cure</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -5421,28 +6265,32 @@
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>아이스 와인 — 동명 2개 상품</t>
+          <t>리뷰가 가장 많은 상품 (29건)</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00106
-pr_goods_base:G00339</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+          <t>[pr_goods_base:G00751] pr_goods_base:G00751  ▸  pr_goods_base: Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00751</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>e017</t>
+          <t>e016</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cheese Feta</t>
+          <t>Ice Wine</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -5450,7 +6298,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>치즈 종류 검색 — 2개 상품</t>
+          <t>아이스 와인 — 동명 2개 상품</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
@@ -5458,20 +6306,26 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00315
-pr_goods_base:G00694</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
+          <t>[pr_goods_base:G00106] pr_goods_base:G00106  ▸  pr_goods_base: Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00339] pr_goods_base:G00339  ▸  pr_goods_base: Wine - Ice Wine | G00339 | 2023-12-18 | Y | 9999.0 | 39000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00106
+pr_goods_base:G00339</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>e018</t>
+          <t>e017</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon wine</t>
+          <t>Cheese Feta</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -5479,27 +6333,34 @@
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>와인 품종 검색</t>
+          <t>치즈 종류 검색 — 2개 상품</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00113</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
+          <t>[pr_goods_base:G00315] pr_goods_base:G00315  ▸  pr_goods_base: Cheese - Feta | G00315 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
+[pr_goods_base:G00694] pr_goods_base:G00694  ▸  pr_goods_base: Cheese - Feta | G00694 | 2023-12-18 | Y | 9999.0 | 55000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00315
+pr_goods_base:G00694</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>e019</t>
+          <t>e018</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Bread 10 Grain</t>
+          <t>Cabernet Sauvignon wine</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -5507,29 +6368,32 @@
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>빵 상품 검색 — 동명 상품 3개</t>
+          <t>와인 품종 검색</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00563
-pr_goods_base:G00817
-pr_goods_base:G01005</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+          <t>[pr_goods_base:G00113] pr_goods_base:G00113  ▸  pr_goods_base: Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00113</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>e020</t>
+          <t>e019</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Garlic Powder</t>
+          <t>Bread 10 Grain</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -5537,13 +6401,55 @@
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
+          <t>빵 상품 검색 — 동명 상품 3개</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00563] pr_goods_base:G00563  ▸  pr_goods_base: Bread - 10 Grain | G00563 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00817] pr_goods_base:G00817  ▸  pr_goods_base: Bread - 10 Grain | G00817 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G01005] pr_goods_base:G01005  ▸  pr_goods_base: Bread - 10 Grain | G01005 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00563
+pr_goods_base:G00817
+pr_goods_base:G01005</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>e020</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Garlic Powder</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
           <t>향신료 검색 — 최저가 상품 중 하나 (1000원)</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00711] pr_goods_base:G00711  ▸  pr_goods_base: Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00711</t>
         </is>
@@ -5560,7 +6466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5570,7 +6476,8 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5619,93 +6526,74 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>qid</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>relevant_count</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>relevant_docs</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>h001</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>프리미엄 스마트폰 최신 모델</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>iPhone 15 Pro 512GB를 직접 언급하지 않고 의미로 검색</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>h002</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>한국 즉석 라면 제품</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5721,7 +6609,7 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Shin Ramyun을 한국어 설명으로 검색</t>
+          <t>iPhone 15 Pro 512GB를 직접 언급하지 않고 의미로 검색</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -5729,19 +6617,24 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00005</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>h003</t>
+          <t>h002</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>이탈리아 숙성 치즈 제품</t>
+          <t>한국 즉석 라면 제품</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -5757,13 +6650,62 @@
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
+          <t>Shin Ramyun을 한국어 설명으로 검색</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>h003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>이탈리아 숙성 치즈 제품</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
           <t>Provolone, Gorgonzola, Parmesan 등 이탈리아 치즈</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00040] pr_goods_base:G00040  ▸  pr_goods_base: Cheese - Provolone | G00040 | 2023-12-18 | Y | 9999.0 | 56000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
+[pr_goods_base:G00083] pr_goods_base:G00083  ▸  pr_goods_base: Cheese - Gorgonzola | G00083 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
+[pr_goods_base:G00442] pr_goods_base:G00442  ▸  pr_goods_base: Cheese - Parmesan Cubes | G00442 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
+[pr_goods_base:G00158] pr_goods_base:G00158  ▸  pr_goods_base: Cheese - Mozzarella | G00158 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00040
 pr_goods_base:G00083
@@ -5772,67 +6714,31 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>h004</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>portable computing device</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>L2</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Galaxy Book을 영어 패러프레이즈로 검색</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00003</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>h005</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Dried Beef 판매 이력</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>cross_table</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>L3</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>상품(pr_goods_base) → 판매이력(pr_goods_sold_hist) FK 조인</t>
+          <t>Galaxy Book을 영어 패러프레이즈로 검색</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -5840,19 +6746,24 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>[pr_goods_base:G00003] pr_goods_base:G00003  ▸  pr_goods_base: Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>h006</t>
+          <t>h005</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Cheese Pont Couvert 리뷰</t>
+          <t>Dried Beef 판매 이력</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -5868,7 +6779,7 @@
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>상품 → 피드백 FK 조인. 27건의 리뷰 존재</t>
+          <t>상품(pr_goods_base) → 판매이력(pr_goods_sold_hist) FK 조인</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
@@ -5876,19 +6787,24 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00997</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>h007</t>
+          <t>h006</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>iPhone 15 Pro 판매 기록은 몇 건인가?</t>
+          <t>Cheese Pont Couvert 리뷰</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -5904,7 +6820,7 @@
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>상품 → 판매이력 FK + 건수 확인 (65건)</t>
+          <t>상품 → 피드백 FK 조인. 27건의 리뷰 존재</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
@@ -5912,35 +6828,40 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>[pr_goods_base:G00997] pr_goods_base:G00997  ▸  pr_goods_base: Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00997</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>h008</t>
+          <t>h007</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>50만원 이상 고가 상품</t>
+          <t>iPhone 15 Pro 판매 기록은 몇 건인가?</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>cross_table</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>price &gt;= 500000 필터. iPhone만 해당 (1,600,000원)</t>
+          <t>상품 → 판매이력 FK + 건수 확인 (65건)</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
@@ -5948,19 +6869,24 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
+          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
           <t>pr_goods_base:G00007</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="80" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>h009</t>
+          <t>h008</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>1000원짜리 최저가 상품</t>
+          <t>50만원 이상 고가 상품</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -5976,13 +6902,62 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
+          <t>price &gt;= 500000 필터. iPhone만 해당 (1,600,000원)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>h009</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>1000원짜리 최저가 상품</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
           <t>price = 1000 필터. 4개 상품</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00072] pr_goods_base:G00072  ▸  pr_goods_base: Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00302] pr_goods_base:G00302  ▸  pr_goods_base: Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 202
+[pr_goods_base:G00711] pr_goods_base:G00711  ▸  pr_goods_base: Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2
+[pr_goods_base:G00892] pr_goods_base:G00892  ▸  pr_goods_base: Plate Pie Foil | G00892 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00072
 pr_goods_base:G00302
@@ -5991,37 +6966,62 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>h010</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>5000원 이하 저가 상품 목록</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>filter</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>L4</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>price &lt;= 5000 필터. 41개 상품</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00063] pr_goods_base:G00063  ▸  pr_goods_base: Chips Potato Swt Chilli Sour | G00063 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-
+[pr_goods_base:G00068] pr_goods_base:G00068  ▸  pr_goods_base: Amarula Cream | G00068 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2
+[pr_goods_base:G00072] pr_goods_base:G00072  ▸  pr_goods_base: Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00089] pr_goods_base:G00089  ▸  pr_goods_base: Quail - Jumbo | G00089 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2
+[pr_goods_base:G00098] pr_goods_base:G00098  ▸  pr_goods_base: Fudge - Chocolate Fudge | G00098 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
+[pr_goods_base:G00202] pr_goods_base:G00202  ▸  pr_goods_base: Pepper - Green Thai | G00202 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
+[pr_goods_base:G00203] pr_goods_base:G00203  ▸  pr_goods_base: Jam - Raspberry,jar | G00203 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
+[pr_goods_base:G00204] pr_goods_base:G00204  ▸  pr_goods_base: Oysters - Smoked | G00204 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00217] pr_goods_base:G00217  ▸  pr_goods_base: Soda Water - Club Soda, 355 Ml | G00217 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00258] pr_goods_base:G00258  ▸  pr_goods_base: Juice - Apple Cider | G00258 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
+[pr_goods_base:G00261] pr_goods_base:G00261  ▸  pr_goods_base: Scotch - Queen Anne | G00261 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
+[pr_goods_base:G00267] pr_goods_base:G00267  ▸  pr_goods_base: Soup - Campbells - Tomato | G00267 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18
+[pr_goods_base:G00283] pr_goods_base:G00283  ▸  pr_goods_base: Chinese Foods - Chicken Wing | G00283 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-
+[pr_goods_base:G00302] pr_goods_base:G00302  ▸  pr_goods_base: Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 202
+[pr_goods_base:G00314] pr_goods_base:G00314  ▸  pr_goods_base: Fondant - Icing | G00314 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
+[pr_goods_base:G00332] pr_goods_base:G00332  ▸  pr_goods_base: Nut - Walnut, Chopped | G00332 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:0
+[pr_goods_base:G00376] pr_goods_base:G00376  ▸  pr_goods_base: Otomegusa Dashi Konbu | G00376 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:0
+[pr_goods_base:G00388] pr_goods_base:G00388  ▸  pr_goods_base: Lettuce - Iceberg | G00388 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00438] pr_goods_base:G00438  ▸  pr_goods_base: Doilies - 8, Paper | G00438 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
+... +21 more</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00005
 pr_goods_base:G00063
@@ -6067,37 +7067,44 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>h011</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>가장 많이 팔린 상품 TOP 3</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>sold_qunt SUM GROUP BY goods_no. Dried Beef(83), Jacket(74), iPhone(69)</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
+[pr_goods_base:G00004] pr_goods_base:G00004  ▸  pr_goods_base: Jacket | 남성 의류 | G00004 | 2024-12-19 | Y | 200.0 | 18500.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
+[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00001
 pr_goods_base:G00004
@@ -6105,37 +7112,46 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>h012</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>리뷰가 가장 많은 상품 TOP 5</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>feedback COUNT GROUP BY goods_no. Wiberg(29), Bread Kimel(28), Pork Ham(28), Sauce Ranch(27), Cheese Pont(27)</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00751] pr_goods_base:G00751  ▸  pr_goods_base: Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
+[pr_goods_base:G00472] pr_goods_base:G00472  ▸  pr_goods_base: Bread - Kimel Stick Poly | G00472 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18
+[pr_goods_base:G00389] pr_goods_base:G00389  ▸  pr_goods_base: Pork Ham Prager | G00389 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00329] pr_goods_base:G00329  ▸  pr_goods_base: Sauce - Ranch Dressing | G00329 | 2023-12-18 | Y | 9999.0 | 88000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
+[pr_goods_base:G00997] pr_goods_base:G00997  ▸  pr_goods_base: Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00751
 pr_goods_base:G00472
@@ -6145,37 +7161,52 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>h013</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>맥주 종류가 총 몇 개인가?</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Beer 포함 상품 COUNT = 11개</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00270] pr_goods_base:G00270  ▸  pr_goods_base: Beer - Mill St Organic | G00270 | 2023-12-18 | Y | 9999.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
+[pr_goods_base:G00466] pr_goods_base:G00466  ▸  pr_goods_base: Beer - Sleemans Honey Brown | G00466 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-
+[pr_goods_base:G00645] pr_goods_base:G00645  ▸  pr_goods_base: Beer - Original Organic Lager | G00645 | 2023-12-18 | Y | 9999.0 | 73000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00700] pr_goods_base:G00700  ▸  pr_goods_base: Beer - Moosehead | G00700 | 2023-12-18 | Y | 9999.0 | 87000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00719] pr_goods_base:G00719  ▸  pr_goods_base: Beer - Original Organic Lager | G00719 | 2023-12-18 | Y | 9999.0 | 74000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00793] pr_goods_base:G00793  ▸  pr_goods_base: Beer - Steamwhistle | G00793 | 2023-12-18 | Y | 9999.0 | 33000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
+[pr_goods_base:G00798] pr_goods_base:G00798  ▸  pr_goods_base: Beer - Original Organic Lager | G00798 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00928] pr_goods_base:G00928  ▸  pr_goods_base: Beer - Rickards Red | G00928 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
+[pr_goods_base:G00937] pr_goods_base:G00937  ▸  pr_goods_base: Beer - Mcauslan Apricot | G00937 | 2023-12-18 | Y | 9999.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
+[pr_goods_base:G00938] pr_goods_base:G00938  ▸  pr_goods_base: Beer - Steamwhistle | G00938 | 2023-12-18 | Y | 9999.0 | 63000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
+[pr_goods_base:G00974] pr_goods_base:G00974  ▸  pr_goods_base: Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 20</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00270
 pr_goods_base:G00466
@@ -6191,51 +7222,15 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>h014</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>5점 리뷰를 가장 많이 받은 상품의 가격은?</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>multi_hop</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>feedback(score=5) 집계 → 상품 조회 → 가격 확인. Flour Masa De Harina(11건 5점, 가격 확인 필요)</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00857</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>h015</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>판매량 1위 상품의 리뷰 평점은?</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -6251,7 +7246,7 @@
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>sold_hist 집계(G00001 Dried Beef=83개) → feedback 평점 확인</t>
+          <t>feedback(score=5) 집계 → 상품 조회 → 가격 확인. Flour Masa De Harina(11건 5점, 가격 확인 필요)</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
@@ -6259,41 +7254,112 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>pr_goods_base:G00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>[pr_goods_base:G00857] pr_goods_base:G00857  ▸  pr_goods_base: Flour - Masa De Harina Mexican | G00857 | 2023-12-18 | Y | 9999.0 | 86000.0 | 2023-12-19 00:00:00 | 2024-</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00857</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>h016</t>
+          <t>h015</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>이 쇼핑몰에서 와인이 몇 종류나 있어?</t>
+          <t>판매량 1위 상품의 리뷰 평점은?</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>conversational</t>
+          <t>multi_hop</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
+          <t>sold_hist 집계(G00001 Dried Beef=83개) → feedback 평점 확인</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>h016</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>이 쇼핑몰에서 와인이 몇 종류나 있어?</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
           <t>Wine 포함 상품 COUNT. 80+ 종류</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00010] pr_goods_base:G00010  ▸  pr_goods_base: Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024
+[pr_goods_base:G00034] pr_goods_base:G00034  ▸  pr_goods_base: Wine - Piper Heidsieck Brut | G00034 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-
+[pr_goods_base:G00048] pr_goods_base:G00048  ▸  pr_goods_base: Wine - Sicilia Igt Nero Avola | G00048 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00055] pr_goods_base:G00055  ▸  pr_goods_base: Wine - Champagne Brut Veuve | G00055 | 2023-12-18 | Y | 9999.0 | 10000.0 | 2023-12-19 00:00:00 | 2024-12-
+[pr_goods_base:G00077] pr_goods_base:G00077  ▸  pr_goods_base: Wine - Magnotta, White | G00077 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
+[pr_goods_base:G00086] pr_goods_base:G00086  ▸  pr_goods_base: Wine - Winzer Krems Gruner | G00086 | 2023-12-18 | Y | 9999.0 | 75000.0 | 2023-12-19 00:00:00 | 2024-12-1
+[pr_goods_base:G00106] pr_goods_base:G00106  ▸  pr_goods_base: Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00112] pr_goods_base:G00112  ▸  pr_goods_base: Wine - Red, Cabernet Merlot | G00112 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-
+[pr_goods_base:G00113] pr_goods_base:G00113  ▸  pr_goods_base: Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18
+[pr_goods_base:G00138] pr_goods_base:G00138  ▸  pr_goods_base: Wine - Fino Tio Pepe Gonzalez | G00138 | 2023-12-18 | Y | 9999.0 | 64000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00144] pr_goods_base:G00144  ▸  pr_goods_base: Wine - Tribal Sauvignon | G00144 | 2023-12-18 | Y | 9999.0 | 38000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
+[pr_goods_base:G00148] pr_goods_base:G00148  ▸  pr_goods_base: Wine - Delicato Merlot | G00148 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
+[pr_goods_base:G00164] pr_goods_base:G00164  ▸  pr_goods_base: Wine - Pinot Grigio Collavini | G00164 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00172] pr_goods_base:G00172  ▸  pr_goods_base: Wine - Red, Pinot Noir, Chateau | G00172 | 2023-12-18 | Y | 9999.0 | 48000.0 | 2023-12-19 00:00:00 | 2024
+[pr_goods_base:G00174] pr_goods_base:G00174  ▸  pr_goods_base: Wine La Vielle Ferme Cote Du | G00174 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12
+[pr_goods_base:G00207] pr_goods_base:G00207  ▸  pr_goods_base: Wine - Rubyport | G00207 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
+[pr_goods_base:G00264] pr_goods_base:G00264  ▸  pr_goods_base: Wine - Rosso Del Veronese Igt | G00264 | 2023-12-18 | Y | 9999.0 | 54000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00277] pr_goods_base:G00277  ▸  pr_goods_base: Wine - Wyndham Estate Bin 777 | G00277 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00282] pr_goods_base:G00282  ▸  pr_goods_base: Wine - Chateauneuf Du Pape | G00282 | 2023-12-18 | Y | 9999.0 | 29000.0 | 2023-12-19 00:00:00 | 2024-12-1
+[pr_goods_base:G00293] pr_goods_base:G00293  ▸  pr_goods_base: Wine - Casablanca Valley | G00293 | 2023-12-18 | Y | 9999.0 | 12000.0 | 2023-12-19 00:00:00 | 2024-12-18
+... +10 more</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00010
 pr_goods_base:G00034
@@ -6328,73 +7394,85 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>h017</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>신라면이 잘 팔리나요?</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>conversational</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>L7</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Shin Ramyun(G00005) 판매이력 확인. 45개 판매로 5위</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00005</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>h018</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>양고기 제품 중 뼈 없는 것</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>L4</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
+          <t>Shin Ramyun(G00005) 판매이력 확인. 45개 판매로 5위</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>h018</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>양고기 제품 중 뼈 없는 것</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
           <t>Lamb + Boneless 필터</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00470] pr_goods_base:G00470  ▸  pr_goods_base: Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18
+[pr_goods_base:G00492] pr_goods_base:G00492  ▸  pr_goods_base: Lamb - Loin, Trimmed, Boneless | G00492 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-1
+[pr_goods_base:G00736] pr_goods_base:G00736  ▸  pr_goods_base: Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00470
 pr_goods_base:G00492
@@ -6402,74 +7480,81 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>h019</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>facial skincare product</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>CLA Mask를 영어 카테고리로 검색</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>[pr_goods_base:G00002] pr_goods_base:G00002  ▸  pr_goods_base: CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
+[pr_goods_base:G00006] pr_goods_base:G00006  ▸  pr_goods_base: Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>pr_goods_base:G00002
 pr_goods_base:G00006</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>h020</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>유저 한 명이 작성한 리뷰 수는 최대 몇 건?</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>user_id GROUP BY COUNT MAX = 23건</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval/data/gt_datasets.xlsx
+++ b/eval/data/gt_datasets.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -887,8 +887,8 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>[products:12800001] products:12800001  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
-[products:12800007] products:12800007  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800007 | 69900.0 | 20.0 | 2932 | 204946800.0</t>
+          <t>1. 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
+2. 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800007 | 69900.0 | 20.0 | 2932 | 204946800.0</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>[products:12800004] products:12800004  ▸  products: 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+          <t>1. 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>[products:12800009] products:12800009  ▸  products: 24SS 린넨 와이드 밴딩 슬랙스 | LBL 시즌2025 S/S NO.1 | 24SS | 12800009 | 99900.0 | 20.0 | 4416 | 441158400.0</t>
+          <t>1. 24SS 린넨 와이드 밴딩 슬랙스 | LBL 시즌2025 S/S NO.1 | 24SS | 12800009 | 99900.0 | 20.0 | 4416 | 441158400.0</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>[products:12800005] products:12800005  ▸  products: 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0</t>
+          <t>1. 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>[colors:1] colors:1  ▸  colors: 소라 | 1</t>
+          <t>1. 소라 | 1</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>[colors:4] colors:4  ▸  colors: 네이비 | 4</t>
+          <t>1. 네이비 | 4</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>[sizes:2] sizes:2  ▸  sizes: 55 | 2</t>
+          <t>1. 55 | 2</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>[reviews:259000003] reviews:259000003  ▸  reviews: 입으면 날씬해 보여요. 핏이 딱 맞아요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000003 | 12800000 | 약간큼</t>
+          <t>1. 입으면 날씬해 보여요. 핏이 딱 맞아요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000003 | 12800000 | 약간큼</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>[reviews:259000000] reviews:259000000  ▸  reviews: 세탁해도 줄지 않고 마감이 깔끔해요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 보통이에요 | 착용감 | 아주편해요 | 259000000 | 12800000 | 중</t>
+          <t>1. 세탁해도 줄지 않고 마감이 깔끔해요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 보통이에요 | 착용감 | 아주편해요 | 259000000 | 12800000 | 중</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>[reviews:259000004] reviews:259000004  ▸  reviews: 엄마 선물로 구매했는데 너무 좋아하세요. 입으면 편안해요 | 사이즈 | 핏 | 넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000004 | 12800000 | 큼</t>
+          <t>1. 엄마 선물로 구매했는데 너무 좋아하세요. 입으면 편안해요 | 사이즈 | 핏 | 넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000004 | 12800000 | 큼</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>[sales_partners:2] sales_partners:2  ▸  sales_partners: 2 | [NEC]패션사업부 | LBL코리아주식회사</t>
+          <t>1. 2 | [NEC]패션사업부 | LBL코리아주식회사</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>[sales_channels:1] sales_channels:1  ▸  sales_channels: MC | 1 | EC | MC | OneTV(MC)</t>
+          <t>1. MC | 1 | EC | MC | OneTV(MC)</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>[broadcasts:1] broadcasts:1  ▸  broadcasts: 1 | 12800000 | 2024-11-15 | 23:00-23:50 | 2024-11-20 | 2024-11-28</t>
+          <t>1. 1 | 12800000 | 2024-11-15 | 23:00-23:50 | 2024-11-20 | 2024-11-28</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>[products:12800006] products:12800006  ▸  products: 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0</t>
+          <t>1. 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>[products:12800004] products:12800004  ▸  products: 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+          <t>1. 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>[products:12800009] products:12800009  ▸  products: 24SS 린넨 와이드 밴딩 슬랙스 | LBL 시즌2025 S/S NO.1 | 24SS | 12800009 | 99900.0 | 20.0 | 4416 | 441158400.0</t>
+          <t>1. 24SS 린넨 와이드 밴딩 슬랙스 | LBL 시즌2025 S/S NO.1 | 24SS | 12800009 | 99900.0 | 20.0 | 4416 | 441158400.0</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>[products:12800001] products:12800001  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0</t>
+          <t>1. 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1735,9 +1735,9 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>[colors:1] colors:1  ▸  colors: 소라 | 1
-[colors:4] colors:4  ▸  colors: 네이비 | 4
-[colors:5] colors:5  ▸  colors: 블랙 | 5</t>
+          <t>1. 소라 | 1
+2. 네이비 | 4
+3. 블랙 | 5</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1780,9 +1780,9 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
-[products:12800001] products:12800001  ▸  products: 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
-[products:12800005] products:12800005  ▸  products: 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0</t>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+2. 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
+3. 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>[reviews:259000002] reviews:259000002  ▸  reviews: 촉감도 좋고 핏도 라인이 예뻐요 ^^만족합니다 | 사이즈 | 핏 | 타이트해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000002 | 12800000 | 중</t>
+          <t>1. 촉감도 좋고 핏도 라인이 예뻐요 ^^만족합니다 | 사이즈 | 핏 | 타이트해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000002 | 12800000 | 중</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1866,8 +1866,8 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>[reviews:259000000] reviews:259000000  ▸  reviews: 세탁해도 줄지 않고 마감이 깔끔해요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 보통이에요 | 착용감 | 아주편해요 | 259000000 | 12800000 | 중
-[reviews:259000004] reviews:259000004  ▸  reviews: 엄마 선물로 구매했는데 너무 좋아하세요. 입으면 편안해요 | 사이즈 | 핏 | 넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000004 | 12800000 | 큼</t>
+          <t>1. 세탁해도 줄지 않고 마감이 깔끔해요 | 사이즈 | 핏 | 약간넉넉해요 | 신축성 | 보통이에요 | 착용감 | 아주편해요 | 259000000 | 12800000 | 중
+2. 엄마 선물로 구매했는데 너무 좋아하세요. 입으면 편안해요 | 사이즈 | 핏 | 넉넉해요 | 신축성 | 잘늘어나요 | 착용감 | 편해요 | 259000004 | 12800000 | 큼</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1909,8 +1909,8 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>[products:12800000] products:12800000  ▸  products: 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
-[products:12800004] products:12800004  ▸  products: 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+2. 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>[sizes:2] sizes:2  ▸  sizes: 55 | 2</t>
+          <t>1. 55 | 2</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>[sales_partners:2] sales_partners:2  ▸  sales_partners: 2 | [NEC]패션사업부 | LBL코리아주식회사</t>
+          <t>1. 2 | [NEC]패션사업부 | LBL코리아주식회사</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>[broadcasts:1] broadcasts:1  ▸  broadcasts: 1 | 12800000 | 2024-11-15 | 23:00-23:50 | 2024-11-20 | 2024-11-28</t>
+          <t>1. 1 | 12800000 | 2024-11-15 | 23:00-23:50 | 2024-11-20 | 2024-11-28</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -2075,8 +2075,8 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>[products:12800005] products:12800005  ▸  products: 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0
-[products:12800006] products:12800006  ▸  products: 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0</t>
+          <t>1. 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0
+2. 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2248,8 +2248,8 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>[8ff32e537262bfa2] 2020년도_(요약) 2020년 온실가스 감축 및 에너지 절약 업무 추진 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-04-08 16:01:49 &lt;/Document-Metadat
-[d986946925263cee] 2020년도_2020년 온실가스 감축 및 에너지 절약 추진 계획(안) #13  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2011-01-14 09:36:36   수정일: 2020-04-09 11:45:30 &lt;/Document-M</t>
+          <t>1. 2020년도_(요약) 2020년 온실가스 감축 및 에너지 절약 업무 추진 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-04-08 16:01:49 &lt;/Document-Metadata&gt;  ‘20년 온실가스 감축 및 에너지 절약 업무 추…
+2. 2020년도_2020년 온실가스 감축 및 에너지 절약 추진 계획(안) #13  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2011-01-14 09:36:36   수정일: 2020-04-09 11:45:30 &lt;/Document-Metadata&gt;  ❍ 전기 자동차 및 연료전지자동차 구…</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -2295,13 +2295,13 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>[9293b657686b140c] 2020년도_200214 (요약) 2020년도 재활힐링승마센터 운영계획(안)ver.6 #14  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: Ryu   작성일: 2020-01-04 13:13:33   수정일: 2020-02-14 11:06:37 &lt;/Document-Metadata&gt;
-[4c2beab48a4fa8ba] 2020년도_200304 (보고)2020년도 재활힐링승마 사업 전략적 홍보방안ver.5 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-05 15:19:27 &lt;/Document-M
-[d3ab6e9ee63de321] 2020년도_200304 2020년도 재활힐링승마 사업 전략적 홍보방안ver.3 #34  ▸  &lt;Document-Metadata&gt;   제목: □    작성자: Ryu   마지막 수정자: Ryu   작성일: 2020-02-20 15:14:45   수정일: 2020-03-04 18:17:25 &lt;/Document-
-[75f6189810773545] 2022년도_재활힐링승마 고도화를 위한 시범과정 운영계획(안) #38  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-03-05 12:48:37   수정일: 2023-04-30 16:21:05 &lt;/Document-Metadata&gt;
-[ae69bf434db74361] 2024년도_재활힐링승마 표준 프로그램 개발연구 시행 계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: □ 2023년 재활힐링승마 시범과정 운영에 따른 사례분석 약식 연구결과   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-05 13:45:52
-[e26613430bc0f1b8] 2020년도_200214 2020년도 재활힐링승마센터 운영계획(안)ver.9 #88  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: Ryu   작성일: 2020-01-04 13:13:33   수정일: 2020-02-14 11:06:08 &lt;/Documen
-[844757da66c84d87] 2024년도_(붙임) 2024년 재활힐링승마 운영 계획(안) #35  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-24 10:15:58   수정일: 2024-02-04 17:57:34 &lt;/Documen</t>
+          <t>1. 2020년도_200214 (요약) 2020년도 재활힐링승마센터 운영계획(안)ver.6 #14  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: Ryu   작성일: 2020-01-04 13:13:33   수정일: 2020-02-14 11:06:37 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp_BIN00…
+2. 2020년도_200304 (보고)2020년도 재활힐링승마 사업 전략적 홍보방안ver.5 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-05 15:19:27 &lt;/Document-Metadata&gt;  ○ 찾아가는 사회공익힐링승마 (상반기…
+3. 2020년도_200304 2020년도 재활힐링승마 사업 전략적 홍보방안ver.3 #34  ▸  &lt;Document-Metadata&gt;   제목: □    작성자: Ryu   마지막 수정자: Ryu   작성일: 2020-02-20 15:14:45   수정일: 2020-03-04 18:17:25 &lt;/Document-Metadata&gt;  예산사항     ○ 총 소요예산 :…
+4. 2022년도_재활힐링승마 고도화를 위한 시범과정 운영계획(안) #38  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-03-05 12:48:37   수정일: 2023-04-30 16:21:05 &lt;/Document-Metadata&gt;  === Extracted Images (Not In…
+5. 2024년도_재활힐링승마 표준 프로그램 개발연구 시행 계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: □ 2023년 재활힐링승마 시범과정 운영에 따른 사례분석 약식 연구결과   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-05 13:45:52   수정일: 2024-06-16 13:48:25 &lt;/Do…
+6. 2020년도_200214 2020년도 재활힐링승마센터 운영계획(안)ver.9 #88  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: Ryu   작성일: 2020-01-04 13:13:33   수정일: 2020-02-14 11:06:08 &lt;/Document-Metadata&gt;  [Image:temp/image…
+7. 2024년도_(붙임) 2024년 재활힐링승마 운영 계획(안) #35  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-24 10:15:58   수정일: 2024-02-04 17:57:34 &lt;/Document-Metadata&gt;  === Extracted Ima…</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -2352,8 +2352,8 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>[790f2015dc65b6e1] 2020년도_(붙임#2) 2020년 인재개발 기본계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 인 사 노 무 처   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-02 10:20:11   수정일: 2020-02-27 16:52:55 &lt;/Do
-[33ad8cb9e391ffb3] 2020년도_(붙임#1) 인재개발 기본계획(안) 요약 #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-27 16:38:24 &lt;/Documen</t>
+          <t>1. 2020년도_(붙임#2) 2020년 인재개발 기본계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 인 사 노 무 처   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-02 10:20:11   수정일: 2020-02-27 16:52:55 &lt;/Document-Metadata&gt;  &lt;table borde…
+2. 2020년도_(붙임#1) 인재개발 기본계획(안) 요약 #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-27 16:38:24 &lt;/Document-Metadata&gt;  2020년 인재개발 기본계획(안…</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -2399,10 +2399,10 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>[0cf478ddca6e92d5] 2023년도_붙임4 2023년 주요사업 인권영향평가 체크리스트(최종) #29  ▸  &lt;Document-Metadata&gt;   작성자: USER   마지막 수정자: KRA   작성일: 2018-09-04 19:31:17   수정일: 2023-12-21 06:44:31 &lt;/Document-Metadata
-[e507dc22077335c1] 2020년도_별첨_2020년 인권영향평가 결과보고 #14  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2020-11-20 14:17:59   수정일: 2021-05-29 15:46:09 &lt;/Documen
-[dd206af597e56188] 2023년도_붙임1 2023년 인권영향평가 결과보고(최종)★_231222 #11  ▸  &lt;Document-Metadata&gt;   제목: 경영관리처   작성자: KRA   마지막 수정자: KRA   작성일: 2023-12-13 14:18:25   수정일: 2023-12-22 10:01:55 &lt;/Docume
-[005599102a43b8f4] 2023년도_붙임3 2023년 기관운영 인권영향평가 체크리스트(최종) #104  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-09-20 01:25:07   수정일: 2023-12-21 06:47:49 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2023년도_붙임4 2023년 주요사업 인권영향평가 체크리스트(최종) #29  ▸  &lt;Document-Metadata&gt;   작성자: USER   마지막 수정자: KRA   작성일: 2018-09-04 19:31:17   수정일: 2023-12-21 06:44:31 &lt;/Document-Metadata&gt;  [Sheet: 교육, 강습 및 기타 사업] [Ta…
+2. 2020년도_별첨_2020년 인권영향평가 결과보고 #14  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2020-11-20 14:17:59   수정일: 2021-05-29 15:46:09 &lt;/Document-Metadata&gt;  ㅇ (교육 관련 이해관계자 인권…
+3. 2023년도_붙임1 2023년 인권영향평가 결과보고(최종)★_231222 #11  ▸  &lt;Document-Metadata&gt;   제목: 경영관리처   작성자: KRA   마지막 수정자: KRA   작성일: 2023-12-13 14:18:25   수정일: 2023-12-22 10:01:55 &lt;/Document-Metadata&gt;  거 주3일 전환 지속 추진  …
+4. 2023년도_붙임3 2023년 기관운영 인권영향평가 체크리스트(최종) #104  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-09-20 01:25:07   수정일: 2023-12-21 06:47:49 &lt;/Document-Metadata&gt;  [Sheet: 11. 직장 내 인권보호] [Tabl…</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -2450,15 +2450,15 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>[2b77cb92e3b2e52e] 2020년도_붙임3. 2020년 총 교배횟수(모든교배내역) #144  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:38:42 &lt;/Document-Metadata&gt;
-[6cdb3f17c1eafe48] 2020년도_붙임2. 2020년 총 교배실적(두수) #111  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:36:12 &lt;/Document-Metadata&gt;
-[bbe40d855e6cc165] 2021년도_경주마 교배 및 번식분야 복지 가이드라인 수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-02 15:44:31 &lt;/Document-M
-[72b1245e55ab96fc] 2021년도_경주마 교배 및 번식분야 복지 가이드라인(안) #17  ▸  &lt;Document-Metadata&gt;   제목: 한국마사회 교배 및 번식 말 복지 가이드라인 초안    작성자: User2007   마지막 수정자: KRA   작성일: 2021-08-07 21:34:58   수정일:
-[57ae80a2b693d18f] 2020년도_붙임4. 2020년 유상교배 수익내역 #6  ▸  &lt;Document-Metadata&gt;   작성자: user   마지막 수정자: KRA   작성일: 2013-10-13 05:56:53   수정일: 2020-12-11 01:28:30 &lt;/Document-Metadata
-[43b8261fe9a4b3ca] 2020년도_@ (결재상신) 2020년 경주마 생산 및 교배지원 결과보고 @ #19  ▸  &lt;Document-Metadata&gt;   제목: 2002. 내륙 민간목장 생산 및 교배지원 결과   작성자: 한국마사회 원당목장팀 대리 임진호   키워드: 
+          <t>1. 2020년도_붙임3. 2020년 총 교배횟수(모든교배내역) #144  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:38:42 &lt;/Document-Metadata&gt;  [Sheet: 2020 총 교배횟수] [Table …
+2. 2020년도_붙임2. 2020년 총 교배실적(두수) #111  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:36:12 &lt;/Document-Metadata&gt;  [Sheet: 2020년 총 교배두수_최종교배기준]…
+3. 2021년도_경주마 교배 및 번식분야 복지 가이드라인 수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-02 15:44:31 &lt;/Document-Metadata&gt;  경주마 교배 및 번식분야 복지 가이드…
+4. 2021년도_경주마 교배 및 번식분야 복지 가이드라인(안) #17  ▸  &lt;Document-Metadata&gt;   제목: 한국마사회 교배 및 번식 말 복지 가이드라인 초안    작성자: User2007   마지막 수정자: KRA   작성일: 2021-08-07 21:34:58   수정일: 2021-12-02 11:22:35 &lt;/Document…
+5. 2020년도_붙임4. 2020년 유상교배 수익내역 #6  ▸  &lt;Document-Metadata&gt;   작성자: user   마지막 수정자: KRA   작성일: 2013-10-13 05:56:53   수정일: 2020-12-11 01:28:30 &lt;/Document-Metadata&gt;  [Sheet: 작업용] [Table Chunk 7…
+6. 2020년도_@ (결재상신) 2020년 경주마 생산 및 교배지원 결과보고 @ #19  ▸  &lt;Document-Metadata&gt;   제목: 2002. 내륙 민간목장 생산 및 교배지원 결과   작성자: 한국마사회 원당목장팀 대리 임진호   키워드: 
     설명: 
-    마지막 수정자: KRA
-[e39b4656a5219700] 2020년도_@ (요약) 2020년 경주마 생산 및 교배지원 결과보고 @ #3  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-12-17 11:13:23 &lt;/Document-Metadat</t>
+    마지막 수정자: KRA   작성일: 2005-08-25 10:09:53   수정…
+7. 2020년도_@ (요약) 2020년 경주마 생산 및 교배지원 결과보고 @ #3  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-12-17 11:13:23 &lt;/Document-Metadata&gt;  두, 민간 1,485두)      ○ 전체 대비…</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -2509,8 +2509,8 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>[803aa364d8f1f722] 2021년도_(별첨) 한국마사회 인권침해 구제절차 및 예방활동 매뉴얼(202112) #0  ▸  &lt;Document-Metadata&gt;   제목: 2017   작성자: ROEN11   마지막 수정자: KRA   작성일: 2017-11-20 09:30:38   수정일: 2023-04-13 13:51:00 &lt;/Docu
-[e074f8fc80056924] 2023년도_(별첨) 한국마사회 인권침해 구제절차 및 예방활동 매뉴얼(202112) #0  ▸  &lt;Document-Metadata&gt;   제목: 2017   작성자: ROEN11   마지막 수정자: KRA   작성일: 2017-11-20 09:30:38   수정일: 2023-04-13 13:51:00 &lt;/Docu</t>
+          <t>1. 2021년도_(별첨) 한국마사회 인권침해 구제절차 및 예방활동 매뉴얼(202112) #0  ▸  &lt;Document-Metadata&gt;   제목: 2017   작성자: ROEN11   마지막 수정자: KRA   작성일: 2017-11-20 09:30:38   수정일: 2023-04-13 13:51:00 &lt;/Document-Metadata&gt;  &lt;table border=…
+2. 2023년도_(별첨) 한국마사회 인권침해 구제절차 및 예방활동 매뉴얼(202112) #0  ▸  &lt;Document-Metadata&gt;   제목: 2017   작성자: ROEN11   마지막 수정자: KRA   작성일: 2017-11-20 09:30:38   수정일: 2023-04-13 13:51:00 &lt;/Document-Metadata&gt;  &lt;table border=…</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -2556,10 +2556,10 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>[3b6b26357ad2ce21] 2020년도_(요약) 2020년 이용자보호 추진계획 보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-21 13:18:29 &lt;/Document-M
-[24413d0baba3f505] 2020년도_(붙임)'20 이용자보호 현업과제 운영계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제도 확산   작성자: KRA   마지막 수정자: KRA   작성일: 2020-06-12 15:43:26   수정일: 2020-07-25 17:48:38 &lt;/Docume
-[d4d20ca93dfcd728] 2020년도_(본문) 2020년 이용자보호 추진계획 #15  ▸  &lt;Document-Metadata&gt;   제목: 회의자료    작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-19 16:10:55   수정일: 2020-03-21 10:39:32 &lt;/Docume
-[5d0dd8502b5a0cb8] 2020년도_(본문) 20년 이용자보호 액션플랜 수립계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 제목    작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-16 09:57:57   수정일: 2020-02-09 15:46:56 &lt;/Document</t>
+          <t>1. 2020년도_(요약) 2020년 이용자보호 추진계획 보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-21 13:18:29 &lt;/Document-Metadata&gt;  * 세부 추진계획은 과제별로 별도 수…
+2. 2020년도_(붙임)'20 이용자보호 현업과제 운영계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제도 확산   작성자: KRA   마지막 수정자: KRA   작성일: 2020-06-12 15:43:26   수정일: 2020-07-25 17:48:38 &lt;/Document-Metadata&gt;  가. 추진절차  &lt;table …
+3. 2020년도_(본문) 2020년 이용자보호 추진계획 #15  ▸  &lt;Document-Metadata&gt;   제목: 회의자료    작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-19 16:10:55   수정일: 2020-03-21 10:39:32 &lt;/Document-Metadata&gt;  (고객보호부) 과제 총괄 관리…
+4. 2020년도_(본문) 20년 이용자보호 액션플랜 수립계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 제목    작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-16 09:57:57   수정일: 2020-02-09 15:46:56 &lt;/Document-Metadata&gt;  [Image:temp/images…</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -2607,8 +2607,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>[012dcbe84f52c595] 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Me
-[2df376eb9253a430] 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Me</t>
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -2654,9 +2654,9 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>[d13b5751987d7a60] 2021년도_(본문) 사회적가치 실현을 위한 2021년 윤리경영 기본계획(안) #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-02 16:19:40   수정일: 2021-07-15 10:25:51 &lt;/Document-Metadata&gt;
-[d908c9b95b9e082a] 2021년도_(요약) 2021년 윤리경영 기본계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2021-07-15 10:
-[8c423366bc12e4d4] 2023년도_★(결재) 2023년 윤리경영 기본계획(이사회 의견 반영 후)★ #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-06-11 15:07:02   수정일: 2023-07-01 14:03:33 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2021년도_(본문) 사회적가치 실현을 위한 2021년 윤리경영 기본계획(안) #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-02 16:19:40   수정일: 2021-07-15 10:25:51 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+2. 2021년도_(요약) 2021년 윤리경영 기본계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2021-07-15 10:28:48 &lt;/Document-Metadata&gt;  조사…
+3. 2023년도_★(결재) 2023년 윤리경영 기본계획(이사회 의견 반영 후)★ #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-06-11 15:07:02   수정일: 2023-07-01 14:03:33 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -2703,9 +2703,9 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>[a4ed66c59a820e40] 2020년도_(붙임#14) 사업별 조직별 예산 계층구조 #78  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-11 08:44:57   수정일: 2020-03-13 01:24:08 &lt;/Document-Metadata&gt;
-[da8efb3618249a33] 2022년도_[붙임2] 2023년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-15 02:28:16   수정일: 2023-02-16 04:38:18 &lt;/Document-Metadata&gt;
-[aa6aff98e2caa723] 2023년도_[붙임2] 2024년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-14 07:46:48   수정일: 2024-01-31 07:29:46 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2020년도_(붙임#14) 사업별 조직별 예산 계층구조 #78  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-11 08:44:57   수정일: 2020-03-13 01:24:08 &lt;/Document-Metadata&gt;  [Sheet: 사업별 예산 계층구조] [Table …
+2. 2022년도_[붙임2] 2023년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-15 02:28:16   수정일: 2023-02-16 04:38:18 &lt;/Document-Metadata&gt;  [Sheet: 조직별 예산 계층구조] [Table …
+3. 2023년도_[붙임2] 2024년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-14 07:46:48   수정일: 2024-01-31 07:29:46 &lt;/Document-Metadata&gt;  [Sheet: 조직별 예산 계층구조] [Table …</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -2752,10 +2752,10 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>[436d43261922a8da] 2020년도_(기재부) 2020년도 예산 및 기금운용계획집행지침 #120  ▸  &lt;Document-Metadata&gt;   제목: ?    작성자: Owner   키워드: 
+          <t>1. 2020년도_(기재부) 2020년도 예산 및 기금운용계획집행지침 #120  ▸  &lt;Document-Metadata&gt;   제목: ?    작성자: Owner   키워드: 
     설명: 
-    마지막 수정자: mafra   작성일: 2005-01-14 10:13:01   수정일: 20
-[4196a8bfffd7ea93] 2024년도_[붙임3] (기재부) 2024년도 예산 및 기금운용계획 집행지침 #282  ▸  &lt;Document-Metadata&gt;   Version Tagetapplication: WORDPROCESSOR   Version Major: 5   Version Minor: 0   Version Micro: 5</t>
+    마지막 수정자: mafra   작성일: 2005-01-14 10:13:01   수정일: 2020-01-08 11:01:36 &lt;/Document-M…
+2. 2024년도_[붙임3] (기재부) 2024년도 예산 및 기금운용계획 집행지침 #282  ▸  &lt;Document-Metadata&gt;   Version Tagetapplication: WORDPROCESSOR   Version Major: 5   Version Minor: 0   Version Micro: 5   Version Buildnumber: 0   Vers…</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -2801,8 +2801,8 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>[27325f8e49d559f4] 2020년도_(본문) 2020년도 내부경영평가제도 개선(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-22 09:53:12 &lt;/Documen
-[06ea8eb0c6498c61] 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-M</t>
+          <t>1. 2020년도_(본문) 2020년도 내부경영평가제도 개선(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-22 09:53:12 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+2. 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-Metadata&gt;  가와 사업성과평가 통합    ◦ (차…</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>[36f5479362d3d864] 2020년도_201020 지사 고객입장 및 방역관리 방안(최종) #25  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-10-16 08:23:47   수정일: 2020-10-20 18:44:49 &lt;/Documen</t>
+          <t>1. 2020년도_201020 지사 고객입장 및 방역관리 방안(최종) #25  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-10-16 08:23:47   수정일: 2020-10-20 18:44:49 &lt;/Document-Metadata&gt;  [Image:temp/image…</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -2893,9 +2893,9 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>[afd0f60cc9c978c0] 2022년도_붙임 1. 스마트 사무환경 구축 및 망분리 개선 견적서(총괄) #27  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-02 04:07:54   수정일: 2023-08-17 03:33:36 &lt;/Document-Metadata&gt;
-[9d226cce773a4434] 2022년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen
-[993ad9a5e29994fc] 2023년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen</t>
+          <t>1. 2022년도_붙임 1. 스마트 사무환경 구축 및 망분리 개선 견적서(총괄) #27  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-02 04:07:54   수정일: 2023-08-17 03:33:36 &lt;/Document-Metadata&gt;  [Sheet: 3.2 SSD] [Image:temp…
+2. 2022년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Document-Metadata&gt;  [Image:temp/image…
+3. 2023년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Document-Metadata&gt;  [Image:temp/image…</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -2942,10 +2942,10 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>[c8ed7811592eac64] 2022년도_(붙임2)재물조사결과내역(전체) #393  ▸  &lt;Document-Metadata&gt;   작성일: 2025-12-05 08:14:00   수정일: 2025-12-05 08:14:00 &lt;/Document-Metadata&gt;  [Page Number: 394]  &lt;tab
-[59854a9e60c7d3ab] 2022년도_(붙임2)재물조사결과내역(전체) #106  ▸  &lt;Document-Metadata&gt;   작성자: KA B &lt;/Document-Metadata&gt;  [Sheet: 전체] [Table Chunk 107/107] | 자산번호 | SAP자산번호 | 자산구분 | 세분류 |
-[6a278de5a7f63982] 2022년도_(붙임1)2022년 정기 재물조사 실시 결과보고 #9  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-23 10:36:27   수정일: 2023-01-19 14:22:42 &lt;/Documen
-[95765c577ef9e336] 2024년도_(붙임1) 2024년 재물조사 시행 결과보고_241227 #15  ▸  &lt;Document-Metadata&gt;   제목: 재물조정   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-12 16:02:40   수정일: 2024-12-27 09:49:24 &lt;/Documen</t>
+          <t>1. 2022년도_(붙임2)재물조사결과내역(전체) #393  ▸  &lt;Document-Metadata&gt;   작성일: 2025-12-05 08:14:00   수정일: 2025-12-05 08:14:00 &lt;/Document-Metadata&gt;  [Page Number: 394]  &lt;table&gt;   &lt;tr&gt;     &lt;th&gt;20220842911…
+2. 2022년도_(붙임2)재물조사결과내역(전체) #106  ▸  &lt;Document-Metadata&gt;   작성자: KA B &lt;/Document-Metadata&gt;  [Sheet: 전체] [Table Chunk 107/107] | 자산번호 | SAP자산번호 | 자산구분 | 세분류 | 본부명 | 자산내역 | 취득일자 | 구매금액 | 단가 …
+3. 2022년도_(붙임1)2022년 정기 재물조사 실시 결과보고 #9  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-23 10:36:27   수정일: 2023-01-19 14:22:42 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+4. 2024년도_(붙임1) 2024년 재물조사 시행 결과보고_241227 #15  ▸  &lt;Document-Metadata&gt;   제목: 재물조정   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-12 16:02:40   수정일: 2024-12-27 09:49:24 &lt;/Document-Metadata&gt;  전 부서    ❍ 조직개편, 인…</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2993,8 +2993,8 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>[e4f72caaf5619284] 2023년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;
-[7d016a8eb300196a] 2024년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2023년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;  [Sheet: 15년도 이하 소형복합기] [Tabl…
+2. 2024년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;  [Sheet: 15년도 이하 소형복합기] [Tabl…</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -3040,8 +3040,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>[1dd7a41b6d49067a] 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-M
-[68c173524cf22c47] 2020년도_붙임_1_2020년 도심승마체험 시행계획(요약, 최종) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-03-07 18:01:46 &lt;/Document-Metadat</t>
+          <t>1. 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-Metadata&gt;  === Extracted Images…
+2. 2020년도_붙임_1_2020년 도심승마체험 시행계획(요약, 최종) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-03-07 18:01:46 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;t…</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -3087,8 +3087,8 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>[a5a7f37b741bdeee] 2020년도_제2차 KPC 개최계획(안) 최종 #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-21 09:21:54   수정일: 2020-08-21 17:42:45 &lt;/Document-Metadata&gt;
-[33640ab36a7a2b8c] 2024년도_2024년 제 2차 KPC 개최 심의 안건 #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-18 12:53:46 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2020년도_제2차 KPC 개최계획(안) 최종 #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-21 09:21:54   수정일: 2020-08-21 17:42:45 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+2. 2024년도_2024년 제 2차 KPC 개최 심의 안건 #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-18 12:53:46 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -3134,26 +3134,26 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>[dd534b8aff2c0b47] 2023년도_(별첨2)말산업 연구사업 과제목록(13-23) #23  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2024-03-30 11:46:30 &lt;/Document-Metadata&gt;
-[858311a17598e098] 2024년도_(별첨2)말산업 연구사업 과제목록(13-23) #23  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2024-03-30 11:46:30 &lt;/Document-Metadata&gt;
-[37d0fe4807f770c9] 2020년도_2020년 말산업 연구사업 추진계획(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2020-05-30 14:55:48 &lt;/Document-M
-[665c95e2452936a4] 2021년도_2021년 말산업 연구사업 추진계획(요약,결재용) #3  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-05-08 09:19:09 &lt;/Documen
-[6498c34e04755c85] 2021년도_[붙임2] 2021년 말산업 분야 기술상용화 연구 추진계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-06-20 11:32:59 &lt;/Documen
-[ca05784c3e5aac4f] 2023년도_2023년 말산업 연구사업 추진계획(요약) #2  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2023-04-05 15:06:47 &lt;/Documen
-[9ef0a8ba81ba8b76] 2024년도_2024년 말산업연구소 주요사업 추진계획(본문)  ▸  2024년도_2024년 말산업연구소 주요사업 추진계획(본문)
-[5751364a07bd6432] 2022년도_(별첨2)말산업연구소 연구과제 목록('13_'22) #22  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2023-04-05 01:26:43 &lt;/Document-Metadata&gt;
-[a327f99bb35ec842] 2020년도_2020년 말산업 연구사업 추진계획(요약) #2  ▸  &lt;Document-Metadata&gt;   작성자: 류성훈   마지막 수정자: KRA   작성일: 2014-07-03 13:36:03   수정일: 2020-05-30 15:39:20 &lt;/Document-Metadata&gt;
-[72abd3a0e6e49e3b] 2020년도_[붙임1] 2020년 말산업 분야 위탁연구과제 추진 계획(안) #7  ▸  &lt;Document-Metadata&gt;   제목: 2016   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-25 11:04:51   수정일: 2020-06-24 16:38:49 &lt;/Documen
-[7391433818c2aa29] 2021년도_2021년 말산업 연구사업 추진계획(안,결재용) #10  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2021-05-09 17:06:29 &lt;/Document-M
-[fd1f3b6cb4f3c808] 2021년도_[붙임1] 2021년 말산업 분야 기술상용화 연구 추진계획(요약) #4  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-06-20 11:32:44 &lt;/Documen
-[69aa111c4c3c9c4e] 2023년도_2023년 말산업 연구사업 변경 및 신규과제 추진계획(요약) #3  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2023-12-21 10:35:31 &lt;/Documen
-[425d5a095aa05d99] 2023년도_2023년 말산업 연구사업 추진계획(본문) #16  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2023-04-05 15:01:17 &lt;/Document-M
-[530eee4771fc7f6a] 2023년도_2023년 말산업연구소 주요사업 추진계획(본문)  ▸  2023년도_2023년 말산업연구소 주요사업 추진계획(본문)
-[3069278768910766] 2023년도_2023년 말산업연구소 주요사업 추진계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2023-03-09 15:45:08 &lt;/Documen
-[dce393b4643910d6] 2023년도_23년_말산업_R&amp;D_연구과제_변경_및 _추진계획(안)) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-12-21 09:45:12 &lt;/Document-M
-[7b6883061d74991f] 2024년도_2024년 말산업 연구사업 추진계획(본문) #25  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2024-03-31 10:52:49 &lt;/Document-M
-[c7acbf436686b08b] 2024년도_2024년 말산업 연구사업 추진계획(요약) #12  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2024-03-31 11:13:34 &lt;/Documen
-[f7f1618283b6dd00] 2024년도_2024년 말산업연구소 주요사업 추진계획(본문)  ▸  2024년도_2024년 말산업연구소 주요사업 추진계획(본문)
+          <t>1. 2023년도_(별첨2)말산업 연구사업 과제목록(13-23) #23  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2024-03-30 11:46:30 &lt;/Document-Metadata&gt;  [Sheet: 분야별] [Table 3] | 계 |…
+2. 2024년도_(별첨2)말산업 연구사업 과제목록(13-23) #23  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2024-03-30 11:46:30 &lt;/Document-Metadata&gt;  [Sheet: 분야별] [Table 3] | 계 |…
+3. 2020년도_2020년 말산업 연구사업 추진계획(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2020-05-30 14:55:48 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+4. 2021년도_2021년 말산업 연구사업 추진계획(요약,결재용) #3  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-05-08 09:19:09 &lt;/Document-Metadata&gt;  * 3번 과제는 제주대와 협업하…
+5. 2021년도_[붙임2] 2021년 말산업 분야 기술상용화 연구 추진계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-06-20 11:32:59 &lt;/Document-Metadata&gt;  4. 소요예산 : 축발기금  &lt;…
+6. 2023년도_2023년 말산업 연구사업 추진계획(요약) #2  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2023-04-05 15:06:47 &lt;/Document-Metadata&gt;  ※ 2022년도 연구사업 7개 …
+7. 2024년도_2024년 말산업연구소 주요사업 추진계획(본문)  ▸  2024년도_2024년 말산업연구소 주요사업 추진계획(본문)
+8. 2022년도_(별첨2)말산업연구소 연구과제 목록('13_'22) #22  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-05 04:00:04   수정일: 2023-04-05 01:26:43 &lt;/Document-Metadata&gt;  [Sheet: 분야별] [Table 3] | 계 |…
+9. 2020년도_2020년 말산업 연구사업 추진계획(요약) #2  ▸  &lt;Document-Metadata&gt;   작성자: 류성훈   마지막 수정자: KRA   작성일: 2014-07-03 13:36:03   수정일: 2020-05-30 15:39:20 &lt;/Document-Metadata&gt;  ※ 민간대상 말산업 기술분야 자율공모(1건) 별도 …
+10. 2020년도_[붙임1] 2020년 말산업 분야 위탁연구과제 추진 계획(안) #7  ▸  &lt;Document-Metadata&gt;   제목: 2016   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-25 11:04:51   수정일: 2020-06-24 16:38:49 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+11. 2021년도_2021년 말산업 연구사업 추진계획(안,결재용) #10  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2021-05-09 17:06:29 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+12. 2021년도_[붙임1] 2021년 말산업 분야 기술상용화 연구 추진계획(요약) #4  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2021-06-20 11:32:44 &lt;/Document-Metadata&gt;  1.gif]         * …
+13. 2023년도_2023년 말산업 연구사업 변경 및 신규과제 추진계획(요약) #3  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2023-12-21 10:35:31 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+14. 2023년도_2023년 말산업 연구사업 추진계획(본문) #16  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2023-04-05 15:01:17 &lt;/Document-Metadata&gt;  자체예산 과제  &lt;table bord…
+15. 2023년도_2023년 말산업연구소 주요사업 추진계획(본문)  ▸  2023년도_2023년 말산업연구소 주요사업 추진계획(본문)
+16. 2023년도_2023년 말산업연구소 주요사업 추진계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2023-03-09 15:45:08 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+17. 2023년도_23년_말산업_R&amp;D_연구과제_변경_및 _추진계획(안)) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-12-21 09:45:12 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+18. 2024년도_2024년 말산업 연구사업 추진계획(본문) #25  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-15 10:56:58   수정일: 2024-03-31 10:52:49 &lt;/Document-Metadata&gt;  (축발기금과제) 축발기금 내 R&amp;D …
+19. 2024년도_2024년 말산업 연구사업 추진계획(요약) #12  ▸  &lt;Document-Metadata&gt;   제목: 운영경과   작성자: Ryu   마지막 수정자: KRA   작성일: 2021-03-10 15:28:13   수정일: 2024-03-31 11:13:34 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+20. 2024년도_2024년 말산업연구소 주요사업 추진계획(본문)  ▸  2024년도_2024년 말산업연구소 주요사업 추진계획(본문)
 ... +2 more</t>
         </is>
       </c>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>[157016074626f25d] 2021년도_(별첨1) 연도별 마주 경제적기준(2007_2021) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-20 01:23:19   수정일: 2021-11-26 04:01:22 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2021년도_(별첨1) 연도별 마주 경제적기준(2007_2021) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-20 01:23:19   수정일: 2021-11-26 04:01:22 &lt;/Document-Metadata&gt;  [Sheet: 정리본] [Table Chunk 7/…</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -3892,26 +3892,26 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>[0346542e0be2b2ab] 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Documen
-[123f03df3479517e] 2022년도_[별첨1] KRA-ESG경영 진단모델(세부 진단기준)_최종 #43  ▸  &lt;Document-Metadata&gt;   제목: 《 KRA   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-04 14:33:57   수정일: 2023-05-27 10:21:04 &lt;/Docume
-[156fec294ba67ae4] 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-M
-[210e0e2db641965a] 2020년도_[붙임 1] 2020년 재활승마 활성화 지원 시범사업 계획(안_요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 말산업육성본부   작성자: KRA   마지막 수정자: KRA   작성일: 2017-05-24 17:59:41   수정일: 2020-08-07 15:31:04 &lt;/Docu
-[2212a005847a8f98] 2023년도_2023년 힐링승마 지원사업 추진 계획(안)_220308_2 #43  ▸  &lt;Document-Metadata&gt;   제목: 목 적   작성자: KRA   설명: |Fasoo_Trace_ID:eyJub2RlMSI6eyJkc2QiOiIwMTAwMDAwMDAwMDAxODMwIiwibG9nVGltZ
-[27dcbb61e82d6f82] 2024년도_과제 및 사업별 담당부서 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-08 02:27:01   수정일: 2024-06-13 05:02:20 &lt;/Document-Metadata&gt;
-[2a67e1073fe83029] 2022년도_2022 힐링승마 지원사업 운영 결과보고_221222 #25  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-08-06 09:18:55   수정일: 2022-12-22 18:09:26 &lt;/Document-Metadata&gt;
-[2d94f6c769030bda] 2020년도_경주마 통합 건강관리시스템 추진계획(안) #19  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2020-05-27 10:31:20 &lt;/Document-M
-[33882770624ec69f] 2022년도_「말의 인도적인 처리 가이드라인」수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2022-12-21 14:48:38 &lt;/Document-M
-[345beb807d95ba70] 2020년도_★(결재) 2020 사회공익힐링 승마 사업 기본 운영 계획 #5  ▸  &lt;Document-Metadata&gt;   제목: 2019 전국민 승마체험 사업 기본계획   작성자: user   마지막 수정자: KRA   작성일: 2019-02-15 13:56:48   수정일: 2020-02-26
-[386c3d238d9e12b0] 2021년도_(요약) 2021 사회공익 힐링승마 사업 결과보고 #4  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-23 17:48:23 &lt;/Document-M
-[3b4dc85349de4eae] 2023년도_(요약) 말등록부 연간 업무 추진계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-21 11:12:57 &lt;/Document-M
-[3fe2d89ca01994f0] 2023년도_[붙임1] 해외종축개발운영위원회규정 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: 2170058   작성일: 2014-08-15 11:42:18   수정일: 2024-05-26 10:50:28 &lt;/Docume
-[40122ffcb05effea] 2020년도_★(요약) 2020 사회공익힐링 승마 사업 기본 운영 계획 #10  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-04 13:13:33   수정일: 2020-02-26 16:19:50 &lt;/Document-Metadata&gt;
-[4c2beab48a4fa8ba] 2020년도_200304 (보고)2020년도 재활힐링승마 사업 전략적 홍보방안ver.5 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-05 15:19:27 &lt;/Document-M
-[4cb0ece55fc920e7] 2023년도_(요약) 2023년 말복지센터 업무 추진계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 2022   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-18 10:11:25   수정일: 2023-02-09 09:59:44 &lt;/Documen
-[4f2b02c85a84bf0f] 2024년도_2. 2024년 경주마 토탈 케어시스템 운영 계획(안) 1부 #23  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-02-04 09:56:05 &lt;/Document-Met
-[4f5b39b0938daff2] 2024년도_(붙임 1) 말용도 다각화 추진계획_요약 #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-06-01 17:40:16 &lt;/Document-M
-[54275dff6b495fb6] 2024년도_1. 2024년 경주마 토탈 케어시스템 운영 계획(안) 1부(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 2022   작성자: KRA   마지막 수정자: KRA   작성일: 2022-04-17 09:56:03   수정일: 2024-02-03 17:32:13 &lt;/Documen
-[551eb387c7145222] 2024년도_[붙임1] 해외종축개발운영위원회규정 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: 2170058   작성일: 2014-08-15 11:42:18   수정일: 2024-05-26 10:50:28 &lt;/Docume
+          <t>1. 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Document-Metadata&gt;  (단, 사업담당자의 재량으로 지…
+2. 2022년도_[별첨1] KRA-ESG경영 진단모델(세부 진단기준)_최종 #43  ▸  &lt;Document-Metadata&gt;   제목: 《 KRA   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-04 14:33:57   수정일: 2023-05-27 10:21:04 &lt;/Document-Metadata&gt;  &lt;table border='1…
+3. 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-Metadata&gt;  (치료) 복지중심 의료서비스 지원 강…
+4. 2020년도_[붙임 1] 2020년 재활승마 활성화 지원 시범사업 계획(안_요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 말산업육성본부   작성자: KRA   마지막 수정자: KRA   작성일: 2017-05-24 17:59:41   수정일: 2020-08-07 15:31:04 &lt;/Document-Metadata&gt;  [Image:temp/im…
+5. 2023년도_2023년 힐링승마 지원사업 추진 계획(안)_220308_2 #43  ▸  &lt;Document-Metadata&gt;   제목: 목 적   작성자: KRA   설명: |Fasoo_Trace_ID:eyJub2RlMSI6eyJkc2QiOiIwMTAwMDAwMDAwMDAxODMwIiwibG9nVGltZSI6IjIwMjItMDEtMjJUMDE6MzM6MjB…
+6. 2024년도_과제 및 사업별 담당부서 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-08 02:27:01   수정일: 2024-06-13 05:02:20 &lt;/Document-Metadata&gt;  [Sheet: 과제 및 사업별 담당] [Table …
+7. 2022년도_2022 힐링승마 지원사업 운영 결과보고_221222 #25  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-08-06 09:18:55   수정일: 2022-12-22 18:09:26 &lt;/Document-Metadata&gt;  &lt; 하반기 현장점검 결과 및 의견 &gt;  &lt;table…
+8. 2020년도_경주마 통합 건강관리시스템 추진계획(안) #19  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2020-05-27 10:31:20 &lt;/Document-Metadata&gt;  === Extracted Images…
+9. 2022년도_「말의 인도적인 처리 가이드라인」수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2022-12-21 14:48:38 &lt;/Document-Metadata&gt;  「말의 인도적인 처리 가이드라인」수립…
+10. 2020년도_★(결재) 2020 사회공익힐링 승마 사업 기본 운영 계획 #5  ▸  &lt;Document-Metadata&gt;   제목: 2019 전국민 승마체험 사업 기본계획   작성자: user   마지막 수정자: KRA   작성일: 2019-02-15 13:56:48   수정일: 2020-02-26 18:10:51 &lt;/Document-Metadata&gt; …
+11. 2021년도_(요약) 2021 사회공익 힐링승마 사업 결과보고 #4  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-23 17:48:23 &lt;/Document-Metadata&gt;  * 스트레스 감소 인원 대상 강습 전…
+12. 2023년도_(요약) 말등록부 연간 업무 추진계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-21 11:12:57 &lt;/Document-Metadata&gt;  3. 소요예산 : 438백만원 (마사…
+13. 2023년도_[붙임1] 해외종축개발운영위원회규정 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: 2170058   작성일: 2014-08-15 11:42:18   수정일: 2024-05-26 10:50:28 &lt;/Document-Metadata&gt;  &lt;table border='1…
+14. 2020년도_★(요약) 2020 사회공익힐링 승마 사업 기본 운영 계획 #10  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-04 13:13:33   수정일: 2020-02-26 16:19:50 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+15. 2020년도_200304 (보고)2020년도 재활힐링승마 사업 전략적 홍보방안ver.5 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-05 15:19:27 &lt;/Document-Metadata&gt;  ○ 찾아가는 사회공익힐링승마 (상반기…
+16. 2023년도_(요약) 2023년 말복지센터 업무 추진계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 2022   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-18 10:11:25   수정일: 2023-02-09 09:59:44 &lt;/Document-Metadata&gt;  * `23년 마주출연 기금(10…
+17. 2024년도_2. 2024년 경주마 토탈 케어시스템 운영 계획(안) 1부 #23  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-02-04 09:56:05 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr…
+18. 2024년도_(붙임 1) 말용도 다각화 추진계획_요약 #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-06-01 17:40:16 &lt;/Document-Metadata&gt;  ㅇ 지원대상 : 국내 말 등록기관*에…
+19. 2024년도_1. 2024년 경주마 토탈 케어시스템 운영 계획(안) 1부(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 2022   작성자: KRA   마지막 수정자: KRA   작성일: 2022-04-17 09:56:03   수정일: 2024-02-03 17:32:13 &lt;/Document-Metadata&gt;  2024년 경주마 토탈 케어시스…
+20. 2024년도_[붙임1] 해외종축개발운영위원회규정 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: 2170058   작성일: 2014-08-15 11:42:18   수정일: 2024-05-26 10:50:28 &lt;/Document-Metadata&gt;  &lt;table border='1…
 ... +47 more</t>
         </is>
       </c>
@@ -4019,18 +4019,18 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>[1c2e14b3e46641c4] 2023년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-M
-[33ad8cb9e391ffb3] 2020년도_(붙임#1) 인재개발 기본계획(안) 요약 #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-27 16:38:24 &lt;/Documen
-[34ee099eaee5f3ae] 2022년도_(본문) 경주마관계자 임시조치 개선계획(안) #34  ▸  &lt;Document-Metadata&gt;   제목: 2022년 교육훈련 기본계획   작성자: KRA   마지막 수정자: KRA   작성일: 2022-03-04 14:47:46   수정일: 2022-11-11 16:14:3
-[3c78d27b62aca0f0] 2022년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-M
-[5cf871e3bcad9e3b] 2025년도_(붙임3) 2025년 한국마사회 수입 및 지출계획서 #12  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2024-12-19 17:06:39 &lt;/Documen
-[6348ecdf3dc5e21e] 2024년도_[요약] 24년 데이터기반행정 활성화 추진계획_240504 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-05-04 09:27:45 &lt;/Document-M
-[7397f4cf3cd4bcb4] 2022년도_(붙임4) 2023년 경마분야 지원 R&amp;D 추진계획(최종) #14  ▸  &lt;Document-Metadata&gt;   제목: 시험시행 종합계획   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-27 11:07:39   수정일: 2023-06-17 13:39:57 &lt;/Do
-[750220b64c1d0833] 2022년도_(경마본부) 2022년 핵심과제 추진실적 #4  ▸  &lt;Document-Metadata&gt;   제목: 감사원 지적사항 조치실적   마지막 수정자: KRA   작성일: 2007-12-13 21:52:10   수정일: 2022-12-20 10:42:23 &lt;/Document-
-[790f2015dc65b6e1] 2020년도_(붙임#2) 2020년 인재개발 기본계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 인 사 노 무 처   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-02 10:20:11   수정일: 2020-02-27 16:52:55 &lt;/Do
-[811aee113d51f0a0] 2023년도_(붙임4) 2023년 경마분야 지원 R&amp;D 추진계획(최종) #14  ▸  &lt;Document-Metadata&gt;   제목: 시험시행 종합계획   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-27 11:07:39   수정일: 2023-06-17 13:39:57 &lt;/Do
-[c13ca063e2675d57] 2022년도_1. 경마안정성 강화 대책 수립 계획(안) #5  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-18 19:10:02   수정일: 2023-02-04 17:46:47 &lt;/Documen
-[d91964b859494daf] 2021년도_(붙임3)_2021년도 수입 및 지출 계획서 #14  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2020-12-18 18:13:07 &lt;/Documen</t>
+          <t>1. 2023년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-Metadata&gt;  * 산업형(100% NCS 적용) 채…
+2. 2020년도_(붙임#1) 인재개발 기본계획(안) 요약 #0  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-27 16:38:24 &lt;/Document-Metadata&gt;  2020년 인재개발 기본계획(안…
+3. 2022년도_(본문) 경주마관계자 임시조치 개선계획(안) #34  ▸  &lt;Document-Metadata&gt;   제목: 2022년 교육훈련 기본계획   작성자: KRA   마지막 수정자: KRA   작성일: 2022-03-04 14:47:46   수정일: 2022-11-11 16:14:31 &lt;/Document-Metadata&gt;  Ⅶ. 협조사…
+4. 2022년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-Metadata&gt;  * 산업형(100% NCS 적용) 채…
+5. 2025년도_(붙임3) 2025년 한국마사회 수입 및 지출계획서 #12  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2024-12-19 17:06:39 &lt;/Document-Metadata&gt;  훈), 예산담당사원(강현석)  …
+6. 2024년도_[요약] 24년 데이터기반행정 활성화 추진계획_240504 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-05-04 09:27:45 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+7. 2022년도_(붙임4) 2023년 경마분야 지원 R&amp;D 추진계획(최종) #14  ▸  &lt;Document-Metadata&gt;   제목: 시험시행 종합계획   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-27 11:07:39   수정일: 2023-06-17 13:39:57 &lt;/Document-Metadata&gt;  선정 가능성 체크리스트…
+8. 2022년도_(경마본부) 2022년 핵심과제 추진실적 #4  ▸  &lt;Document-Metadata&gt;   제목: 감사원 지적사항 조치실적   마지막 수정자: KRA   작성일: 2007-12-13 21:52:10   수정일: 2022-12-20 10:42:23 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; …
+9. 2020년도_(붙임#2) 2020년 인재개발 기본계획(안) #8  ▸  &lt;Document-Metadata&gt;   제목: 인 사 노 무 처   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-02 10:20:11   수정일: 2020-02-27 16:52:55 &lt;/Document-Metadata&gt;  &lt;table borde…
+10. 2023년도_(붙임4) 2023년 경마분야 지원 R&amp;D 추진계획(최종) #14  ▸  &lt;Document-Metadata&gt;   제목: 시험시행 종합계획   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-27 11:07:39   수정일: 2023-06-17 13:39:57 &lt;/Document-Metadata&gt;  선정 가능성 체크리스트…
+11. 2022년도_1. 경마안정성 강화 대책 수립 계획(안) #5  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-18 19:10:02   수정일: 2023-02-04 17:46:47 &lt;/Document-Metadata&gt;  (대고객 사과) 1.15(일) …
+12. 2021년도_(붙임3)_2021년도 수입 및 지출 계획서 #14  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2020-12-18 18:13:07 &lt;/Document-Metadata&gt;  재원), 예산담당대리(권오경) …</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -4082,26 +4082,26 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>[0346542e0be2b2ab] 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Documen
-[0370e8a4dce03ce3] 2020년도_경마실황 무선중계시스템 도입 계획(안) #9  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-20 12:54:03   수정일: 2020-08-08 11:33:53 &lt;/Document-Metadata&gt;
-[08712ddb117bedbb] 2023년도_2023 온라인 방송 추진 계획(안)_최종 #12  ▸  &lt;Document-Metadata&gt;   제목: 미래비전의 초석   작성자: KRA   마지막 수정자: KRA   작성일: 2022-05-28 14:52:15   수정일: 2023-07-23 09:58:23 &lt;/Doc
-[123f03df3479517e] 2022년도_[별첨1] KRA-ESG경영 진단모델(세부 진단기준)_최종 #43  ▸  &lt;Document-Metadata&gt;   제목: 《 KRA   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-04 14:33:57   수정일: 2023-05-27 10:21:04 &lt;/Docume
-[133dd2fda4f7c41d] 2024년도_(붙임 1) 제1회 국산마 품평회 개최계획 #18  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-15 17:31:04   수정일: 2024-06-19 17:49:01 &lt;/Documen
-[156fec294ba67ae4] 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-M
-[17a6323f30b615ff] 2024년도_(요약) 보고서(2024년 부경본부 후반기 입장인원 증대계획) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2024-07-24 17:56:30 &lt;/Document-Metadat
-[1e7df0e389317f02] 2024년도_2024년 봄 야간경마 시즌 드라이브 스루 베팅존 운영계획(안) 240225 결재 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:54:36   수정일: 2024-02-25 16:31:26 &lt;/Document-M
-[24fa325d76c7cd8a] 2024년도_2024년 서울경마공원 발매사업 운영계획(안)_최종 #0  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2024-03-22 09:44:13 &lt;/Docume
-[2965f2e46bcfa371] 2024년도_(붙임1) 제주 경마방송 노후 동기 신호 발생기 교체 계획(안)_V2 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-18 09:43:45   수정일: 2024-05-12 16:07:00 &lt;/Document-M
-[2e907c84c2a15612] 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-M
-[30e5c01f74f2a2b2] 2024년도_2024년 발매사업 운영계획(안)_ver3.0 #16  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2024-03-03 16:48:21 &lt;/Docume
-[329af5c7de78350a] 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Documen
-[3899cc22b412106f] 2022년도_(친환경탄소중립) 2022 보고서 작성_환경_5차 워크숍_컨설팅_최종 #40  ▸  &lt;Document-Metadata&gt;   제목: 1. 전략기획 및 사회적책임   마지막 수정자: KRA   작성일: 2015-01-15 14:27:57   수정일: 2023-02-19 14:55:17 &lt;/Documen
-[38bd220368aba4ab] 2023년도_[붙임 1] (요약) 말산업 R&amp;D 중장기 로드맵 구축 연구 #10  ▸  &lt;Document-Metadata&gt;   제목: 사업개요   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-19 15:06:14   수정일: 2024-03-03 16:48:29 &lt;/Documen
-[3d8c8292183997c8] 2023년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
-[3e1e3c7c7c6dbc28] 2024년도_[붙임2] 개정 「내부통제규정」전문 #10  ▸  &lt;Document-Metadata&gt;   제목: 제1장  총칙                                      작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-28 17:38:1
-[3f4afc51b550193f] 2023년도_2. [본문] 2023년 영향평가 시행 계획(안) #15  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2023-05-18 09:24:05 &lt;/Document-Met
-[3fb6428d743036ee] 2022년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
-[419a0013fb52efe2] 2024년도_(요약)'24년 안전보건경영시스템 경영자 검토보고 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-28 16:47:06   수정일: 2024-12-27 09:58:43 &lt;/Document-Metadata&gt;
+          <t>1. 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Document-Metadata&gt;  (단, 사업담당자의 재량으로 지…
+2. 2020년도_경마실황 무선중계시스템 도입 계획(안) #9  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-20 12:54:03   수정일: 2020-08-08 11:33:53 &lt;/Document-Metadata&gt;  나. 계약 방법 : 견적 최저가       LTE …
+3. 2023년도_2023 온라인 방송 추진 계획(안)_최종 #12  ▸  &lt;Document-Metadata&gt;   제목: 미래비전의 초석   작성자: KRA   마지막 수정자: KRA   작성일: 2022-05-28 14:52:15   수정일: 2023-07-23 09:58:23 &lt;/Document-Metadata&gt;  ❍ 내용 : 온라인 발매…
+4. 2022년도_[별첨1] KRA-ESG경영 진단모델(세부 진단기준)_최종 #43  ▸  &lt;Document-Metadata&gt;   제목: 《 KRA   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-04 14:33:57   수정일: 2023-05-27 10:21:04 &lt;/Document-Metadata&gt;  &lt;table border='1…
+5. 2024년도_(붙임 1) 제1회 국산마 품평회 개최계획 #18  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-15 17:31:04   수정일: 2024-06-19 17:49:01 &lt;/Document-Metadata&gt;  소요예산 : 97,200천원  …
+6. 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-Metadata&gt;  (치료) 복지중심 의료서비스 지원 강…
+7. 2024년도_(요약) 보고서(2024년 부경본부 후반기 입장인원 증대계획) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2024-07-24 17:56:30 &lt;/Document-Metadata&gt;  (요약) (부경본부) 2024년 후반기 입장인원…
+8. 2024년도_2024년 봄 야간경마 시즌 드라이브 스루 베팅존 운영계획(안) 240225 결재 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:54:36   수정일: 2024-02-25 16:31:26 &lt;/Document-Metadata&gt;  , 매출액(101백만원)       …
+9. 2024년도_2024년 서울경마공원 발매사업 운영계획(안)_최종 #0  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2024-03-22 09:44:13 &lt;/Document-Metadata&gt;  &lt;table border='1…
+10. 2024년도_(붙임1) 제주 경마방송 노후 동기 신호 발생기 교체 계획(안)_V2 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-18 09:43:45   수정일: 2024-05-12 16:07:00 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+11. 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-Metadata&gt;  □ 추진기간 : 2021. 6월 ∼ …
+12. 2024년도_2024년 발매사업 운영계획(안)_ver3.0 #16  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2024-03-03 16:48:21 &lt;/Document-Metadata&gt;  &lt;table border='1…
+13. 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+14. 2022년도_(친환경탄소중립) 2022 보고서 작성_환경_5차 워크숍_컨설팅_최종 #40  ▸  &lt;Document-Metadata&gt;   제목: 1. 전략기획 및 사회적책임   마지막 수정자: KRA   작성일: 2015-01-15 14:27:57   수정일: 2023-02-19 14:55:17 &lt;/Document-Metadata&gt;  [Image:temp/image…
+15. 2023년도_[붙임 1] (요약) 말산업 R&amp;D 중장기 로드맵 구축 연구 #10  ▸  &lt;Document-Metadata&gt;   제목: 사업개요   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-19 15:06:14   수정일: 2024-03-03 16:48:29 &lt;/Document-Metadata&gt;  === Extracted Ima…
+16. 2023년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-Metadata&gt;  전환에 대비한 시공간 제약 없는 원격…
+17. 2024년도_[붙임2] 개정 「내부통제규정」전문 #10  ▸  &lt;Document-Metadata&gt;   제목: 제1장  총칙                                      작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-28 17:38:15   수정일: 2024-12-14 09:38:18 &lt;…
+18. 2023년도_2. [본문] 2023년 영향평가 시행 계획(안) #15  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2023-05-18 09:24:05 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr…
+19. 2022년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-Metadata&gt;  전환에 대비한 시공간 제약 없는 원격…
+20. 2024년도_(요약)'24년 안전보건경영시스템 경영자 검토보고 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-28 16:47:06   수정일: 2024-12-27 09:58:43 &lt;/Document-Metadata&gt;  5. 향후계획 : 차년도 산업안전보건 계획 수립 시…
 ... +67 more</t>
         </is>
       </c>
@@ -4229,28 +4229,28 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>[030292b5e5db1492] 2023년도_(요약본) 2023년 기록관리 기본계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-03-30 09:55:50 &lt;/Document-M
-[06b38c6a346a2385] 2023년도_2023년 바로마켓 운영 계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2011-01-14 09:36:36   수정일: 2023-02-05 17:18:03 &lt;/Document-M
-[06ea8eb0c6498c61] 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-M
-[0f9e1947b0221b27] 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-M
-[1002c0855b631621] 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document
-[10f09627fe81dec0] 2024년도_2024 마권 용지 및 구매표 구매 계획 요약 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-22 11:16:41 &lt;/Document-M
-[1288cb8b3a80b7a4] 2025년도_[요약] 2025년 학교체육 승마 지원사업 운영계획(안) 241201 #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-12-01 14:34:19 &lt;/Document-M
-[19fa870b8e483f1c] 2024년도_512.기부금관리규정(전문) #31  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
+          <t>1. 2023년도_(요약본) 2023년 기록관리 기본계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-03-30 09:55:50 &lt;/Document-Metadata&gt;  3. 2023년 기본계획 (안)   …
+2. 2023년도_2023년 바로마켓 운영 계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2011-01-14 09:36:36   수정일: 2023-02-05 17:18:03 &lt;/Document-Metadata&gt;  *바로마켓 사용료 산출산식 : 참여농…
+3. 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-Metadata&gt;  가와 사업성과평가 통합    ◦ (차…
+4. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+5. 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt;…
+6. 2024년도_2024 마권 용지 및 구매표 구매 계획 요약 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-22 11:16:41 &lt;/Document-Metadata&gt;  : 현 재고량(4,754 BOX)에 …
+7. 2025년도_[요약] 2025년 학교체육 승마 지원사업 운영계획(안) 241201 #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-12-01 14:34:19 &lt;/Document-Metadata&gt;  전학년 20명 이하의 학교    ❍ …
+8. 2024년도_512.기부금관리규정(전문) #31  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
     설명: 
-    마지막 수정자: KRA   작성일: 2006-03-14 14:40:25   수정일: 2024-12-05 18:
-[1a1522e81a560fbf] 2020년도_(본문)20년 말산업 컨설팅 추진계획(안) #32  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2015-02-08 08:46:52   수정일: 2020-03-25 11:26:26 &lt;/Document-Metadata&gt;
-[1c82399b98aebbba] 2024년도_(양식) 상반기 자본예산 집행실적 #21  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-05 10:21:26   수정일: 2024-06-13 06:23:29 &lt;/Document-Metadata&gt;
-[1d6b0fc02595dbd7] 2020년도_(요약) 2020 한국경마 대국민 인식조사 결과보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-01-28 13:35:00 &lt;/Document-M
-[2170040846621df2] 2020년도_붙임 2.  2020 박람회추진계획(안)(요약) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-27 10:42:10 &lt;/Document-M
-[21a9f52b725a25b7] 2021년도_20210327 2021년 바로마켓 운영 계획(안) 요약보고 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-03-27 17:30:56 &lt;/Document-M
-[23f259fe9f9c25d9] 2020년도_200828_언택트발매추진단 하반기 사업계획 및 예산 #4  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-21 12:13:34   수정일: 2020-08-28 13:15:23 &lt;/Document-M
-[2520e4f72ad580ae] 2022년도_(제23-11호) 인권경영 실행지침 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-04 09:10:19   수정일: 2023-04-23 10:51:13 &lt;/Do
-[257c21115efd0262] 2022년도_2022년도 기관경영평가 재무예산관리 지표 경영실적보고서(수정, 02.18) #96  ▸  &lt;Document-Metadata&gt;   제목: 1. 전략기획 및 사회적책임   마지막 수정자: KRA   작성일: 2015-01-15 14:27:57   수정일: 2023-02-18 17:30:08 &lt;/Documen
-[26804b9bb678ce82] 2020년도_('20.08.06) 공공기관 자회사 운영실태 평가 계획(비대면) #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-08-09 15:07:56 &lt;/Document-M
-[2a3a0e1ad3162f25] 2024년도_(붙임2) '24년 마권용지 및 구매표 구매계획(안)_최종 #24  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2011-03-04 12:47:46   수정일: 2024-02-22 11:20:58 &lt;/Document-M
-[2e907c84c2a15612] 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-M
-[2ffc5467d8f17d86] 2020년도_(본문) 2020년 한국마사회 지식경영 운영계획(안)(200417) #19  ▸  &lt;Document-Metadata&gt;   제목: 2017년 지식경영 운영계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-13 15:38:51   수정일: 2020-04-17 10:22:3
+    마지막 수정자: KRA   작성일: 2006-03-14 14:40:25   수정일: 2024-12-05 18:46:10 &lt;/Document-Metadata&gt;  ※ …
+9. 2020년도_(본문)20년 말산업 컨설팅 추진계획(안) #32  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2015-02-08 08:46:52   수정일: 2020-03-25 11:26:26 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp_BIN00…
+10. 2024년도_(양식) 상반기 자본예산 집행실적 #21  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-05 10:21:26   수정일: 2024-06-13 06:23:29 &lt;/Document-Metadata&gt;  [Sheet: Sheet1] [Table 3] | …
+11. 2020년도_(요약) 2020 한국경마 대국민 인식조사 결과보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-01-28 13:35:00 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+12. 2020년도_붙임 2.  2020 박람회추진계획(안)(요약) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-27 10:42:10 &lt;/Document-Metadata&gt;  □ (융‧복합형) 비즈니스 산업과 엔…
+13. 2021년도_20210327 2021년 바로마켓 운영 계획(안) 요약보고 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-03-27 17:30:56 &lt;/Document-Metadata&gt;  -‘20년도 정상개장(워킹스루) : …
+14. 2020년도_200828_언택트발매추진단 하반기 사업계획 및 예산 #4  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-21 12:13:34   수정일: 2020-08-28 13:15:23 &lt;/Document-Metadata&gt;  및 말산업 생태계 보존     (이용…
+15. 2022년도_(제23-11호) 인권경영 실행지침 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-04 09:10:19   수정일: 2023-04-23 10:51:13 &lt;/Document-Metadata&gt;  동과 아동노동도 허용하…
+16. 2022년도_2022년도 기관경영평가 재무예산관리 지표 경영실적보고서(수정, 02.18) #96  ▸  &lt;Document-Metadata&gt;   제목: 1. 전략기획 및 사회적책임   마지막 수정자: KRA   작성일: 2015-01-15 14:27:57   수정일: 2023-02-18 17:30:08 &lt;/Document-Metadata&gt;  [Image:temp/image…
+17. 2020년도_('20.08.06) 공공기관 자회사 운영실태 평가 계획(비대면) #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-08-09 15:07:56 &lt;/Document-Metadata&gt;  「고용부, 자회사 운영 실태평가 」지…
+18. 2024년도_(붙임2) '24년 마권용지 및 구매표 구매계획(안)_최종 #24  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2011-03-04 12:47:46   수정일: 2024-02-22 11:20:58 &lt;/Document-Metadata&gt;  * 최종 단가는 경쟁입찰 낙찰단가를 …
+19. 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-Metadata&gt;  □ 추진기간 : 2021. 6월 ∼ …
+20. 2020년도_(본문) 2020년 한국마사회 지식경영 운영계획(안)(200417) #19  ▸  &lt;Document-Metadata&gt;   제목: 2017년 지식경영 운영계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-13 15:38:51   수정일: 2020-04-17 10:22:34 &lt;/Document-Metadata&gt;  부서 심사 …
 ... +113 more</t>
         </is>
       </c>
@@ -4424,17 +4424,17 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>[08dbb848822964aa] 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:
-[2b77cb92e3b2e52e] 2020년도_붙임3. 2020년 총 교배횟수(모든교배내역) #144  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:38:42 &lt;/Document-Metadata&gt;
-[43b8261fe9a4b3ca] 2020년도_@ (결재상신) 2020년 경주마 생산 및 교배지원 결과보고 @ #19  ▸  &lt;Document-Metadata&gt;   제목: 2002. 내륙 민간목장 생산 및 교배지원 결과   작성자: 한국마사회 원당목장팀 대리 임진호   키워드: 
+          <t>1. 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:50:21 &lt;/Document-Metadata&gt;  20…
+2. 2020년도_붙임3. 2020년 총 교배횟수(모든교배내역) #144  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:38:42 &lt;/Document-Metadata&gt;  [Sheet: 2020 총 교배횟수] [Table …
+3. 2020년도_@ (결재상신) 2020년 경주마 생산 및 교배지원 결과보고 @ #19  ▸  &lt;Document-Metadata&gt;   제목: 2002. 내륙 민간목장 생산 및 교배지원 결과   작성자: 한국마사회 원당목장팀 대리 임진호   키워드: 
     설명: 
-    마지막 수정자: KRA
-[481cdea45e2aa69d] 2020년도_붙임1. 2020년 경주마 생산실적 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:32:35 &lt;/Document-Metadata&gt;
-[57ae80a2b693d18f] 2020년도_붙임4. 2020년 유상교배 수익내역 #6  ▸  &lt;Document-Metadata&gt;   작성자: user   마지막 수정자: KRA   작성일: 2013-10-13 05:56:53   수정일: 2020-12-11 01:28:30 &lt;/Document-Metadata
-[6cdb3f17c1eafe48] 2020년도_붙임2. 2020년 총 교배실적(두수) #111  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:36:12 &lt;/Document-Metadata&gt;
-[72b1245e55ab96fc] 2021년도_경주마 교배 및 번식분야 복지 가이드라인(안) #17  ▸  &lt;Document-Metadata&gt;   제목: 한국마사회 교배 및 번식 말 복지 가이드라인 초안    작성자: User2007   마지막 수정자: KRA   작성일: 2021-08-07 21:34:58   수정일:
-[bbe40d855e6cc165] 2021년도_경주마 교배 및 번식분야 복지 가이드라인 수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-02 15:44:31 &lt;/Document-M
-[e39b4656a5219700] 2020년도_@ (요약) 2020년 경주마 생산 및 교배지원 결과보고 @ #3  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-12-17 11:13:23 &lt;/Document-Metadat</t>
+    마지막 수정자: KRA   작성일: 2005-08-25 10:09:53   수정…
+4. 2020년도_붙임1. 2020년 경주마 생산실적 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:32:35 &lt;/Document-Metadata&gt;  [Sheet: 2020년 생산내역 (수정)] [Ta…
+5. 2020년도_붙임4. 2020년 유상교배 수익내역 #6  ▸  &lt;Document-Metadata&gt;   작성자: user   마지막 수정자: KRA   작성일: 2013-10-13 05:56:53   수정일: 2020-12-11 01:28:30 &lt;/Document-Metadata&gt;  [Sheet: 작업용] [Table Chunk 7…
+6. 2020년도_붙임2. 2020년 총 교배실적(두수) #111  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-05 06:52:33   수정일: 2020-12-11 01:36:12 &lt;/Document-Metadata&gt;  [Sheet: 2020년 총 교배두수_최종교배기준]…
+7. 2021년도_경주마 교배 및 번식분야 복지 가이드라인(안) #17  ▸  &lt;Document-Metadata&gt;   제목: 한국마사회 교배 및 번식 말 복지 가이드라인 초안    작성자: User2007   마지막 수정자: KRA   작성일: 2021-08-07 21:34:58   수정일: 2021-12-02 11:22:35 &lt;/Document…
+8. 2021년도_경주마 교배 및 번식분야 복지 가이드라인 수립 결과 보고 #0  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-02 15:44:31 &lt;/Document-Metadata&gt;  경주마 교배 및 번식분야 복지 가이드…
+9. 2020년도_@ (요약) 2020년 경주마 생산 및 교배지원 결과보고 @ #3  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-12-17 11:13:23 &lt;/Document-Metadata&gt;  두, 민간 1,485두)      ○ 전체 대비…</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -4483,19 +4483,19 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>[0f9e1947b0221b27] 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-M
-[19fe4e04b9ae46af] 2023년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Met
-[3d8c8292183997c8] 2023년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
-[3fb6428d743036ee] 2022년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-M
-[53036042c659a508] 2024년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-M
-[5b4cfb9e5eb0817f] 2024년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Met
-[7d016a8eb300196a] 2024년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;
-[8c8f02475898d6e9] 2024년도_(요약)스마트 사무환경 고도화 추진 계획 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-21 11:12:09 &lt;/Document-M
-[993ad9a5e29994fc] 2023년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen
-[9d226cce773a4434] 2022년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Documen
-[a869fa35476990c2] 2023년도_서울경마공원 콜센터 설비 이중화 및 망분리 계획(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-09 11:14:17   수정일: 2024-04-06 17:02:38 &lt;/Document-Metadata&gt;
-[afd0f60cc9c978c0] 2022년도_붙임 1. 스마트 사무환경 구축 및 망분리 개선 견적서(총괄) #27  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-02 04:07:54   수정일: 2023-08-17 03:33:36 &lt;/Document-Metadata&gt;
-[e4f72caaf5619284] 2023년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+2. 2023년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp…
+3. 2023년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-Metadata&gt;  전환에 대비한 시공간 제약 없는 원격…
+4. 2022년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-Metadata&gt;  전환에 대비한 시공간 제약 없는 원격…
+5. 2024년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+6. 2024년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp…
+7. 2024년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;  [Sheet: 15년도 이하 소형복합기] [Tabl…
+8. 2024년도_(요약)스마트 사무환경 고도화 추진 계획 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-21 11:12:09 &lt;/Document-Metadata&gt;  최 운영부서 근무자 기준 약 450대…
+9. 2023년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Document-Metadata&gt;  [Image:temp/image…
+10. 2022년도_스마트 사무환경 구축 및 망분리 개선 추진계획(안) V1.0 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-08-18 09:26:47 &lt;/Document-Metadata&gt;  [Image:temp/image…
+11. 2023년도_서울경마공원 콜센터 설비 이중화 및 망분리 계획(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-09 11:14:17   수정일: 2024-04-06 17:02:38 &lt;/Document-Metadata&gt;  □ 예산과목: 노후통신시스템교체(1431040-24…
+12. 2022년도_붙임 1. 스마트 사무환경 구축 및 망분리 개선 견적서(총괄) #27  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-02 04:07:54   수정일: 2023-08-17 03:33:36 &lt;/Document-Metadata&gt;  [Sheet: 3.2 SSD] [Image:temp…
+13. 2023년도_붙임3.2024년도 교체대상 정보화기기 #13  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-05-26 04:02:11   수정일: 2024-05-26 04:49:07 &lt;/Document-Metadata&gt;  [Sheet: 15년도 이하 소형복합기] [Tabl…</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -4548,28 +4548,28 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>[012dcbe84f52c595] 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Me
-[05dbe5ea6c8d03fe] 2024년도_(붙임3) 2024년 제주방송 프로그램 연간 제작계획 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-02-02 04:18:57   수정일: 2024-01-26 05:46:09 &lt;/Document-Metadata&gt;
-[0787b40b4734cb4b] 2023년도_[붙임2] (본문) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #9  ▸  &lt;Document-Metadata&gt;   제목: 2019   작성자: KRA   마지막 수정자: KRA   작성일: 2019-07-24 15:06:06   수정일: 2024-05-25 09:18:53 &lt;/Documen
-[110f8ff7eb5dbdc1] 2022년도_첨부1_2022년 한국 대상경주 레이스 레이팅 총괄(연말최종) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-12-28 05:32:05   수정일: 2022-12-16 01:40:34 &lt;/Document-Metadata&gt;
-[134ceaf0ae1ba751] 2023년도_(요약) 23년 국제경주(코리아컵 코리아스프린트) 시행계획 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-04-28 10:50:47 &lt;/Document-M
-[22bf2d7e00a0f6d9] 2024년도_2024년 시리즈 경주 시행 결과보고 #25  ▸  &lt;Document-Metadata&gt;   제목: 대상경주 시리즈 선발체계 홍보   작성자: KRA   마지막 수정자: KRA   작성일: 2024-12-12 09:56:21   수정일: 2024-12-13 18:21:
-[2df376eb9253a430] 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Me
-[33640ab36a7a2b8c] 2024년도_2024년 제 2차 KPC 개최 심의 안건 #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-18 12:53:46 &lt;/Document-Metadata&gt;
-[517703ddbb49e0f6] 2024년도_붙임  (요약)야간경마 행사 추진계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-11 16:38:58 &lt;/Document-M
-[5d259d9a09f37c29] 2024년도_[붙임2] (본문) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #9  ▸  &lt;Document-Metadata&gt;   제목: 2019   작성자: KRA   마지막 수정자: KRA   작성일: 2019-07-24 15:06:06   수정일: 2024-05-25 09:18:53 &lt;/Documen
-[606afb85836eff9c] 2024년도_붙임2) (경주분류위원회)부의안건 #17  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-28 09:41:41 &lt;/Document-Metadata&gt;
-[6f3bfd6f2d2b9b04] 2022년도_(211230)2022_제주경마계획_책자원고(최종수정) #141  ▸  &lt;Document-Metadata&gt;   제목: Ⅱ. 경마 시행 개요   키워드: 
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2024년도_(붙임3) 2024년 제주방송 프로그램 연간 제작계획 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-02-02 04:18:57   수정일: 2024-01-26 05:46:09 &lt;/Document-Metadata&gt;  [Sheet: Sheet1] [Table Chunk…
+3. 2023년도_[붙임2] (본문) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #9  ▸  &lt;Document-Metadata&gt;   제목: 2019   작성자: KRA   마지막 수정자: KRA   작성일: 2019-07-24 15:06:06   수정일: 2024-05-25 09:18:53 &lt;/Document-Metadata&gt;  === Extracted Ima…
+4. 2022년도_첨부1_2022년 한국 대상경주 레이스 레이팅 총괄(연말최종) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-12-28 05:32:05   수정일: 2022-12-16 01:40:34 &lt;/Document-Metadata&gt;  [Sheet: Sheet1] [Table Chunk…
+5. 2023년도_(요약) 23년 국제경주(코리아컵 코리아스프린트) 시행계획 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-04-28 10:50:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+6. 2024년도_2024년 시리즈 경주 시행 결과보고 #25  ▸  &lt;Document-Metadata&gt;   제목: 대상경주 시리즈 선발체계 홍보   작성자: KRA   마지막 수정자: KRA   작성일: 2024-12-12 09:56:21   수정일: 2024-12-13 18:21:21 &lt;/Document-Metadata&gt;  === E…
+7. 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+8. 2024년도_2024년 제 2차 KPC 개최 심의 안건 #18  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-18 12:53:46 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+9. 2024년도_붙임  (요약)야간경마 행사 추진계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-11 16:38:58 &lt;/Document-Metadata&gt;  문인증 이벤트 등 축제 방문객 경마참…
+10. 2024년도_[붙임2] (본문) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #9  ▸  &lt;Document-Metadata&gt;   제목: 2019   작성자: KRA   마지막 수정자: KRA   작성일: 2019-07-24 15:06:06   수정일: 2024-05-25 09:18:53 &lt;/Document-Metadata&gt;  === Extracted Ima…
+11. 2024년도_붙임2) (경주분류위원회)부의안건 #17  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-18 09:16:43   수정일: 2024-12-28 09:41:41 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+12. 2022년도_(211230)2022_제주경마계획_책자원고(최종수정) #141  ▸  &lt;Document-Metadata&gt;   제목: Ⅱ. 경마 시행 개요   키워드: 
     설명: 
-    마지막 수정자: KRA   작성일: 2005-01-06 17:05:55   수정일: 2021-12-
-[788bbf4ba82b5320] 2022년도_첨부2_2022년 대상경주별 레이스 레이팅 세부 현황(연말 최종) #37  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-14 00:44:46   수정일: 2022-12-16 01:40:17 &lt;/Document-Me
-[83680adc07f09d42] 2022년도_연말연시 대고객 무료입장 행사 시행 결과보고 #7  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-26 11:21:25   수정일: 2022-12-23 09:30:05 &lt;/Document-M
-[929899bce4b8ff3e] 2023년도_첨부2_2023년 대상경주별 레이스 레이팅 세부 현황(연말 최종) #37  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-22 01:15:23   수정일: 2023-12-28 05:16:45 &lt;/Document-Me
-[9e0b5f9c2ae462c6] 2023년도_1등급 경주마 레이팅 현실화_최종 #15  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: user   마지막 수정자: KRA   작성일: 2018-04-17 13:51:47   수정일: 2023-11-26 14:39:29 &lt;/Document-
-[b0fc75f5da7a1c86] 2024년도_(붙임1) 2024년 제주경마방송 운영 계획(안)_요약 (최종) #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-07 09:19:14 &lt;/Document-M
-[b693b284424819ba] 2023년도_붙임_2023년 대상경주 레이스 레이팅 부여결과 보고 #11  ▸  &lt;Document-Metadata&gt;   제목: 2016년 주요 대상경주 Race Rating 부여결과 보고   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-06 09:42:57   수정일:
-[b990e68b5d5d78da] 2023년도_[붙임1] (요약) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2023-11-03 09:16:57   수정일: 2024-05-24 19:48:59 &lt;/Document-M
-[be51e42247813522] 2022년도_시리즈 경주 시행 결과보고 #25  ▸  &lt;Document-Metadata&gt;   제목: 2021년 시리즈 경주 시행 결과보고   작성자: KRA   마지막 수정자: KRA   작성일: 2021-12-15 13:12:50   수정일: 2022-12-17 11
+    마지막 수정자: KRA   작성일: 2005-01-06 17:05:55   수정일: 2021-12-30 13:58:40 &lt;/Document-Metadat…
+13. 2022년도_첨부2_2022년 대상경주별 레이스 레이팅 세부 현황(연말 최종) #37  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-14 00:44:46   수정일: 2022-12-16 01:40:17 &lt;/Document-Metadata&gt;  [Sheet: 대상특별 레이스 레이팅]…
+14. 2022년도_연말연시 대고객 무료입장 행사 시행 결과보고 #7  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-26 11:21:25   수정일: 2022-12-23 09:30:05 &lt;/Document-Metadata&gt;  * 대조군 : 무료입장 시행일 전·후…
+15. 2023년도_첨부2_2023년 대상경주별 레이스 레이팅 세부 현황(연말 최종) #37  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-22 01:15:23   수정일: 2023-12-28 05:16:45 &lt;/Document-Metadata&gt;  [Sheet: 대상특별 레이스 레이팅]…
+16. 2023년도_1등급 경주마 레이팅 현실화_최종 #15  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: user   마지막 수정자: KRA   작성일: 2018-04-17 13:51:47   수정일: 2023-11-26 14:39:29 &lt;/Document-Metadata&gt;  - 서울은 “라온더파이터”, 부경은…
+17. 2024년도_(붙임1) 2024년 제주경마방송 운영 계획(안)_요약 (최종) #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-07 09:19:14 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+18. 2023년도_붙임_2023년 대상경주 레이스 레이팅 부여결과 보고 #11  ▸  &lt;Document-Metadata&gt;   제목: 2016년 주요 대상경주 Race Rating 부여결과 보고   작성자: KRA   마지막 수정자: KRA   작성일: 2017-01-06 09:42:57   수정일: 2023-12-28 14:16:06 &lt;/Document…
+19. 2023년도_[붙임1] (요약) 대상경주 우승 기수 「시상대 검량」 추진 계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2023-11-03 09:16:57   수정일: 2024-05-24 19:48:59 &lt;/Document-Metadata&gt;  * 출장로 및 마도를 통한 우승마 대…
+20. 2022년도_시리즈 경주 시행 결과보고 #25  ▸  &lt;Document-Metadata&gt;   제목: 2021년 시리즈 경주 시행 결과보고   작성자: KRA   마지막 수정자: KRA   작성일: 2021-12-15 13:12:50   수정일: 2022-12-17 11:36:04 &lt;/Document-Metadata&gt;  […
 ... +8 more</t>
         </is>
       </c>
@@ -4638,10 +4638,10 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>[59854a9e60c7d3ab] 2022년도_(붙임2)재물조사결과내역(전체) #106  ▸  &lt;Document-Metadata&gt;   작성자: KA B &lt;/Document-Metadata&gt;  [Sheet: 전체] [Table Chunk 107/107] | 자산번호 | SAP자산번호 | 자산구분 | 세분류 |
-[6a278de5a7f63982] 2022년도_(붙임1)2022년 정기 재물조사 실시 결과보고 #9  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-23 10:36:27   수정일: 2023-01-19 14:22:42 &lt;/Documen
-[95765c577ef9e336] 2024년도_(붙임1) 2024년 재물조사 시행 결과보고_241227 #15  ▸  &lt;Document-Metadata&gt;   제목: 재물조정   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-12 16:02:40   수정일: 2024-12-27 09:49:24 &lt;/Documen
-[c8ed7811592eac64] 2022년도_(붙임2)재물조사결과내역(전체) #393  ▸  &lt;Document-Metadata&gt;   작성일: 2025-12-05 08:14:00   수정일: 2025-12-05 08:14:00 &lt;/Document-Metadata&gt;  [Page Number: 394]  &lt;tab</t>
+          <t>1. 2022년도_(붙임2)재물조사결과내역(전체) #106  ▸  &lt;Document-Metadata&gt;   작성자: KA B &lt;/Document-Metadata&gt;  [Sheet: 전체] [Table Chunk 107/107] | 자산번호 | SAP자산번호 | 자산구분 | 세분류 | 본부명 | 자산내역 | 취득일자 | 구매금액 | 단가 …
+2. 2022년도_(붙임1)2022년 정기 재물조사 실시 결과보고 #9  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-23 10:36:27   수정일: 2023-01-19 14:22:42 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+3. 2024년도_(붙임1) 2024년 재물조사 시행 결과보고_241227 #15  ▸  &lt;Document-Metadata&gt;   제목: 재물조정   작성자: KRA   마지막 수정자: KRA   작성일: 2024-04-12 16:02:40   수정일: 2024-12-27 09:49:24 &lt;/Document-Metadata&gt;  전 부서    ❍ 조직개편, 인…
+4. 2022년도_(붙임2)재물조사결과내역(전체) #393  ▸  &lt;Document-Metadata&gt;   작성일: 2025-12-05 08:14:00   수정일: 2025-12-05 08:14:00 &lt;/Document-Metadata&gt;  [Page Number: 394]  &lt;table&gt;   &lt;tr&gt;     &lt;th&gt;20220842911…</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -4685,8 +4685,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>[8390d154aeb39727] 2022년도_붙임 3. 예산전용 세부내역 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-13 05:10:41   수정일: 2023-08-18 04:08:23 &lt;/Document-Metadata&gt;
-[e9e64a316174aed5] 2022년도_[붙임]출전준비소 바닥면 탄성포장 추진안 #1  ▸  &lt;Document-Metadata&gt;   제목: 조명탑 및 감시카메라    작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-26 15:45:00   수정일: 2022-10-15 15:21:52 &lt;</t>
+          <t>1. 2022년도_붙임 3. 예산전용 세부내역 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-08-13 05:10:41   수정일: 2023-08-18 04:08:23 &lt;/Document-Metadata&gt;  [Sheet: 2. 예산산출내역] &lt;table bo…
+2. 2022년도_[붙임]출전준비소 바닥면 탄성포장 추진안 #1  ▸  &lt;Document-Metadata&gt;   제목: 조명탑 및 감시카메라    작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-26 15:45:00   수정일: 2022-10-15 15:21:52 &lt;/Document-Metadata&gt;  2. 바닥 현황 …</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>[17bd81589a0131cf] 2024년도_[붙임2] (제24-63호) 직제규정시행세칙 일부 개정(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-15 13:06:07   수정일: 2024-12-13 17:50:27 &lt;/Document-M
-[27dcbb61e82d6f82] 2024년도_과제 및 사업별 담당부서 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-08 02:27:01   수정일: 2024-06-13 05:02:20 &lt;/Document-Metadata&gt;
-[4fbf4a8a7bd53b63] 2023년도_(붙임) D-공원레저 및 지역상생(230222) #50  ▸  &lt;Document-Metadata&gt;   제목: 3   작성자: KRA   마지막 수정자: KRA   작성일: 2021-11-28 15:41:36   수정일: 2023-02-22 14:37:47 &lt;/Document-M
-[a4ed66c59a820e40] 2020년도_(붙임#14) 사업별 조직별 예산 계층구조 #78  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-11 08:44:57   수정일: 2020-03-13 01:24:08 &lt;/Document-Metadata&gt;
-[aa6aff98e2caa723] 2023년도_[붙임2] 2024년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-14 07:46:48   수정일: 2024-01-31 07:29:46 &lt;/Document-Metadata&gt;
-[da8efb3618249a33] 2022년도_[붙임2] 2023년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-15 02:28:16   수정일: 2023-02-16 04:38:18 &lt;/Document-Metadata&gt;</t>
+          <t>1. 2024년도_[붙임2] (제24-63호) 직제규정시행세칙 일부 개정(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-15 13:06:07   수정일: 2024-12-13 17:50:27 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+2. 2024년도_과제 및 사업별 담당부서 #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-08 02:27:01   수정일: 2024-06-13 05:02:20 &lt;/Document-Metadata&gt;  [Sheet: 과제 및 사업별 담당] [Table …
+3. 2023년도_(붙임) D-공원레저 및 지역상생(230222) #50  ▸  &lt;Document-Metadata&gt;   제목: 3   작성자: KRA   마지막 수정자: KRA   작성일: 2021-11-28 15:41:36   수정일: 2023-02-22 14:37:47 &lt;/Document-Metadata&gt;  [Image:temp/images/h…
+4. 2020년도_(붙임#14) 사업별 조직별 예산 계층구조 #78  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-11 08:44:57   수정일: 2020-03-13 01:24:08 &lt;/Document-Metadata&gt;  [Sheet: 사업별 예산 계층구조] [Table …
+5. 2023년도_[붙임2] 2024년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-14 07:46:48   수정일: 2024-01-31 07:29:46 &lt;/Document-Metadata&gt;  [Sheet: 조직별 예산 계층구조] [Table …
+6. 2022년도_[붙임2] 2023년 사업별 조직별 예산 계층구조 #160  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-15 02:28:16   수정일: 2023-02-16 04:38:18 &lt;/Document-Metadata&gt;  [Sheet: 조직별 예산 계층구조] [Table …</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -4779,25 +4779,25 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>[012dcbe84f52c595] 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Me
-[0cc573d6922d1cfd] 2024년도_★ 2024년 공정관리 업무추진 계획(안) #5  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-03 15:15:28 &lt;/Document-M
-[157016074626f25d] 2021년도_(별첨1) 연도별 마주 경제적기준(2007_2021) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-20 01:23:19   수정일: 2021-11-26 04:01:22 &lt;/Document-Metadata&gt;
-[1ff851c7c3ee9eb5] 2021년도_(2021) 제 99주년 경마의 날 기념식 시행계획(안)_요약보고 #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2021-05-08 14:10:03 &lt;/Document-Metadat
-[2df376eb9253a430] 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Me
-[5cf871e3bcad9e3b] 2025년도_(붙임3) 2025년 한국마사회 수입 및 지출계획서 #12  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2024-12-19 17:06:39 &lt;/Documen
-[6e8edf545decf5bf] 2021년도_(붙임1) 2021년 더러브렛 마주 운영 개선(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 2021년 마주제도 개선 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-11 15:25:28   수정일: 2021-11-28 09:56:
-[7744ef805224b82a] 2022년도_(제23-14호) 더러브렛등록규정 시행세칙 일부 개정(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2020-05-24 10:48:12   수정일: 2023-04-21 16:37:04 &lt;/Do
-[864c7ea3086114e0] 2021년도_(제21-31호) 경마비위 신고포상금 지급규정 개정_결재(최종)★ #1  ▸  &lt;Document-Metadata&gt;   제목: 임원 징계 규정 제정   작성자: sinyoungpark   마지막 수정자: KRA   작성일: 2020-07-14 15:57:47   수정일: 2021-07-23 17
-[bd4e6e178c18810b] 2022년도_경마시행규정 시행세칙 등 개정(안) #37  ▸  &lt;Document-Metadata&gt;   제목: kjhll   키워드: 
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2024년도_★ 2024년 공정관리 업무추진 계획(안) #5  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-03 15:15:28 &lt;/Document-Metadata&gt;  등 사전예방활동으로 경마공정성 강화 …
+3. 2021년도_(별첨1) 연도별 마주 경제적기준(2007_2021) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-20 01:23:19   수정일: 2021-11-26 04:01:22 &lt;/Document-Metadata&gt;  [Sheet: 정리본] [Table Chunk 7/…
+4. 2021년도_(2021) 제 99주년 경마의 날 기념식 시행계획(안)_요약보고 #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2021-05-08 14:10:03 &lt;/Document-Metadata&gt;  제 99주년 경마의 날 기념식 시행 (안) 보고…
+5. 2023년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #167  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2023-12-28 04:23:52   수정일: 2023-12-28 04:35:56 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+6. 2025년도_(붙임3) 2025년 한국마사회 수입 및 지출계획서 #12  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2024-12-19 17:06:39 &lt;/Document-Metadata&gt;  훈), 예산담당사원(강현석)  …
+7. 2021년도_(붙임1) 2021년 더러브렛 마주 운영 개선(안) #11  ▸  &lt;Document-Metadata&gt;   제목: 2021년 마주제도 개선 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-11 15:25:28   수정일: 2021-11-28 09:56:00 &lt;/Document-Metadata&gt;  0대 이상…
+8. 2022년도_(제23-14호) 더러브렛등록규정 시행세칙 일부 개정(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2020-05-24 10:48:12   수정일: 2023-04-21 16:37:04 &lt;/Document-Metadata&gt;  &lt;table borde…
+9. 2021년도_(제21-31호) 경마비위 신고포상금 지급규정 개정_결재(최종)★ #1  ▸  &lt;Document-Metadata&gt;   제목: 임원 징계 규정 제정   작성자: sinyoungpark   마지막 수정자: KRA   작성일: 2020-07-14 15:57:47   수정일: 2021-07-23 17:57:06 &lt;/Document-Metadata&gt;  &lt;…
+10. 2022년도_경마시행규정 시행세칙 등 개정(안) #37  ▸  &lt;Document-Metadata&gt;   제목: kjhll   키워드: 
     설명: 
-    마지막 수정자: KRA   작성일: 2006-01-20 14:28:49   수정일: 2023-02-25 17:
-[c142c30f937d4868] 2020년도_[붙임1] (요약) 2020년 K-Nicks를 활용한 국내산마 미국 수출 지원계획(안) #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-04-13 11:03:16   수정일: 2020-06-04 16:21:38 &lt;/Document-Metadata&gt;
-[c1ebd6c13900514d] 2021년도_(붙임2) 경주퇴역마 복지 가이드라인(최종안) #3  ▸  &lt;Document-Metadata&gt;   제목: 경주퇴역마 가이드라인 제정 관련   작성자: KRA   마지막 수정자: KRA   작성일: 2021-08-13 09:51:05   수정일: 2021-12-04 10:33
-[d91964b859494daf] 2021년도_(붙임3)_2021년도 수입 및 지출 계획서 #14  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2020-12-18 18:13:07 &lt;/Documen
-[da80398d5e7b1d5b] 2021년도_2020 한국경마 대국민 인식조사 설문지 #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-02-26 15:05:29   수정일: 2021-02-26 15:06:19 &lt;/Document-Metadata&gt;
-[de08827cf2920b82] 2024년도_(요약) 2024년 서울경마공원 경주마 재활지원 프로그램 운영계획 #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-23 17:05:09 &lt;/Document-M
-[f960b0c32b20eee5] 2024년도_(요약) 2024년 서울경마공원 경주마 재활지원 프로그램 운영계획 #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-23 17:05:09 &lt;/Document-M
-[fe8f39c7158239fe] 2023년도_2023 가을승마주간 시행 기본계획(안) #20  ▸  &lt;Document-Metadata&gt;   제목: 서울 경마공원에서    작성자: KRA   마지막 수정자: KRA   작성일: 2023-10-06 08:45:07   수정일: 2023-10-14 18:38:53 &lt;/D</t>
+    마지막 수정자: KRA   작성일: 2006-01-20 14:28:49   수정일: 2023-02-25 17:22:06 &lt;/Document-Metadata&gt;  &lt;t…
+11. 2020년도_[붙임1] (요약) 2020년 K-Nicks를 활용한 국내산마 미국 수출 지원계획(안) #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-04-13 11:03:16   수정일: 2020-06-04 16:21:38 &lt;/Document-Metadata&gt;  농가 홍보    말등록원 : 수출시 수출증명서 발행…
+12. 2021년도_(붙임2) 경주퇴역마 복지 가이드라인(최종안) #3  ▸  &lt;Document-Metadata&gt;   제목: 경주퇴역마 가이드라인 제정 관련   작성자: KRA   마지막 수정자: KRA   작성일: 2021-08-13 09:51:05   수정일: 2021-12-04 10:33:13 &lt;/Document-Metadata&gt;  라. 말…
+13. 2021년도_(붙임3)_2021년도 수입 및 지출 계획서 #14  ▸  &lt;Document-Metadata&gt;   제목: 2018   작성자: KRA   마지막 수정자: KRA   작성일: 2018-12-08 16:36:27   수정일: 2020-12-18 18:13:07 &lt;/Document-Metadata&gt;  재원), 예산담당대리(권오경) …
+14. 2021년도_2020 한국경마 대국민 인식조사 설문지 #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-02-26 15:05:29   수정일: 2021-02-26 15:06:19 &lt;/Document-Metadata&gt;  의 결혼상태는 어떻습니까?   	ཧĀ	1. 미혼  …
+15. 2024년도_(요약) 2024년 서울경마공원 경주마 재활지원 프로그램 운영계획 #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-23 17:05:09 &lt;/Document-Metadata&gt;  서울경마공원  2024년 경주마 재활…
+16. 2024년도_(요약) 2024년 서울경마공원 경주마 재활지원 프로그램 운영계획 #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-03-23 17:05:09 &lt;/Document-Metadata&gt;  서울경마공원  2024년 경주마 재활…
+17. 2023년도_2023 가을승마주간 시행 기본계획(안) #20  ▸  &lt;Document-Metadata&gt;   제목: 서울 경마공원에서    작성자: KRA   마지막 수정자: KRA   작성일: 2023-10-06 08:45:07   수정일: 2023-10-14 18:38:53 &lt;/Document-Metadata&gt;  &lt;table bord…</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -4854,18 +4854,18 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>[23f259fe9f9c25d9] 2020년도_200828_언택트발매추진단 하반기 사업계획 및 예산 #4  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-21 12:13:34   수정일: 2020-08-28 13:15:23 &lt;/Document-M
-[24413d0baba3f505] 2020년도_(붙임)'20 이용자보호 현업과제 운영계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제도 확산   작성자: KRA   마지막 수정자: KRA   작성일: 2020-06-12 15:43:26   수정일: 2020-07-25 17:48:38 &lt;/Docume
-[3b6b26357ad2ce21] 2020년도_(요약) 2020년 이용자보호 추진계획 보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-21 13:18:29 &lt;/Document-M
-[594cc15f51062da3] 2023년도_[붙임] 2023년 ESG경영 추진계획(안)_최종 #37  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-05-27 10:36:47 &lt;/Document-Metadata&gt;
-[5d0dd8502b5a0cb8] 2020년도_(본문) 20년 이용자보호 액션플랜 수립계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 제목    작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-16 09:57:57   수정일: 2020-02-09 15:46:56 &lt;/Document
-[853bed249201f55c] 2020년도_[붙임1](요약)온라인 고도화 및 미래대응체계구축 기본계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-15 09:26:37   수정일: 2020-03-28 14:50:47 &lt;/Documen
-[93494a02861846af] 2023년도_붙임_2023년 사감위 건전화평가 관리계획(안)_230617_결재 #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-08 17:12:29   수정일: 2023-06-17 15:12:03 &lt;/Document-Metadata&gt;
-[957fa34075bbf580] 2021년도_(요약) `21년경마 건전화 추진 계획(안) #4  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2021-07-23 14:
-[9c30b7128e4e1947] 2020년도_(별첨) 참고_과제별중장기실행계획('19년) #0  ▸  &lt;Document-Metadata&gt;   제목: □ 과제개요   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-09 14:11:10   수정일: 2020-02-09 14:46:38 &lt;/Docum
-[c1967d59910a20e6] 2021년도_(본문) `21년 경마 건전화 추진 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2015-11-06 10:21:54   수정일: 2021-07-23 14:20:18 &lt;/Document-Metadata&gt;
-[cc2b1d26273fcdab] 2024년도_붙임_2024년 사행산업사업자 건전화평가 관리계획(안)_240518_결재 #24  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-08 17:12:29   수정일: 2024-05-18 17:43:16 &lt;/Document-Metadata&gt;
-[d4d20ca93dfcd728] 2020년도_(본문) 2020년 이용자보호 추진계획 #15  ▸  &lt;Document-Metadata&gt;   제목: 회의자료    작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-19 16:10:55   수정일: 2020-03-21 10:39:32 &lt;/Docume</t>
+          <t>1. 2020년도_200828_언택트발매추진단 하반기 사업계획 및 예산 #4  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-21 12:13:34   수정일: 2020-08-28 13:15:23 &lt;/Document-Metadata&gt;  및 말산업 생태계 보존     (이용…
+2. 2020년도_(붙임)'20 이용자보호 현업과제 운영계획 #7  ▸  &lt;Document-Metadata&gt;   제목: 제도 확산   작성자: KRA   마지막 수정자: KRA   작성일: 2020-06-12 15:43:26   수정일: 2020-07-25 17:48:38 &lt;/Document-Metadata&gt;  가. 추진절차  &lt;table …
+3. 2020년도_(요약) 2020년 이용자보호 추진계획 보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-03-21 13:18:29 &lt;/Document-Metadata&gt;  * 세부 추진계획은 과제별로 별도 수…
+4. 2023년도_[붙임] 2023년 ESG경영 추진계획(안)_최종 #37  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-01-28 11:07:34   수정일: 2023-05-27 10:36:47 &lt;/Document-Metadata&gt;  * ESG 추진과제 관련 현안 발생 시 별도 보고 …
+5. 2020년도_(본문) 20년 이용자보호 액션플랜 수립계획(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 제목    작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-16 09:57:57   수정일: 2020-02-09 15:46:56 &lt;/Document-Metadata&gt;  [Image:temp/images…
+6. 2020년도_[붙임1](요약)온라인 고도화 및 미래대응체계구축 기본계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 보고자    작성자: KRA   마지막 수정자: KRA   작성일: 2020-03-15 09:26:37   수정일: 2020-03-28 14:50:47 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+7. 2023년도_붙임_2023년 사감위 건전화평가 관리계획(안)_230617_결재 #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-08 17:12:29   수정일: 2023-06-17 15:12:03 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+8. 2021년도_(요약) `21년경마 건전화 추진 계획(안) #4  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2021-07-23 14:20:55 &lt;/Document-Metadata&gt;  보안…
+9. 2020년도_(별첨) 참고_과제별중장기실행계획('19년) #0  ▸  &lt;Document-Metadata&gt;   제목: □ 과제개요   작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-09 14:11:10   수정일: 2020-02-09 14:46:38 &lt;/Document-Metadata&gt;  &lt;table border='…
+10. 2021년도_(본문) `21년 경마 건전화 추진 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2015-11-06 10:21:54   수정일: 2021-07-23 14:20:18 &lt;/Document-Metadata&gt;  * `21년 건전화 평가 편람 개요 : 4개 부문,…
+11. 2024년도_붙임_2024년 사행산업사업자 건전화평가 관리계획(안)_240518_결재 #24  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-06-08 17:12:29   수정일: 2024-05-18 17:43:16 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+12. 2020년도_(본문) 2020년 이용자보호 추진계획 #15  ▸  &lt;Document-Metadata&gt;   제목: 회의자료    작성자: KRA   마지막 수정자: KRA   작성일: 2020-02-19 16:10:55   수정일: 2020-03-21 10:39:32 &lt;/Document-Metadata&gt;  (고객보호부) 과제 총괄 관리…</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -4917,30 +4917,30 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>[03e46e426c5e0a40] 2022년도_(붙임1) 인사규정시행세칙 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:10:39 &lt;/Document-Metadata&gt;
-[0fdd2b845b06532f] 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-M
-[1002c0855b631621] 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document
-[2520e4f72ad580ae] 2022년도_(제23-11호) 인권경영 실행지침 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-04 09:10:19   수정일: 2023-04-23 10:51:13 &lt;/Do
-[27e3f288a3dda838] 2024년도_지사, 문화센터 홈페이지 개편 계획(안)_240526(수정) #11  ▸  &lt;Document-Metadata&gt;   제목: □ 통합신고센터 운영개선을 통해 불법경마 신고접수 전문인력 양성   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-24 13:51:43   수정일
-[320953785300baf0] 2023년도_(붙임4) 위촉직관리지침 일부 개정(안) #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:09 &lt;/Document-Metadata&gt;
-[329af5c7de78350a] 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Documen
-[3a729c75753c7cf2] 2024년도_붙임1. 인권경영위원회 회의자료 #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-10-13 14:35:36   수정일: 2024-11-27 13:38:05 &lt;/Document-Metadata&gt;
-[3b38d7e7d3da74e2] 2024년도_(요약) 2024년 인권경영 기본계획(안)  ▸  2024년도_(요약) 2024년 인권경영 기본계획(안)
-[455c41ea7d950aff] 2020년도_불법경마사이트 신고 활성화를 위한 고객신고 제도 분석 및 운영 개선(안) #9  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-04 16:43:55   수정일: 2020-01-19 13:58:22 &lt;/Document-M
-[475035a5d7c43233] 2023년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;
-[499f2103edc5d6e1] 2021년도_(본문) 2021년 인권경영 기본계획 #30  ▸  &lt;Document-Metadata&gt;   제목: 2021년도 인권경영 추진계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-05-14 10:44:55   수정일: 2021-05-29 15:39:
-[4cab49368cf80ad5] 2023년도_(결재) 2023년 인권경영 기본계획(최종) #1  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2023-04-13 17:11:11 &lt;/Documen
-[4e67027b23247ea7] 2022년도_[붙임] 「불법경마 신고포상금 지급 등에 관한 규정」 일부 개정안 #0  ▸  &lt;Document-Metadata&gt;   제목: 경주정보 불법 송출   작성자: KRA   마지막 수정자: KRA   작성일: 2022-07-09 19:23:20   수정일: 2022-12-04 15:24:16 &lt;/D
-[55ab962e1bccc09b] 2022년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;
-[6c8917aa77bbade5] 2021년도_(요약) 2021년 인권경영 기본계획 #8  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2021-05-29 15:
-[7137b1d9495ea540] 2024년도_붙임1. 인권경영실행지침 일부 개정(안)_수정(241012) #15  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2023-11-01 14:09:00   수정일: 2024-10-12 16:56:29 &lt;/Document-M
-[722ac78a66cc46c2] 2024년도_[붙임1] 601. 취업규칙 전문(20241214)-제36차 개정 #34  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
+          <t>1. 2022년도_(붙임1) 인사규정시행세칙 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:10:39 &lt;/Document-Metadata&gt;  ※ 작성방법 : 점검결과에 ‘적정’ 또는 ‘부적정’…
+2. 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-Metadata&gt;  6) 추진일정    - 프로그램별 세…
+3. 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt;…
+4. 2022년도_(제23-11호) 인권경영 실행지침 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-04 09:10:19   수정일: 2023-04-23 10:51:13 &lt;/Document-Metadata&gt;  동과 아동노동도 허용하…
+5. 2024년도_지사, 문화센터 홈페이지 개편 계획(안)_240526(수정) #11  ▸  &lt;Document-Metadata&gt;   제목: □ 통합신고센터 운영개선을 통해 불법경마 신고접수 전문인력 양성   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-24 13:51:43   수정일: 2024-05-26 09:42:09 &lt;/Docume…
+6. 2023년도_(붙임4) 위촉직관리지침 일부 개정(안) #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:09 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+7. 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+8. 2024년도_붙임1. 인권경영위원회 회의자료 #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-10-13 14:35:36   수정일: 2024-11-27 13:38:05 &lt;/Document-Metadata&gt;  ○ 교육, 강습 및 기타사업 분야  &lt;table b…
+9. 2024년도_(요약) 2024년 인권경영 기본계획(안)  ▸  2024년도_(요약) 2024년 인권경영 기본계획(안)
+10. 2020년도_불법경마사이트 신고 활성화를 위한 고객신고 제도 분석 및 운영 개선(안) #9  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-04 16:43:55   수정일: 2020-01-19 13:58:22 &lt;/Document-Metadata&gt;  시 (2분기)     ※ 불법경마 대…
+11. 2023년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;  년    월    일   &lt;table border=…
+12. 2021년도_(본문) 2021년 인권경영 기본계획 #30  ▸  &lt;Document-Metadata&gt;   제목: 2021년도 인권경영 추진계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-05-14 10:44:55   수정일: 2021-05-29 15:39:40 &lt;/Document-Metadata&gt;  === E…
+13. 2023년도_(결재) 2023년 인권경영 기본계획(최종) #1  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2023-04-13 17:11:11 &lt;/Document-Metadata&gt;  8.)        * 경영평가…
+14. 2022년도_[붙임] 「불법경마 신고포상금 지급 등에 관한 규정」 일부 개정안 #0  ▸  &lt;Document-Metadata&gt;   제목: 경주정보 불법 송출   작성자: KRA   마지막 수정자: KRA   작성일: 2022-07-09 19:23:20   수정일: 2022-12-04 15:24:16 &lt;/Document-Metadata&gt;  『불법경마 신고포상금…
+15. 2022년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;  년    월    일   &lt;table border=…
+16. 2021년도_(요약) 2021년 인권경영 기본계획 #8  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2021-05-29 15:41:30 &lt;/Document-Metadata&gt;  &lt;t…
+17. 2024년도_붙임1. 인권경영실행지침 일부 개정(안)_수정(241012) #15  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2023-11-01 14:09:00   수정일: 2024-10-12 16:56:29 &lt;/Document-Metadata&gt;  20  .   .     인권경영책임…
+18. 2024년도_[붙임1] 601. 취업규칙 전문(20241214)-제36차 개정 #34  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
     설명: 
-    마지막 수정자: KRA   작성일: 2006-03-14 16:07:44   수정일: 2024-12-15 09:
-[725ae7e3f94266ed] 2024년도_붙임1. ‘24년 제1차 인권경영위원회 개최계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: 개최개요   작성자: KRA   마지막 수정자: KRA   작성일: 2023-12-06 16:00:46   수정일: 2024-08-10 14:26:38 &lt;/Documen
-[7610ecb82f1d71e2] 2024년도_(전문)성희롱·성폭력_ 직장내 괴롭힘 및 스토킹 예방지침(241228)최종 #22  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
+    마지막 수정자: KRA   작성일: 2006-03-14 16:07:44   수정일: 2024-12-15 09:17:04 &lt;/Document-Metadata&gt;  [별…
+19. 2024년도_붙임1. ‘24년 제1차 인권경영위원회 개최계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: 개최개요   작성자: KRA   마지막 수정자: KRA   작성일: 2023-12-06 16:00:46   수정일: 2024-08-10 14:26:38 &lt;/Document-Metadata&gt;  ‘24년 제1차 인권경영위원회 …
+20. 2024년도_(전문)성희롱·성폭력_ 직장내 괴롭힘 및 스토킹 예방지침(241228)최종 #22  ▸  &lt;Document-Metadata&gt;   제목: 인사,후생   키워드: 
     설명: 
-    마지막 수정자: KRA   작성일: 2006-03-14 16:07:44   수정일: 2024-12-28 09:
+    마지막 수정자: KRA   작성일: 2006-03-14 16:07:44   수정일: 2024-12-28 09:23:18 &lt;/Document-Metadata&gt;  [별…
 ... +30 more</t>
         </is>
       </c>
@@ -5031,19 +5031,19 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>[1dd7a41b6d49067a] 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-M
-[230b3c89a0f6cfdc] 2023년도_붙임 1. 2023년 학교체육 승마 시범사업 운영계획(안) #35  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-11-04 14:57:12   수정일: 2022-12-02 16:28:09 &lt;/Document-Metadata&gt;
-[2cbdb440161c0502] 2024년도_2024년 제주경마공원 승마체험장 및 관상마체험장 운영계획 #17  ▸  &lt;Document-Metadata&gt;   제목: 2014   마지막 수정자: KRA   작성일: 2014-02-07 09:49:57   수정일: 2024-02-28 11:03:22 &lt;/Document-Metadata&gt;
-[345beb807d95ba70] 2020년도_★(결재) 2020 사회공익힐링 승마 사업 기본 운영 계획 #5  ▸  &lt;Document-Metadata&gt;   제목: 2019 전국민 승마체험 사업 기본계획   작성자: user   마지막 수정자: KRA   작성일: 2019-02-15 13:56:48   수정일: 2020-02-26
-[3811d5c616420fc2] 2024년도_240307 2024 유소년 승마지원 기본계획(요약)(최최종) #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-17 13:38:28   수정일: 2024-03-08 14:41:05 &lt;/Document-M
-[49833f0ed56ba434] 2023년도_제18회 제주마 축제 공고문 및 제안서 #37  ▸  &lt;Document-Metadata&gt;   제목: g   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-01 15:17:22   수정일: 2023-08-20 16:04:43 &lt;/Document-M
-[5619e37e7ee1470d] 2024년도_(양식) 말산업육성지원사업 추진실적 #2  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-28 14:58:32   수정일: 2024-06-13 14:38:26 &lt;/Document-Metadata&gt;
-[68c173524cf22c47] 2020년도_붙임_1_2020년 도심승마체험 시행계획(요약, 최종) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-03-07 18:01:46 &lt;/Document-Metadat
-[7b5af8d8a80073c5] 2023년도_[요약] 2023년 힐링승마 지원사업 추진 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-03-09 14:06:41 &lt;/Document-M
-[affde3091ecbe443] 2024년도_제주마축제 홍보 계획_최종 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-31 19:39:40 &lt;/Document-M
-[c3b5928050f2e9aa] 2024년도_(붙임1) 2024년 도심공원 승마체험 운영계획 변경(안) #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-07 14:26:11   수정일: 2024-06-07 17:52:12 &lt;/Document-M
-[c4f8c5320a9a943c] 2023년도_제18회 제주마 축제 시행계획(안) #26  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2023-08-20 16:19:01 &lt;/Docume
-[edf8fe17a083f95c] 2024년도_[붙임#1] (요약본) 2024년 힐링승마 지원사업 추진 계획(안)_ver2 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-02-22 19:09:53 &lt;/Document-M</t>
+          <t>1. 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-Metadata&gt;  === Extracted Images…
+2. 2023년도_붙임 1. 2023년 학교체육 승마 시범사업 운영계획(안) #35  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-11-04 14:57:12   수정일: 2022-12-02 16:28:09 &lt;/Document-Metadata&gt;  * 학교별 전·출입 인원을 감안하여 5% 범위에서 …
+3. 2024년도_2024년 제주경마공원 승마체험장 및 관상마체험장 운영계획 #17  ▸  &lt;Document-Metadata&gt;   제목: 2014   마지막 수정자: KRA   작성일: 2014-02-07 09:49:57   수정일: 2024-02-28 11:03:22 &lt;/Document-Metadata&gt;  【붙임 2】  관상마사 시설현황     주요시설  …
+4. 2020년도_★(결재) 2020 사회공익힐링 승마 사업 기본 운영 계획 #5  ▸  &lt;Document-Metadata&gt;   제목: 2019 전국민 승마체험 사업 기본계획   작성자: user   마지막 수정자: KRA   작성일: 2019-02-15 13:56:48   수정일: 2020-02-26 18:10:51 &lt;/Document-Metadata&gt; …
+5. 2024년도_240307 2024 유소년 승마지원 기본계획(요약)(최최종) #0  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2024-01-17 13:38:28   수정일: 2024-03-08 14:41:05 &lt;/Document-Metadata&gt;  2024 유소년 승마지원 기본계획(안…
+6. 2023년도_제18회 제주마 축제 공고문 및 제안서 #37  ▸  &lt;Document-Metadata&gt;   제목: g   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-01 15:17:22   수정일: 2023-08-20 16:04:43 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+7. 2024년도_(양식) 말산업육성지원사업 추진실적 #2  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-28 14:58:32   수정일: 2024-06-13 14:38:26 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+8. 2020년도_붙임_1_2020년 도심승마체험 시행계획(요약, 최종) #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2020-03-07 18:01:46 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;t…
+9. 2023년도_[요약] 2023년 힐링승마 지원사업 추진 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-03-09 14:06:41 &lt;/Document-Metadata&gt;  ※ 출석율 및 신청취소 등을 감안하여…
+10. 2024년도_제주마축제 홍보 계획_최종 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-31 19:39:40 &lt;/Document-Metadata&gt;  다양한 홍보 및 광고로 사전 행사 분…
+11. 2024년도_(붙임1) 2024년 도심공원 승마체험 운영계획 변경(안) #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-07 14:26:11   수정일: 2024-06-07 17:52:12 &lt;/Document-Metadata&gt;  * 도심승마체험 가능 장소에 직접 방…
+12. 2023년도_제18회 제주마 축제 시행계획(안) #26  ▸  &lt;Document-Metadata&gt;   제목: 외부 환경   작성자: KRA   마지막 수정자: KRA   작성일: 2017-11-14 10:11:04   수정일: 2023-08-20 16:19:01 &lt;/Document-Metadata&gt;  약합니다.    1. 본인은“…
+13. 2024년도_[붙임#1] (요약본) 2024년 힐링승마 지원사업 추진 계획(안)_ver2 #3  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-02-22 19:09:53 &lt;/Document-Metadata&gt;  5. 추진일정  &lt;table bord…</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -5096,26 +5096,26 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>[03e46e426c5e0a40] 2022년도_(붙임1) 인사규정시행세칙 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:10:39 &lt;/Document-Metadata&gt;
-[06ea8eb0c6498c61] 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-M
-[0cc6e308b2160025] 2024년도_(요약) 2024년 선수단(유도탁구) 운영 계획_240427 #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-19 14:09:35   수정일: 2024-04-27 10:24:26 &lt;/Document-Metadata&gt;
-[0fdd2b845b06532f] 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-M
-[1ab7e770624479a7] 2024년도_(입찰공고문) 스마트 조교정보시스템 구축 #9  ▸  &lt;Document-Metadata&gt;   제목: 입찰공고문   마지막 수정자: KRA   작성일: 2007-05-20 11:05:36   수정일: 2024-05-10 17:36:20 &lt;/Document-Metadata
-[210e0e2db641965a] 2020년도_[붙임 1] 2020년 재활승마 활성화 지원 시범사업 계획(안_요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 말산업육성본부   작성자: KRA   마지막 수정자: KRA   작성일: 2017-05-24 17:59:41   수정일: 2020-08-07 15:31:04 &lt;/Docu
-[27325f8e49d559f4] 2020년도_(본문) 2020년도 내부경영평가제도 개선(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-22 09:53:12 &lt;/Documen
-[2a67e1073fe83029] 2022년도_2022 힐링승마 지원사업 운영 결과보고_221222 #25  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-08-06 09:18:55   수정일: 2022-12-22 18:09:26 &lt;/Document-Metadata&gt;
-[2c473c597114e075] 2024년도_(요약) 2024년 윤리경영 추진계획(안) (1) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-05-30 11:08:03 &lt;/Document-M
-[2ffc5467d8f17d86] 2020년도_(본문) 2020년 한국마사회 지식경영 운영계획(안)(200417) #19  ▸  &lt;Document-Metadata&gt;   제목: 2017년 지식경영 운영계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-13 15:38:51   수정일: 2020-04-17 10:22:3
-[320953785300baf0] 2023년도_(붙임4) 위촉직관리지침 일부 개정(안) #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:09 &lt;/Document-Metadata&gt;
-[363c897a38703bf5] 2023년도_[요약]한국마사회 CEO·임차인 「청·심·환 간담회」 결과보고 #2  ▸  &lt;Document-Metadata&gt;   제목: □ 편의점 물건   작성자: KRA   마지막 수정자: KRA   작성일: 2022-12-27 14:49:26   수정일: 2023-09-07 14:18:28 &lt;/Doc
-[386c3d238d9e12b0] 2021년도_(요약) 2021 사회공익 힐링승마 사업 결과보고 #4  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-23 17:48:23 &lt;/Document-M
-[40122ffcb05effea] 2020년도_★(요약) 2020 사회공익힐링 승마 사업 기본 운영 계획 #10  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-04 13:13:33   수정일: 2020-02-26 16:19:50 &lt;/Document-Metadata&gt;
-[470d301f2c963cc9] 2020년도_(요약) 2020년 한국마사회 지식경영 운영계획(안)(200417) #1  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2020-04-17 09:
-[475035a5d7c43233] 2023년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;
-[49833f0ed56ba434] 2023년도_제18회 제주마 축제 공고문 및 제안서 #37  ▸  &lt;Document-Metadata&gt;   제목: g   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-01 15:17:22   수정일: 2023-08-20 16:04:43 &lt;/Document-M
-[499f2103edc5d6e1] 2021년도_(본문) 2021년 인권경영 기본계획 #30  ▸  &lt;Document-Metadata&gt;   제목: 2021년도 인권경영 추진계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-05-14 10:44:55   수정일: 2021-05-29 15:39:
-[4b93e74ded9f99c1] 2020년도_2020년 지사 맞춤형 사회적가치 실현  추진 계획(안)) #39  ▸  &lt;Document-Metadata&gt;   제목: 일자리 창출 중장기 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-09-12 12:21:29   수정일: 2020-03-15 17:49:55
-[4bd81a5d3f7d0759] 2024년도_2024년 청심환 간담회 시행 계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: □    작성자: KRA   마지막 수정자: KRA   작성일: 2023-07-13 17:49:14   수정일: 2024-07-20 15:25:58 &lt;/Document-
+          <t>1. 2022년도_(붙임1) 인사규정시행세칙 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:10:39 &lt;/Document-Metadata&gt;  ※ 작성방법 : 점검결과에 ‘적정’ 또는 ‘부적정’…
+2. 2020년도_(요약) 2020년도 내부경영평가제도 개선(안) #2  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2020-02-22 09:53:35 &lt;/Document-Metadata&gt;  가와 사업성과평가 통합    ◦ (차…
+3. 2024년도_(요약) 2024년 선수단(유도탁구) 운영 계획_240427 #3  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2024-03-19 14:09:35   수정일: 2024-04-27 10:24:26 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+4. 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-Metadata&gt;  6) 추진일정    - 프로그램별 세…
+5. 2024년도_(입찰공고문) 스마트 조교정보시스템 구축 #9  ▸  &lt;Document-Metadata&gt;   제목: 입찰공고문   마지막 수정자: KRA   작성일: 2007-05-20 11:05:36   수정일: 2024-05-10 17:36:20 &lt;/Document-Metadata&gt;  제출서류는 계약서에 특별히 명기하는 내용 외에는 …
+6. 2020년도_[붙임 1] 2020년 재활승마 활성화 지원 시범사업 계획(안_요약) #0  ▸  &lt;Document-Metadata&gt;   제목: 말산업육성본부   작성자: KRA   마지막 수정자: KRA   작성일: 2017-05-24 17:59:41   수정일: 2020-08-07 15:31:04 &lt;/Document-Metadata&gt;  [Image:temp/im…
+7. 2020년도_(본문) 2020년도 내부경영평가제도 개선(안) #21  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2020-02-22 09:53:12 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+8. 2022년도_2022 힐링승마 지원사업 운영 결과보고_221222 #25  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-08-06 09:18:55   수정일: 2022-12-22 18:09:26 &lt;/Document-Metadata&gt;  &lt; 하반기 현장점검 결과 및 의견 &gt;  &lt;table…
+9. 2024년도_(요약) 2024년 윤리경영 추진계획(안) (1) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-05-30 11:08:03 &lt;/Document-Metadata&gt;  □ CEO 주도의 윤리경영 활동 및 …
+10. 2020년도_(본문) 2020년 한국마사회 지식경영 운영계획(안)(200417) #19  ▸  &lt;Document-Metadata&gt;   제목: 2017년 지식경영 운영계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-13 15:38:51   수정일: 2020-04-17 10:22:34 &lt;/Document-Metadata&gt;  부서 심사 …
+11. 2023년도_(붙임4) 위촉직관리지침 일부 개정(안) #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:09 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+12. 2023년도_[요약]한국마사회 CEO·임차인 「청·심·환 간담회」 결과보고 #2  ▸  &lt;Document-Metadata&gt;   제목: □ 편의점 물건   작성자: KRA   마지막 수정자: KRA   작성일: 2022-12-27 14:49:26   수정일: 2023-09-07 14:18:28 &lt;/Document-Metadata&gt;  &lt;table border…
+13. 2021년도_(요약) 2021 사회공익 힐링승마 사업 결과보고 #4  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-12-23 17:48:23 &lt;/Document-Metadata&gt;  * 스트레스 감소 인원 대상 강습 전…
+14. 2020년도_★(요약) 2020 사회공익힐링 승마 사업 기본 운영 계획 #10  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-04 13:13:33   수정일: 2020-02-26 16:19:50 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+15. 2020년도_(요약) 2020년 한국마사회 지식경영 운영계획(안)(200417) #1  ▸  &lt;Document-Metadata&gt;   제목: 제1차 청렴옴부즈만 회의 개최 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2010-05-16 09:55:27   수정일: 2020-04-17 09:40:22 &lt;/Document-Metadata&gt;  3.…
+16. 2023년도_(붙임3) 전임직관리지침 일부 개정(안) #7  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:11:16 &lt;/Document-Metadata&gt;  년    월    일   &lt;table border=…
+17. 2023년도_제18회 제주마 축제 공고문 및 제안서 #37  ▸  &lt;Document-Metadata&gt;   제목: g   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-01 15:17:22   수정일: 2023-08-20 16:04:43 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+18. 2021년도_(본문) 2021년 인권경영 기본계획 #30  ▸  &lt;Document-Metadata&gt;   제목: 2021년도 인권경영 추진계획   작성자: KRA   마지막 수정자: KRA   작성일: 2021-05-14 10:44:55   수정일: 2021-05-29 15:39:40 &lt;/Document-Metadata&gt;  === E…
+19. 2020년도_2020년 지사 맞춤형 사회적가치 실현  추진 계획(안)) #39  ▸  &lt;Document-Metadata&gt;   제목: 일자리 창출 중장기 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-09-12 12:21:29   수정일: 2020-03-15 17:49:55 &lt;/Document-Metadata&gt;  &lt;table b…
+20. 2024년도_2024년 청심환 간담회 시행 계획(안) #2  ▸  &lt;Document-Metadata&gt;   제목: □    작성자: KRA   마지막 수정자: KRA   작성일: 2023-07-13 17:49:14   수정일: 2024-07-20 15:25:58 &lt;/Document-Metadata&gt;  □ 주요내용    ○ 참석 임차인 …
 ... +39 more</t>
         </is>
       </c>
@@ -5337,8 +5337,8 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>[7b891a6e2bfdb9a0] (not found in graph)
-[d4e8e7e0de0bee24] (not found in graph)</t>
+          <t>1. [7b891a6e2bfdb9a0] (not found)
+2. [d4e8e7e0de0bee24] (not found)</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -5372,8 +5372,8 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>[abf6b885cc56106c] (not found in graph)
-[1d7a8c5b7cde9f12] (not found in graph)</t>
+          <t>1. [abf6b885cc56106c] (not found)
+2. [1d7a8c5b7cde9f12] (not found)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>[a3e51e3ccd5f7a45] (not found in graph)</t>
+          <t>1. [a3e51e3ccd5f7a45] (not found)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>[b5c2f8e7a11b3290] (not found in graph)</t>
+          <t>1. [b5c2f8e7a11b3290] (not found)</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>[e2b4c1d7f5a3a908] (not found in graph)</t>
+          <t>1. [e2b4c1d7f5a3a908] (not found)</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -5506,8 +5506,8 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>[f6a42e8c3b1d2f47] (not found in graph)
-[9c3e7a1b5d6f8290] (not found in graph)</t>
+          <t>1. [f6a42e8c3b1d2f47] (not found)
+2. [9c3e7a1b5d6f8290] (not found)</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>[c8f4e2d1a7b5c390] (not found in graph)</t>
+          <t>1. [c8f4e2d1a7b5c390] (not found)</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>[a1b2c3d4e5f67890] (not found in graph)</t>
+          <t>1. [a1b2c3d4e5f67890] (not found)</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>[d7e9f1a3b5c79024] (not found in graph)</t>
+          <t>1. [d7e9f1a3b5c79024] (not found)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>[b8c2d4e6f8a1b024] (not found in graph)</t>
+          <t>1. [b8c2d4e6f8a1b024] (not found)</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00003] pr_goods_base:G00003  ▸  pr_goods_base: Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00002] pr_goods_base:G00002  ▸  pr_goods_base: CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+          <t>1. CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00006] pr_goods_base:G00006  ▸  pr_goods_base: Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-</t>
+          <t>1. Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G01006] pr_goods_base:G01006  ▸  pr_goods_base: Cheese - Boursin, Garlic / Herbs | G01006 | 2023-12-18 | Y | 9999.0 | 77000.0 | 2023-12-19 00:00:00 | 202</t>
+          <t>1. Cheese - Boursin, Garlic / Herbs | G01006 | 2023-12-18 | Y | 9999.0 | 77000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -6034,8 +6034,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00010] pr_goods_base:G00010  ▸  pr_goods_base: Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024
-[pr_goods_base:G00462] pr_goods_base:G00462  ▸  pr_goods_base: Wine - Niagara Peninsula Vqa | G00462 | 2023-12-18 | Y | 9999.0 | 22000.0 | 2023-12-19 00:00:00 | 2024-12</t>
+          <t>1. Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Wine - Niagara Peninsula Vqa | G00462 | 2023-12-18 | Y | 9999.0 | 22000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G01004] pr_goods_base:G01004  ▸  pr_goods_base: Chicken - Soup Base | G01004 | 2023-12-18 | Y | 9999.0 | 52000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00</t>
+          <t>1. Chicken - Soup Base | G01004 | 2023-12-18 | Y | 9999.0 | 52000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00992] pr_goods_base:G00992  ▸  pr_goods_base: Pastry - Banana Muffin - Mini | G00992 | 2023-12-18 | Y | 9999.0 | 24000.0 | 2023-12-19 00:00:00 | 2024-1</t>
+          <t>1. Pastry - Banana Muffin - Mini | G00992 | 2023-12-18 | Y | 9999.0 | 24000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -6135,8 +6135,8 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00082] pr_goods_base:G00082  ▸  pr_goods_base: Jameson - Irish Whiskey | G00082 | 2023-12-18 | Y | 9999.0 | 58000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
-[pr_goods_base:G00968] pr_goods_base:G00968  ▸  pr_goods_base: Jameson Irish Whiskey | G00968 | 2023-12-18 | Y | 9999.0 | 15000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:</t>
+          <t>1. Jameson - Irish Whiskey | G00082 | 2023-12-18 | Y | 9999.0 | 58000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Jameson Irish Whiskey | G00968 | 2023-12-18 | Y | 9999.0 | 15000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -6170,8 +6170,8 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00470] pr_goods_base:G00470  ▸  pr_goods_base: Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18
-[pr_goods_base:G00736] pr_goods_base:G00736  ▸  pr_goods_base: Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18</t>
+          <t>1. Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -6205,8 +6205,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00467] pr_goods_base:G00467  ▸  pr_goods_base: English Muffin | G00467 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
-[pr_goods_base:G00569] pr_goods_base:G00569  ▸  pr_goods_base: English Muffin | G00569 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |</t>
+          <t>1. English Muffin | G00467 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. English Muffin | G00569 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00974] pr_goods_base:G00974  ▸  pr_goods_base: Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 20</t>
+          <t>1. Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00751] pr_goods_base:G00751  ▸  pr_goods_base: Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -6306,8 +6306,8 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00106] pr_goods_base:G00106  ▸  pr_goods_base: Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00339] pr_goods_base:G00339  ▸  pr_goods_base: Wine - Ice Wine | G00339 | 2023-12-18 | Y | 9999.0 | 39000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+          <t>1. Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Wine - Ice Wine | G00339 | 2023-12-18 | Y | 9999.0 | 39000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -6341,8 +6341,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00315] pr_goods_base:G00315  ▸  pr_goods_base: Cheese - Feta | G00315 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
-[pr_goods_base:G00694] pr_goods_base:G00694  ▸  pr_goods_base: Cheese - Feta | G00694 | 2023-12-18 | Y | 9999.0 | 55000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |</t>
+          <t>1. Cheese - Feta | G00315 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Cheese - Feta | G00694 | 2023-12-18 | Y | 9999.0 | 55000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00113] pr_goods_base:G00113  ▸  pr_goods_base: Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18</t>
+          <t>1. Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -6409,9 +6409,9 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00563] pr_goods_base:G00563  ▸  pr_goods_base: Bread - 10 Grain | G00563 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00817] pr_goods_base:G00817  ▸  pr_goods_base: Bread - 10 Grain | G00817 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G01005] pr_goods_base:G01005  ▸  pr_goods_base: Bread - 10 Grain | G01005 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+          <t>1. Bread - 10 Grain | G00563 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Bread - 10 Grain | G00817 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Bread - 10 Grain | G01005 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00711] pr_goods_base:G00711  ▸  pr_goods_base: Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2</t>
+          <t>1. Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -6699,10 +6699,10 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00040] pr_goods_base:G00040  ▸  pr_goods_base: Cheese - Provolone | G00040 | 2023-12-18 | Y | 9999.0 | 56000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
-[pr_goods_base:G00083] pr_goods_base:G00083  ▸  pr_goods_base: Cheese - Gorgonzola | G00083 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
-[pr_goods_base:G00442] pr_goods_base:G00442  ▸  pr_goods_base: Cheese - Parmesan Cubes | G00442 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
-[pr_goods_base:G00158] pr_goods_base:G00158  ▸  pr_goods_base: Cheese - Mozzarella | G00158 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00</t>
+          <t>1. Cheese - Provolone | G00040 | 2023-12-18 | Y | 9999.0 | 56000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Cheese - Gorgonzola | G00083 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Cheese - Parmesan Cubes | G00442 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Cheese - Mozzarella | G00158 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00003] pr_goods_base:G00003  ▸  pr_goods_base: Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00997] pr_goods_base:G00997  ▸  pr_goods_base: Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:</t>
+          <t>1. Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -6951,10 +6951,10 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00072] pr_goods_base:G00072  ▸  pr_goods_base: Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00302] pr_goods_base:G00302  ▸  pr_goods_base: Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 202
-[pr_goods_base:G00711] pr_goods_base:G00711  ▸  pr_goods_base: Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2
-[pr_goods_base:G00892] pr_goods_base:G00892  ▸  pr_goods_base: Plate Pie Foil | G00892 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |</t>
+          <t>1. Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Plate Pie Foil | G00892 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -6998,26 +6998,26 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00063] pr_goods_base:G00063  ▸  pr_goods_base: Chips Potato Swt Chilli Sour | G00063 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-
-[pr_goods_base:G00068] pr_goods_base:G00068  ▸  pr_goods_base: Amarula Cream | G00068 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2
-[pr_goods_base:G00072] pr_goods_base:G00072  ▸  pr_goods_base: Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00089] pr_goods_base:G00089  ▸  pr_goods_base: Quail - Jumbo | G00089 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2
-[pr_goods_base:G00098] pr_goods_base:G00098  ▸  pr_goods_base: Fudge - Chocolate Fudge | G00098 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
-[pr_goods_base:G00202] pr_goods_base:G00202  ▸  pr_goods_base: Pepper - Green Thai | G00202 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
-[pr_goods_base:G00203] pr_goods_base:G00203  ▸  pr_goods_base: Jam - Raspberry,jar | G00203 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
-[pr_goods_base:G00204] pr_goods_base:G00204  ▸  pr_goods_base: Oysters - Smoked | G00204 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00217] pr_goods_base:G00217  ▸  pr_goods_base: Soda Water - Club Soda, 355 Ml | G00217 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00258] pr_goods_base:G00258  ▸  pr_goods_base: Juice - Apple Cider | G00258 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
-[pr_goods_base:G00261] pr_goods_base:G00261  ▸  pr_goods_base: Scotch - Queen Anne | G00261 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:
-[pr_goods_base:G00267] pr_goods_base:G00267  ▸  pr_goods_base: Soup - Campbells - Tomato | G00267 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18
-[pr_goods_base:G00283] pr_goods_base:G00283  ▸  pr_goods_base: Chinese Foods - Chicken Wing | G00283 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-
-[pr_goods_base:G00302] pr_goods_base:G00302  ▸  pr_goods_base: Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 202
-[pr_goods_base:G00314] pr_goods_base:G00314  ▸  pr_goods_base: Fondant - Icing | G00314 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
-[pr_goods_base:G00332] pr_goods_base:G00332  ▸  pr_goods_base: Nut - Walnut, Chopped | G00332 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:0
-[pr_goods_base:G00376] pr_goods_base:G00376  ▸  pr_goods_base: Otomegusa Dashi Konbu | G00376 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:0
-[pr_goods_base:G00388] pr_goods_base:G00388  ▸  pr_goods_base: Lettuce - Iceberg | G00388 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00438] pr_goods_base:G00438  ▸  pr_goods_base: Doilies - 8, Paper | G00438 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Chips Potato Swt Chilli Sour | G00063 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Amarula Cream | G00068 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Quail - Jumbo | G00089 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+6. Fudge - Chocolate Fudge | G00098 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+7. Pepper - Green Thai | G00202 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+8. Jam - Raspberry,jar | G00203 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+9. Oysters - Smoked | G00204 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+10. Soda Water - Club Soda, 355 Ml | G00217 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+11. Juice - Apple Cider | G00258 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+12. Scotch - Queen Anne | G00261 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+13. Soup - Campbells - Tomato | G00267 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+14. Chinese Foods - Chicken Wing | G00283 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+15. Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+16. Fondant - Icing | G00314 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+17. Nut - Walnut, Chopped | G00332 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+18. Otomegusa Dashi Konbu | G00376 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+19. Lettuce - Iceberg | G00388 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+20. Doilies - 8, Paper | G00438 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
 ... +21 more</t>
         </is>
       </c>
@@ -7099,9 +7099,9 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
-[pr_goods_base:G00004] pr_goods_base:G00004  ▸  pr_goods_base: Jacket | 남성 의류 | G00004 | 2024-12-19 | Y | 200.0 | 18500.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 |
-[pr_goods_base:G00007] pr_goods_base:G00007  ▸  pr_goods_base: iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 202</t>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Jacket | 남성 의류 | G00004 | 2024-12-19 | Y | 200.0 | 18500.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -7144,11 +7144,11 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00751] pr_goods_base:G00751  ▸  pr_goods_base: Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
-[pr_goods_base:G00472] pr_goods_base:G00472  ▸  pr_goods_base: Bread - Kimel Stick Poly | G00472 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18
-[pr_goods_base:G00389] pr_goods_base:G00389  ▸  pr_goods_base: Pork Ham Prager | G00389 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00329] pr_goods_base:G00329  ▸  pr_goods_base: Sauce - Ranch Dressing | G00329 | 2023-12-18 | Y | 9999.0 | 88000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
-[pr_goods_base:G00997] pr_goods_base:G00997  ▸  pr_goods_base: Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:</t>
+          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Bread - Kimel Stick Poly | G00472 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Pork Ham Prager | G00389 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Sauce - Ranch Dressing | G00329 | 2023-12-18 | Y | 9999.0 | 88000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -7193,17 +7193,17 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00270] pr_goods_base:G00270  ▸  pr_goods_base: Beer - Mill St Organic | G00270 | 2023-12-18 | Y | 9999.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
-[pr_goods_base:G00466] pr_goods_base:G00466  ▸  pr_goods_base: Beer - Sleemans Honey Brown | G00466 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-
-[pr_goods_base:G00645] pr_goods_base:G00645  ▸  pr_goods_base: Beer - Original Organic Lager | G00645 | 2023-12-18 | Y | 9999.0 | 73000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00700] pr_goods_base:G00700  ▸  pr_goods_base: Beer - Moosehead | G00700 | 2023-12-18 | Y | 9999.0 | 87000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00719] pr_goods_base:G00719  ▸  pr_goods_base: Beer - Original Organic Lager | G00719 | 2023-12-18 | Y | 9999.0 | 74000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00793] pr_goods_base:G00793  ▸  pr_goods_base: Beer - Steamwhistle | G00793 | 2023-12-18 | Y | 9999.0 | 33000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
-[pr_goods_base:G00798] pr_goods_base:G00798  ▸  pr_goods_base: Beer - Original Organic Lager | G00798 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00928] pr_goods_base:G00928  ▸  pr_goods_base: Beer - Rickards Red | G00928 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
-[pr_goods_base:G00937] pr_goods_base:G00937  ▸  pr_goods_base: Beer - Mcauslan Apricot | G00937 | 2023-12-18 | Y | 9999.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
-[pr_goods_base:G00938] pr_goods_base:G00938  ▸  pr_goods_base: Beer - Steamwhistle | G00938 | 2023-12-18 | Y | 9999.0 | 63000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00
-[pr_goods_base:G00974] pr_goods_base:G00974  ▸  pr_goods_base: Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 20</t>
+          <t>1. Beer - Mill St Organic | G00270 | 2023-12-18 | Y | 9999.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Beer - Sleemans Honey Brown | G00466 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Beer - Original Organic Lager | G00645 | 2023-12-18 | Y | 9999.0 | 73000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Beer - Moosehead | G00700 | 2023-12-18 | Y | 9999.0 | 87000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Beer - Original Organic Lager | G00719 | 2023-12-18 | Y | 9999.0 | 74000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+6. Beer - Steamwhistle | G00793 | 2023-12-18 | Y | 9999.0 | 33000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+7. Beer - Original Organic Lager | G00798 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+8. Beer - Rickards Red | G00928 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+9. Beer - Mcauslan Apricot | G00937 | 2023-12-18 | Y | 9999.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+10. Beer - Steamwhistle | G00938 | 2023-12-18 | Y | 9999.0 | 63000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+11. Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00857] pr_goods_base:G00857  ▸  pr_goods_base: Flour - Masa De Harina Mexican | G00857 | 2023-12-18 | Y | 9999.0 | 86000.0 | 2023-12-19 00:00:00 | 2024-</t>
+          <t>1. Flour - Masa De Harina Mexican | G00857 | 2023-12-18 | Y | 9999.0 | 86000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00001] pr_goods_base:G00001  ▸  pr_goods_base: Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0</t>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -7336,26 +7336,26 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00010] pr_goods_base:G00010  ▸  pr_goods_base: Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024
-[pr_goods_base:G00034] pr_goods_base:G00034  ▸  pr_goods_base: Wine - Piper Heidsieck Brut | G00034 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-
-[pr_goods_base:G00048] pr_goods_base:G00048  ▸  pr_goods_base: Wine - Sicilia Igt Nero Avola | G00048 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00055] pr_goods_base:G00055  ▸  pr_goods_base: Wine - Champagne Brut Veuve | G00055 | 2023-12-18 | Y | 9999.0 | 10000.0 | 2023-12-19 00:00:00 | 2024-12-
-[pr_goods_base:G00077] pr_goods_base:G00077  ▸  pr_goods_base: Wine - Magnotta, White | G00077 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
-[pr_goods_base:G00086] pr_goods_base:G00086  ▸  pr_goods_base: Wine - Winzer Krems Gruner | G00086 | 2023-12-18 | Y | 9999.0 | 75000.0 | 2023-12-19 00:00:00 | 2024-12-1
-[pr_goods_base:G00106] pr_goods_base:G00106  ▸  pr_goods_base: Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00112] pr_goods_base:G00112  ▸  pr_goods_base: Wine - Red, Cabernet Merlot | G00112 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-
-[pr_goods_base:G00113] pr_goods_base:G00113  ▸  pr_goods_base: Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18
-[pr_goods_base:G00138] pr_goods_base:G00138  ▸  pr_goods_base: Wine - Fino Tio Pepe Gonzalez | G00138 | 2023-12-18 | Y | 9999.0 | 64000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00144] pr_goods_base:G00144  ▸  pr_goods_base: Wine - Tribal Sauvignon | G00144 | 2023-12-18 | Y | 9999.0 | 38000.0 | 2023-12-19 00:00:00 | 2024-12-18 0
-[pr_goods_base:G00148] pr_goods_base:G00148  ▸  pr_goods_base: Wine - Delicato Merlot | G00148 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00
-[pr_goods_base:G00164] pr_goods_base:G00164  ▸  pr_goods_base: Wine - Pinot Grigio Collavini | G00164 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00172] pr_goods_base:G00172  ▸  pr_goods_base: Wine - Red, Pinot Noir, Chateau | G00172 | 2023-12-18 | Y | 9999.0 | 48000.0 | 2023-12-19 00:00:00 | 2024
-[pr_goods_base:G00174] pr_goods_base:G00174  ▸  pr_goods_base: Wine La Vielle Ferme Cote Du | G00174 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12
-[pr_goods_base:G00207] pr_goods_base:G00207  ▸  pr_goods_base: Wine - Rubyport | G00207 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00
-[pr_goods_base:G00264] pr_goods_base:G00264  ▸  pr_goods_base: Wine - Rosso Del Veronese Igt | G00264 | 2023-12-18 | Y | 9999.0 | 54000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00277] pr_goods_base:G00277  ▸  pr_goods_base: Wine - Wyndham Estate Bin 777 | G00277 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00282] pr_goods_base:G00282  ▸  pr_goods_base: Wine - Chateauneuf Du Pape | G00282 | 2023-12-18 | Y | 9999.0 | 29000.0 | 2023-12-19 00:00:00 | 2024-12-1
-[pr_goods_base:G00293] pr_goods_base:G00293  ▸  pr_goods_base: Wine - Casablanca Valley | G00293 | 2023-12-18 | Y | 9999.0 | 12000.0 | 2023-12-19 00:00:00 | 2024-12-18
+          <t>1. Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Wine - Piper Heidsieck Brut | G00034 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Wine - Sicilia Igt Nero Avola | G00048 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Wine - Champagne Brut Veuve | G00055 | 2023-12-18 | Y | 9999.0 | 10000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Wine - Magnotta, White | G00077 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+6. Wine - Winzer Krems Gruner | G00086 | 2023-12-18 | Y | 9999.0 | 75000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+7. Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+8. Wine - Red, Cabernet Merlot | G00112 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+9. Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+10. Wine - Fino Tio Pepe Gonzalez | G00138 | 2023-12-18 | Y | 9999.0 | 64000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+11. Wine - Tribal Sauvignon | G00144 | 2023-12-18 | Y | 9999.0 | 38000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+12. Wine - Delicato Merlot | G00148 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+13. Wine - Pinot Grigio Collavini | G00164 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+14. Wine - Red, Pinot Noir, Chateau | G00172 | 2023-12-18 | Y | 9999.0 | 48000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+15. Wine La Vielle Ferme Cote Du | G00174 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+16. Wine - Rubyport | G00207 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+17. Wine - Rosso Del Veronese Igt | G00264 | 2023-12-18 | Y | 9999.0 | 54000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+18. Wine - Wyndham Estate Bin 777 | G00277 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+19. Wine - Chateauneuf Du Pape | G00282 | 2023-12-18 | Y | 9999.0 | 29000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+20. Wine - Casablanca Valley | G00293 | 2023-12-18 | Y | 9999.0 | 12000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
 ... +10 more</t>
         </is>
       </c>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00005] pr_goods_base:G00005  ▸  pr_goods_base: Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00</t>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -7467,9 +7467,9 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00470] pr_goods_base:G00470  ▸  pr_goods_base: Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18
-[pr_goods_base:G00492] pr_goods_base:G00492  ▸  pr_goods_base: Lamb - Loin, Trimmed, Boneless | G00492 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-1
-[pr_goods_base:G00736] pr_goods_base:G00736  ▸  pr_goods_base: Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18</t>
+          <t>1. Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Lamb - Loin, Trimmed, Boneless | G00492 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -7512,8 +7512,8 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>[pr_goods_base:G00002] pr_goods_base:G00002  ▸  pr_goods_base: CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:0
-[pr_goods_base:G00006] pr_goods_base:G00006  ▸  pr_goods_base: Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-</t>
+          <t>1. CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">

--- a/eval/data/gt_datasets.xlsx
+++ b/eval/data/gt_datasets.xlsx
@@ -9,13 +9,16 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="assort" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="assort_hard" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="krra" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="krra_graph" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="krra_hard" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="krra_multihop" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="x2bee" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="x2bee_hard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="assort_conversational" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="assort_hard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="krra" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="krra_conversational" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="krra_graph" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="krra_hard" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="krra_multihop" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="x2bee" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="x2bee_conversational" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="x2bee_hard" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -533,20 +536,20 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>assort_hard</t>
+          <t>assort_conversational</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>패션 이커머스 정형 데이터 난이도별 평가 — L2~L7. node title 기반 GT.</t>
+          <t>assort 패션 이커머스 데이터에 대한 복합·대화형 질문 30개 — 리뷰 감성, 사이즈/핏, 시즌 조합, 쇼핑 추천</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>doc_id</t>
+          <t>node_title</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -558,12 +561,16 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>krra</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
+          <t>assort_hard</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>패션 이커머스 정형 데이터 난이도별 평가 — L2~L7. node title 기반 GT.</t>
+        </is>
+      </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -579,12 +586,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>krra_graph</t>
+          <t>krra</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -600,16 +607,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>krra_hard</t>
+          <t>krra_conversational</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>난이도별 평가 쿼리 — L2(패러프레이즈) ~ L7(자연어). 실제 doc_id 기반 GT.</t>
+          <t>KRRA 경마/말산업 문서에 대한 복합·대화형 질문 30개 — 패러프레이즈, 교차문서, 필터, 멀티홉</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -625,16 +632,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>krra_multihop</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>복합/교차 문서 검색 쿼리 — 3세대 파이프라인 검증용</t>
-        </is>
-      </c>
+          <t>krra_graph</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
       <c r="C11" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -650,48 +653,123 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>x2bee</t>
+          <t>krra_hard</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>X2BEE ai_lab_main 이커머스 데이터 검색 GT (6 tables, ~19,843 nodes). 상품/판매/피드백 정형 데이터.</t>
+          <t>난이도별 평가 쿼리 — L2(패러프레이즈) ~ L7(자연어). 실제 doc_id 기반 GT.</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>node_title</t>
+          <t>doc_id</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>KO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>krra_multihop</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>복합/교차 문서 검색 쿼리 — 3세대 파이프라인 검증용</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>doc_id</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>x2bee</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>X2BEE ai_lab_main 이커머스 데이터 검색 GT (6 tables, ~19,843 nodes). 상품/판매/피드백 정형 데이터.</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>node_title</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>x2bee_conversational</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>X2BEE 이커머스 데이터에 대한 복합·대화형 질문 30개 — 멀티홉 추론, 조건부 집계, 자연어 필터, 비교, 추천 쿼리</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>node_title</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>x2bee_hard</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>X2BEE ai_lab_main 이커머스 고난이도 검색 GT — 패러프레이즈, FK조인, 필터, 집계, 멀티홉</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C16" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>node_title</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
@@ -701,6 +779,3277 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>x2bee</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>X2BEE ai_lab_main 이커머스 데이터 검색 GT (6 tables, ~19,843 nodes). 상품/판매/피드백 정형 데이터.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>id_field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>node_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Total queries</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>qid</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_count</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>e001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 15 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>상품명 정확 검색</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>e002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Shin Ramyun</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>상품명 정확 검색</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>e003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Galaxy Book</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>상품명 정확 검색</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>e004</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Dried Beef</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>상품명 정확 검색 — 동명 상품 가능</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>e005</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CLA Mask</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>상품명 정확 검색</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>1. CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>e006</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Volume Lip plumper maxi</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>상품명 정확 검색 (화장품)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>1. Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00006</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>e007</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Cheese Boursin Garlic Herbs</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>상품명 부분 검색</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>1. Cheese - Boursin, Garlic / Herbs | G01006 | 2023-12-18 | Y | 9999.0 | 77000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G01006</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>e008</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Wine Niagara Reisling</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>와인 상품 검색</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>1. Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Wine - Niagara Peninsula Vqa | G00462 | 2023-12-18 | Y | 9999.0 | 22000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00010
+pr_goods_base:G00462</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>e009</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Chicken Soup Base</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>상품명 검색</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>1. Chicken - Soup Base | G01004 | 2023-12-18 | Y | 9999.0 | 52000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G01004</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>e010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Pastry Banana Muffin</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>복합 상품명 검색</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>1. Pastry - Banana Muffin - Mini | G00992 | 2023-12-18 | Y | 9999.0 | 24000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00992</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>e011</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Jameson Irish Whiskey</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>주류 상품 검색 — 동명 상품 2개 (dash 유무 차이)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>1. Jameson - Irish Whiskey | G00082 | 2023-12-18 | Y | 9999.0 | 58000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Jameson Irish Whiskey | G00968 | 2023-12-18 | Y | 9999.0 | 15000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00082
+pr_goods_base:G00968</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>e012</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Lamb Shoulder Boneless</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>식재료 검색 — 유사 상품 다수</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>1. Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00470
+pr_goods_base:G00736</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>e013</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>English Muffin</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>동명 상품 2개</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>1. English Muffin | G00467 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. English Muffin | G00569 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00467
+pr_goods_base:G00569</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>e014</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Beer Alexander Kieths Pale Ale</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>맥주 상품 검색</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>1. Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00974</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>e015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Wiberg Super Cure</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>리뷰가 가장 많은 상품 (29건)</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00751</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>e016</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Ice Wine</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>아이스 와인 — 동명 2개 상품</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>1. Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Wine - Ice Wine | G00339 | 2023-12-18 | Y | 9999.0 | 39000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00106
+pr_goods_base:G00339</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>e017</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Cheese Feta</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>치즈 종류 검색 — 2개 상품</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>1. Cheese - Feta | G00315 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Cheese - Feta | G00694 | 2023-12-18 | Y | 9999.0 | 55000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00315
+pr_goods_base:G00694</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>e018</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Cabernet Sauvignon wine</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>와인 품종 검색</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>1. Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00113</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>e019</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Bread 10 Grain</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>빵 상품 검색 — 동명 상품 3개</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1. Bread - 10 Grain | G00563 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Bread - 10 Grain | G00817 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Bread - 10 Grain | G01005 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00563
+pr_goods_base:G00817
+pr_goods_base:G01005</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>e020</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Garlic Powder</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>향신료 검색 — 최저가 상품 중 하나 (1000원)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>1. Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00711</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>x2bee_conversational</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>X2BEE 이커머스 데이터에 대한 복합·대화형 질문 30개 — 멀티홉 추론, 조건부 집계, 자연어 필터, 비교, 추천 쿼리</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>id_field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>node_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Total queries</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>qid</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_count</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>c001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 15 Pro의 총 판매량이 얼마나 되나요?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>상품 → 판매이력 집계 (join + sum)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>c002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Shin Ramyun의 평균 리뷰 평점을 알려줘</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>상품 → 피드백 조인 + 평균</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>c003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2023년 12월 판매된 상품 건수는 몇 건이야?</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>sold_dtm 범위 필터 + count</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>1. SH0003377 | G00940 | 2.0 | 2024-01-07 17:02:57</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_sold_hist:SH0003377</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>c004</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>월별 매출 추이를 보여줘</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>sold_dtm 월별 그룹화</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>1. SH0003377 | G00940 | 2.0 | 2024-01-07 17:02:57</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_sold_hist:SH0003377</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>c005</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1만원 이상 와인 상품 중에서 리뷰가 10개 넘는 것은?</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>와인 + 가격 필터 + 리뷰 카운트 조건</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00751</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>c006</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>손님이 "매운 한국 라면 있어?" 라고 물으면 뭐라고 답해?</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>패러프레이즈 → Shin Ramyun 발견 + 추천</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>c007</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>전자제품 중에 제일 비싼 거 뭐야?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 15 Pro 최고가 (1,600,000원)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>c008</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>치즈 종류가 이 쇼핑몰에 몇 개나 있어?</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>cheese 포함 상품 카운트 (34개)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>1. Cheese - Fontina | A | G00020 | 2023-12-18 | Y | 9999.0 | 37000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Cheese - Provolone | G00040 | 2023-12-18 | Y | 9999.0 | 56000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Cheese - Gorgonzola | G00083 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Cheese - Mozzarella | G00158 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Cheese - Parmesan Cubes | G00442 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00020
+pr_goods_base:G00040
+pr_goods_base:G00083
+pr_goods_base:G00158
+pr_goods_base:G00442</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>c009</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>빵 제품이 몇 종류 있는지 확인해줘</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>bread 포함 상품 카운트 (31개)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>1. Bread - 10 Grain | G01005 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G01005</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>c010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>평점 5점을 받은 상품 중 가장 저렴한 것은?</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>리뷰 5점 + 상품 조인 + 최저가</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>1. Flour - Masa De Harina Mexican | G00857 | 2023-12-18 | Y | 9999.0 | 86000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00857</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>c011</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>1만원에서 5만원 사이 상품이 몇 개?</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>가격 범위 필터 (between)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>c012</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>판매량 TOP 3와 리뷰 수 TOP 3를 비교해줘</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>두 개의 집계 결과 비교</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Jacket | 남성 의류 | G00004 | 2024-12-19 | Y | 200.0 | 18500.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Bread - Kimel Stick Poly | G00472 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+6. Pork Ham Prager | G00389 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001
+pr_goods_base:G00004
+pr_goods_base:G00007
+pr_goods_base:G00751
+pr_goods_base:G00472
+pr_goods_base:G00389</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>c013</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>친구 생일 선물로 뭐가 좋을까? 5만원 이하로 추천해줘</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>가격 필터 + 추천 (리뷰 평점 고려)</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>c014</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Cheese 카테고리에서 리뷰가 가장 많은 상품은?</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>치즈 필터 + 리뷰 수 최대</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>1. Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00997</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>c015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Galaxy Book에 대한 리뷰 내용을 보여줘</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>cross_table</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>상품 → 리뷰 FK 조인</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>c016</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>유저당 평균 리뷰 작성 개수는?</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>user_id 집계 + 평균</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>c017</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2023년 여름(6-8월)에 팔린 상품 목록</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>날짜 범위 필터</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>1. SH0003377 | G00940 | 2.0 | 2024-01-07 17:02:57</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_sold_hist:SH0003377</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>c018</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>어떤 유저가 리뷰를 가장 많이 썼어?</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>user_id GROUP BY + 최대</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>c019</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>판매량 10개 이상 팔린 상품은 몇 개야?</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>sold_hist 집계 + HAVING count &gt;= 10</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>c020</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>초록 치즈 파스타에 어울리는 와인 추천해줘</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>패러프레이즈 + 조합 추천 (화이트 와인)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>1. Wine - Magnotta, White | G00077 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00077</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>c021</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>가장 많이 팔린 상품의 리뷰 평균 점수는?</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>판매량 1위 (G00001) → 리뷰 평균</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>c022</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>70000원 정확히 인 상품 있어?</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>가격 == 필터</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>1. Jacket | 남성 의류 | G00004 | 2024-12-19 | Y | 200.0 | 18500.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>c023</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>아이폰보다 저렴한 전자기기는?</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 가격 확인 후 비교 필터</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>c024</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>score 1점짜리 불만 리뷰는 몇 건?</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>score==1 필터 + count</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>c025</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>1점 리뷰를 가장 많이 받은 상품이 뭐야?</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>feedback where score=1 group by goods_no max</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00751</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>c026</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>아침 식사용으로 좋은 제품 3가지만 골라줘</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Bread/Muffin/Cheese/Coffee 카테고리</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>1. Bread - 10 Grain | G01005 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Pastry - Banana Muffin - Mini | G00992 | 2023-12-18 | Y | 9999.0 | 24000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Coffee - Almond Amaretto | G01009 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G01005
+pr_goods_base:G00992
+pr_goods_base:G01009</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>c027</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>재고가 200개 이하인 상품</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>sales_stock 필터</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007
+pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>c028</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Beer 카테고리 상품 11개의 총 판매량 합계는?</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>beer 필터 + 각 상품 판매량 집계 합산</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>1. Beer - Mill St Organic | G00270 | 2023-12-18 | Y | 9999.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00270
+pr_goods_base:G00974</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>c029</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>달달한 음료 찾고 있어. 뭐가 있을까?</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Cream Soda, Syrup, Liqueur 등 패러프레이즈</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>1. The Pop Shoppe - Cream Soda | G01007 | 2023-12-18 | Y | 9999.0 | 76000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Syrup - Pancake | G01003 | 2023-12-18 | Y | 9999.0 | 73000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G01007
+pr_goods_base:G01003</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>c030</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>재고가 가장 적은 상품의 리뷰 개수는?</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>최저 재고 → 상품 식별 → 리뷰 조인</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>x2bee_hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>X2BEE ai_lab_main 이커머스 고난이도 검색 GT — 패러프레이즈, FK조인, 필터, 집계, 멀티홉</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>id_field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>node_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Total queries</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>qid</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_count</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>h001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>프리미엄 스마트폰 최신 모델</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 15 Pro 512GB를 직접 언급하지 않고 의미로 검색</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>h002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>한국 즉석 라면 제품</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Shin Ramyun을 한국어 설명으로 검색</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>h003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>이탈리아 숙성 치즈 제품</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Provolone, Gorgonzola, Parmesan 등 이탈리아 치즈</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>1. Cheese - Provolone | G00040 | 2023-12-18 | Y | 9999.0 | 56000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Cheese - Gorgonzola | G00083 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Cheese - Parmesan Cubes | G00442 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Cheese - Mozzarella | G00158 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00040
+pr_goods_base:G00083
+pr_goods_base:G00442
+pr_goods_base:G00158</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>h004</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>portable computing device</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Galaxy Book을 영어 패러프레이즈로 검색</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>h005</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Dried Beef 판매 이력</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>cross_table</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>상품(pr_goods_base) → 판매이력(pr_goods_sold_hist) FK 조인</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>h006</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Cheese Pont Couvert 리뷰</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>cross_table</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>상품 → 피드백 FK 조인. 27건의 리뷰 존재</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>1. Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00997</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>h007</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 15 Pro 판매 기록은 몇 건인가?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>cross_table</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>상품 → 판매이력 FK + 건수 확인 (65건)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>h008</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>50만원 이상 고가 상품</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>price &gt;= 500000 필터. iPhone만 해당 (1,600,000원)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>h009</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>1000원짜리 최저가 상품</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>price = 1000 필터. 4개 상품</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>1. Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Plate Pie Foil | G00892 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00072
+pr_goods_base:G00302
+pr_goods_base:G00711
+pr_goods_base:G00892</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>h010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>5000원 이하 저가 상품 목록</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>price &lt;= 5000 필터. 41개 상품</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Chips Potato Swt Chilli Sour | G00063 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Amarula Cream | G00068 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Quail - Jumbo | G00089 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+6. Fudge - Chocolate Fudge | G00098 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+7. Pepper - Green Thai | G00202 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+8. Jam - Raspberry,jar | G00203 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+9. Oysters - Smoked | G00204 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+10. Soda Water - Club Soda, 355 Ml | G00217 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+11. Juice - Apple Cider | G00258 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+12. Scotch - Queen Anne | G00261 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+13. Soup - Campbells - Tomato | G00267 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+14. Chinese Foods - Chicken Wing | G00283 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+15. Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+16. Fondant - Icing | G00314 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+17. Nut - Walnut, Chopped | G00332 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+18. Otomegusa Dashi Konbu | G00376 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+19. Lettuce - Iceberg | G00388 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+20. Doilies - 8, Paper | G00438 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+... +21 more</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005
+pr_goods_base:G00063
+pr_goods_base:G00068
+pr_goods_base:G00072
+pr_goods_base:G00089
+pr_goods_base:G00098
+pr_goods_base:G00202
+pr_goods_base:G00203
+pr_goods_base:G00204
+pr_goods_base:G00217
+pr_goods_base:G00258
+pr_goods_base:G00261
+pr_goods_base:G00267
+pr_goods_base:G00283
+pr_goods_base:G00302
+pr_goods_base:G00314
+pr_goods_base:G00332
+pr_goods_base:G00376
+pr_goods_base:G00388
+pr_goods_base:G00438
+pr_goods_base:G00444
+pr_goods_base:G00492
+pr_goods_base:G00529
+pr_goods_base:G00554
+pr_goods_base:G00557
+pr_goods_base:G00583
+pr_goods_base:G00634
+pr_goods_base:G00635
+pr_goods_base:G00667
+pr_goods_base:G00688
+pr_goods_base:G00711
+pr_goods_base:G00738
+pr_goods_base:G00754
+pr_goods_base:G00768
+pr_goods_base:G00769
+pr_goods_base:G00778
+pr_goods_base:G00783
+pr_goods_base:G00787
+pr_goods_base:G00892
+pr_goods_base:G00965
+pr_goods_base:G01009</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>h011</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>가장 많이 팔린 상품 TOP 3</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>sold_qunt SUM GROUP BY goods_no. Dried Beef(83), Jacket(74), iPhone(69)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Jacket | 남성 의류 | G00004 | 2024-12-19 | Y | 200.0 | 18500.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001
+pr_goods_base:G00004
+pr_goods_base:G00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>h012</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>리뷰가 가장 많은 상품 TOP 5</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>feedback COUNT GROUP BY goods_no. Wiberg(29), Bread Kimel(28), Pork Ham(28), Sauce Ranch(27), Cheese Pont(27)</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Bread - Kimel Stick Poly | G00472 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Pork Ham Prager | G00389 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Sauce - Ranch Dressing | G00329 | 2023-12-18 | Y | 9999.0 | 88000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00751
+pr_goods_base:G00472
+pr_goods_base:G00389
+pr_goods_base:G00329
+pr_goods_base:G00997</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>h013</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>맥주 종류가 총 몇 개인가?</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Beer 포함 상품 COUNT = 11개</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>1. Beer - Mill St Organic | G00270 | 2023-12-18 | Y | 9999.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Beer - Sleemans Honey Brown | G00466 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Beer - Original Organic Lager | G00645 | 2023-12-18 | Y | 9999.0 | 73000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Beer - Moosehead | G00700 | 2023-12-18 | Y | 9999.0 | 87000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Beer - Original Organic Lager | G00719 | 2023-12-18 | Y | 9999.0 | 74000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+6. Beer - Steamwhistle | G00793 | 2023-12-18 | Y | 9999.0 | 33000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+7. Beer - Original Organic Lager | G00798 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+8. Beer - Rickards Red | G00928 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+9. Beer - Mcauslan Apricot | G00937 | 2023-12-18 | Y | 9999.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+10. Beer - Steamwhistle | G00938 | 2023-12-18 | Y | 9999.0 | 63000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+11. Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00270
+pr_goods_base:G00466
+pr_goods_base:G00645
+pr_goods_base:G00700
+pr_goods_base:G00719
+pr_goods_base:G00793
+pr_goods_base:G00798
+pr_goods_base:G00928
+pr_goods_base:G00937
+pr_goods_base:G00938
+pr_goods_base:G00974</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>h014</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>5점 리뷰를 가장 많이 받은 상품의 가격은?</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>feedback(score=5) 집계 → 상품 조회 → 가격 확인. Flour Masa De Harina(11건 5점, 가격 확인 필요)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>1. Flour - Masa De Harina Mexican | G00857 | 2023-12-18 | Y | 9999.0 | 86000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00857</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>h015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>판매량 1위 상품의 리뷰 평점은?</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>sold_hist 집계(G00001 Dried Beef=83개) → feedback 평점 확인</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>h016</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>이 쇼핑몰에서 와인이 몇 종류나 있어?</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Wine 포함 상품 COUNT. 80+ 종류</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>1. Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Wine - Piper Heidsieck Brut | G00034 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Wine - Sicilia Igt Nero Avola | G00048 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+4. Wine - Champagne Brut Veuve | G00055 | 2023-12-18 | Y | 9999.0 | 10000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+5. Wine - Magnotta, White | G00077 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+6. Wine - Winzer Krems Gruner | G00086 | 2023-12-18 | Y | 9999.0 | 75000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+7. Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+8. Wine - Red, Cabernet Merlot | G00112 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+9. Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+10. Wine - Fino Tio Pepe Gonzalez | G00138 | 2023-12-18 | Y | 9999.0 | 64000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+11. Wine - Tribal Sauvignon | G00144 | 2023-12-18 | Y | 9999.0 | 38000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+12. Wine - Delicato Merlot | G00148 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+13. Wine - Pinot Grigio Collavini | G00164 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+14. Wine - Red, Pinot Noir, Chateau | G00172 | 2023-12-18 | Y | 9999.0 | 48000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+15. Wine La Vielle Ferme Cote Du | G00174 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+16. Wine - Rubyport | G00207 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+17. Wine - Rosso Del Veronese Igt | G00264 | 2023-12-18 | Y | 9999.0 | 54000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+18. Wine - Wyndham Estate Bin 777 | G00277 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+19. Wine - Chateauneuf Du Pape | G00282 | 2023-12-18 | Y | 9999.0 | 29000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+20. Wine - Casablanca Valley | G00293 | 2023-12-18 | Y | 9999.0 | 12000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+... +10 more</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00010
+pr_goods_base:G00034
+pr_goods_base:G00048
+pr_goods_base:G00055
+pr_goods_base:G00077
+pr_goods_base:G00086
+pr_goods_base:G00106
+pr_goods_base:G00112
+pr_goods_base:G00113
+pr_goods_base:G00138
+pr_goods_base:G00144
+pr_goods_base:G00148
+pr_goods_base:G00164
+pr_goods_base:G00172
+pr_goods_base:G00174
+pr_goods_base:G00207
+pr_goods_base:G00264
+pr_goods_base:G00277
+pr_goods_base:G00282
+pr_goods_base:G00293
+pr_goods_base:G00306
+pr_goods_base:G00330
+pr_goods_base:G00333
+pr_goods_base:G00339
+pr_goods_base:G00379
+pr_goods_base:G00402
+pr_goods_base:G00405
+pr_goods_base:G00424
+pr_goods_base:G00449
+pr_goods_base:G00462</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>h017</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>신라면이 잘 팔리나요?</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Shin Ramyun(G00005) 판매이력 확인. 45개 판매로 5위</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>h018</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>양고기 제품 중 뼈 없는 것</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Lamb + Boneless 필터</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>1. Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Lamb - Loin, Trimmed, Boneless | G00492 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+3. Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00470
+pr_goods_base:G00492
+pr_goods_base:G00736</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>h019</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>facial skincare product</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>CLA Mask를 영어 카테고리로 검색</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1. CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
+2. Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>pr_goods_base:G00002
+pr_goods_base:G00006</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>h020</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>유저 한 명이 작성한 리뷰 수는 최대 몇 건?</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>user_id GROUP BY COUNT MAX = 23건</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1338,6 +4687,1358 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>assort_conversational</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>assort 패션 이커머스 데이터에 대한 복합·대화형 질문 30개 — 리뷰 감성, 사이즈/핏, 시즌 조합, 쇼핑 추천</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>id_field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>node_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Total queries</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>qid</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_count</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>c001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>이번 시즌(25SS)에 몇 벌이나 나왔어?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>season = 25SS 카운트 (29개)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+2. 25SS 코튼 스트라이프 라운드넥 티셔츠 | LBL 시즌2025 S/S NO.1 | 25SS | 12800002 | 19900.0 | 2406 | 47879400.0
+3. 25SS 코튼 스트라이프 라운드넥 티셔츠 | LBL 시즌2024 F/W NO.2 | 25SS | 12800008 | 89900.0 | 40.0 | 6424 | 577517600.0
+4. 25SS 쉬폰 프릴 페플럼 블라우스 | LBL 시즌2024 F/W NO.3 | 25SS | 12800010 | 49900.0 | 50.0 | 5162 | 257583800.0</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000
+products:12800002
+products:12800008
+products:12800010</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>c002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>10만원 이하 티셔츠 추천해줘</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>price &lt;= 100000 + 티셔츠</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 코튼 스트라이프 라운드넥 티셔츠 | LBL 시즌2025 S/S NO.1 | 25SS | 12800002 | 19900.0 | 2406 | 47879400.0</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>products:12800002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>c003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>가장 판매량 많은 상품의 평균 리뷰 평점은?</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>cumulative_sales TOP + review 평균</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>c004</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>사이즈가 크다는 리뷰가 많은 상품 있어?</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>review_sentiment</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>size_satisfaction=큼 + product 집계</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>c005</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>봄에 입기 좋은 니트 뭐가 있을까?</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>25SS + 니트 필터</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+2. 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0
+3. 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2024 S/S NO.1 | 24SS | 12800011 | 59900.0 | 2372 | 142082800.0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000
+products:12800004
+products:12800011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>c006</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>결혼식 하객으로 입기 좋은 원피스?</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>원피스 + 고가 제품 추천</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>1. 24FW 저지 랩 원피스 | LBL 시즌2024 F/W NO.1 | 24FW | 12800016 | 19900.0 | 10.0 | 1798 | 35780200.0</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>products:12800016</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>c007</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>할인율 20% 이상 상품 중 누적 판매량 3000개 넘는 것</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>discount_rate + cumulative_sales 복합 필터</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+2. 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000
+products:12800004</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>c008</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>색상별로 몇 개의 상품 variant이 있어?</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>product_variants GROUP BY color_id</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>1. 소라 | 1
+2. 그린 | 2
+3. 베이지 | 3</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>colors:1
+colors:2
+colors:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>c009</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>실크블렌드 가디건의 모든 사이즈 버전</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>cross_table</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>products → product_variants 조인</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>c010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>55사이즈로 예쁜 거 뭐 있어?</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>size=55 variant + product 조인</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>1. 55 | 2</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>sizes:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>c011</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>"촉감이 좋다"는 리뷰가 있는 상품은?</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>review_sentiment</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>review_content contains 촉감</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>c012</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>어느 시즌 상품이 가장 많이 팔려?</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>season GROUP BY + SUM cumulative_sales</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+2. 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000
+products:12800001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>c013</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>5만원 미만 상품 전부 보여줘</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>selling_price &lt; 50000</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 코튼 스트라이프 라운드넥 티셔츠 | LBL 시즌2025 S/S NO.1 | 25SS | 12800002 | 19900.0 | 2406 | 47879400.0
+2. 24SS 스웨이드 A라인 미니 스커트 | LBL 시즌2024 F/W NO.1 | 24SS | 12800003 | 19900.0 | 40.0 | 3691 | 73450900.0
+3. 25SS 쉬폰 프릴 페플럼 블라우스 | LBL 시즌2024 F/W NO.3 | 25SS | 12800010 | 49900.0 | 50.0 | 5162 | 257583800.0</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>products:12800002
+products:12800003
+products:12800010</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>c014</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>방송 판매된 상품 중 가장 누적 매출이 큰 것은?</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>broadcasts 조인 + cumulative_amount 최대</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>c015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>엄마 선물로 괜찮은 블라우스 있을까?</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>블라우스 + 고가(품질) 추천</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>1. 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0
+2. 25SS 모달 레이스 트리밍 블라우스 | LBL 시즌2024 F/W NO.3 | 25SS | 12800013 | 69900.0 | 20.0 | 5007 | 349989300.0
+3. 25SS 모달 레이스 트리밍 블라우스 | LBL 시즌2024 F/W NO.1 | 25SS | 12800015 | 89900.0 | 30.0 | 706 | 63469400.0</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>products:12800005
+products:12800013
+products:12800015</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>c016</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>상품당 평균 리뷰 개수는?</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>reviews GROUP BY product_code + avg</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>c017</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>핑크 색상 variant이 있는 상품은?</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>colors:핑크 → variant → product</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>c018</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>재구매 후기가 있는 상품은?</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>review_sentiment</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>review_content contains 재구매</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>c019</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>24SS 시즌 상품 중에 가장 비싼 것</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>season=24SS + max price</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1. 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
+2. 24SS 린넨 와이드 밴딩 슬랙스 | LBL 시즌2025 S/S NO.1 | 24SS | 12800009 | 99900.0 | 20.0 | 4416 | 441158400.0</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>products:12800001
+products:12800009</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>c020</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>이번주 홈쇼핑 방송 예정 상품 있어?</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>broadcasts 최신 + 상품</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>1. 1 | 12800000 | 2024-11-15 | 23:00-23:50 | 2024-11-20 | 2024-11-28</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>broadcasts:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>c021</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>평균 할인율이 얼마야?</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>discount_rate 평균</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>c022</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>30% 이상 할인 중인 상품 중 25SS 신상은?</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>discount + season 복합 필터</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>c023</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>12800000 상품에 대해 알려진 모든 정보</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>cross_table</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>product + variants + reviews + broadcasts + sales 통합</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>c024</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>스커트 종류 뭐가 있어?</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>product_name contains 스커트</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>1. 24SS 시폰 플리츠 롱 스커트 | LBL 시즌2024 S/S NO.3 | 24SS | 12800001 | 99900.0 | 1862 | 186013800.0
+2. 24SS 스웨이드 A라인 미니 스커트 | LBL 시즌2024 F/W NO.1 | 24SS | 12800003 | 19900.0 | 40.0 | 3691 | 73450900.0
+3. 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>products:12800001
+products:12800003
+products:12800006</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>c025</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>블랙 컬러가 들어간 variant 개수는?</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>colors:블랙 → variant 카운트</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>1. 블랙 | 5</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>colors:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>c026</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>엄마 선물로 샀다는 리뷰가 달린 상품 목록</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>review_sentiment</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>review_content contains 엄마</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>c027</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>가성비 좋은 걸로 3개만 추천해줘</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>가격 저렴 + 판매량 많음 조합</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 코튼 스트라이프 라운드넥 티셔츠 | LBL 시즌2025 S/S NO.1 | 25SS | 12800002 | 19900.0 | 2406 | 47879400.0
+2. 24SS 스웨이드 A라인 미니 스커트 | LBL 시즌2024 F/W NO.1 | 24SS | 12800003 | 19900.0 | 40.0 | 3691 | 73450900.0</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>products:12800002
+products:12800003</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>c028</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>FREE 사이즈 상품은 몇 가지 색상이 있어?</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>sizes:FREE → variant → color 집계</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>1. FREE | 6</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>sizes:6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>c029</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>24FW 가을/겨울 신상품 목록</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>season = 24FW</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>1. 24FW 모달 레이스 트리밍 블라우스 | LBL 시즌2024 S/S NO.1 | 24FW | 12800005 | 79900.0 | 20.0 | 3327 | 265827300.0
+2. 24FW 데님 A라인 미디 스커트 | LBL 시즌2024 S/S NO.3 | 24FW | 12800006 | 69900.0 | 4314 | 301548600.0
+3. 24FW 저지 랩 원피스 | LBL 시즌2024 F/W NO.1 | 24FW | 12800016 | 19900.0 | 10.0 | 1798 | 35780200.0</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>products:12800005
+products:12800006
+products:12800016</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>c030</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>오늘 뭘 사면 좋을지 추천해줄래?</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>cumulative_sales 상위 + 할인 조합</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1. 25SS 실크블렌드 플라워 아플리케 가디건+하프니트 앙상블 | LBL 시즌2024 S/S NO.2 | 25SS | 12800000 | 59900.0 | 10.0 | 2926 | 175267400.0
+2. 24SS 울 캐시미어 브이넥 니트 | LBL 시즌2025 S/S NO.1 | 24SS | 12800004 | 89900.0 | 40.0 | 4547 | 408775300.0</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>products:12800000
+products:12800004</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2091,7 +6792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3234,7 +7935,1627 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>krra_conversational</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KRRA 경마/말산업 문서에 대한 복합·대화형 질문 30개 — 패러프레이즈, 교차문서, 필터, 멀티홉</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>id_field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>doc_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Total queries</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Answer resolved?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YES — see relevant_answer column</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>qid</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>query</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_count</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_answer</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>relevant_docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>c001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>경마 시행 운영 계획을 요약해줘</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['경마시행', '운영계획']</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>1. 2023년도_썸즈업 워터페스티벌 요약_최종 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023년 계묘년 신년 및 설맞이 고객사은 행사 시행    작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-04 10:42:29   수정일: 2023-06-08 16:26:23 &lt;/Document-Me…
+2. 2024년도_24년 11월 서울 부경 경마시행계획_v5_241012 #26  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-10-12 15:14:53 …
+3. 2020년도_2020년 팀제 운영계획_최종 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-12-28 16:28:13   수정일: 2020-05-08 09:59:45 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+4. 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-Metadata&gt;  (치료) 복지중심 의료서비스 지원 강…
+5. 2024년도_24년 5월 서울 부경 경마시행계획 v7 #24  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-04-17 17:46:10 …</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>06a77998947ddb80
+0ac3271720f05406
+0ac741faaa2da029
+156fec294ba67ae4
+1b3a2926650166e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>c002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>말 산업 장기 발전 방안은?</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['말산업', '발전계획']</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_(요약) 자율주행 트랙터 개발·도입 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-05-17 12:51:23   수정일: 2023-08-17 11:00:09 &lt;/Document-Metadata&gt;  비, 제석, 예취, 파종 등 제반 초지관리 작업 수…
+2. 2023년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-Metadata&gt;  * 산업형(100% NCS 적용) 채…
+3. 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-Metadata&gt;  === Extracted Images…
+4. 2024년도_2. 2024년도 말산업실태조사 추진계획(안) #27  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2016-01-12 09:37:29   수정일: 2024-05-30 11:19:34 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp_BIN00…
+5. 2024년도_1. (제24-10호) 말산업 관련 자격시험 관리규정 일부 개정(안) #19  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2020-05-24 10:48:12   수정일: 2024-03-10 09:25:42 &lt;/Document-Metadata&gt;  &lt;table borde…</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>027e0c5f0f5686c0
+1c2e14b3e46641c4
+1dd7a41b6d49067a
+2eaa8a7351dbfb3c
+2eede8200e1e0db8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>c003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>온라인 도박 단속 대응 방침</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['불법경마', '사설경마']</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_지사, 문화센터 홈페이지 개편 계획(안)_240526(수정) #11  ▸  &lt;Document-Metadata&gt;   제목: □ 통합신고센터 운영개선을 통해 불법경마 신고접수 전문인력 양성   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-24 13:51:43   수정일: 2024-05-26 09:42:09 &lt;/Docume…
+2. 2020년도_불법경마사이트 신고 활성화를 위한 고객신고 제도 분석 및 운영 개선(안) #9  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-04 16:43:55   수정일: 2020-01-19 13:58:22 &lt;/Document-Metadata&gt;  시 (2분기)     ※ 불법경마 대…
+3. 2022년도_[붙임] 「불법경마 신고포상금 지급 등에 관한 규정」 일부 개정안 #0  ▸  &lt;Document-Metadata&gt;   제목: 경주정보 불법 송출   작성자: KRA   마지막 수정자: KRA   작성일: 2022-07-09 19:23:20   수정일: 2022-12-04 15:24:16 &lt;/Document-Metadata&gt;  『불법경마 신고포상금…
+4. 2022년도_2022년 불법경마 신고포상금 제도 개선계획(안) #32  ▸  &lt;Document-Metadata&gt;   제목: 경주정보 불법 송출   작성자: KRA   마지막 수정자: KRA   작성일: 2022-07-09 19:23:20   수정일: 2022-11-03 17:25:49 &lt;/Document-Metadata&gt;  자 불편 방지 위해 …
+5. 2020년도_2020년 불법사설경마 대응계획(안) #10  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-15 18:10:24   수정일: 2020-02-26 15:34:04 &lt;/Document-Metadata&gt;  &lt;table border='1'…</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>27e3f288a3dda838
+455c41ea7d950aff
+4e67027b23247ea7
+8170c85ae9a0a3cb
+855606d43a06c210</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>c004</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>탄소 중립을 위한 친환경 전략</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['ESG', '지속가능', '탄소']</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>1. 2023년도_[붙임] 2023년 지사 ESG 추진계획(230827_최종) #5  ▸  &lt;Document-Metadata&gt;   제목: 2015   작성자: KRA   마지막 수정자: KRA   작성일: 2016-02-11 13:58:39   수정일: 2023-08-27 14:31:28 &lt;/Document-Metadata&gt;  &lt;table border='1'…
+2. 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt;…
+3. 2022년도_[별첨1] KRA-ESG경영 진단모델(세부 진단기준)_최종 #43  ▸  &lt;Document-Metadata&gt;   제목: 《 KRA   작성자: KRA   마지막 수정자: KRA   작성일: 2022-11-04 14:33:57   수정일: 2023-05-27 10:21:04 &lt;/Document-Metadata&gt;  &lt;table border='1…
+4. 2024년도_(요약) 2024년 윤리경영 추진계획(안) (1) #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-05-30 11:08:03 &lt;/Document-Metadata&gt;  □ CEO 주도의 윤리경영 활동 및 …
+5. 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Document-Metadata&gt;  &lt;table border='1'…</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>0f20c1821479c167
+1002c0855b631621
+123f03df3479517e
+2c473c597114e075
+329af5c7de78350a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>c005</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>직원 복리후생 개선 계획</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['복지', '직원']</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Document-Metadata&gt;  (단, 사업담당자의 재량으로 지…
+2. 2022년도_(붙임1) 인사규정시행세칙 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-04-16 10:59:14   수정일: 2023-09-08 11:10:39 &lt;/Document-Metadata&gt;  ※ 작성방법 : 점검결과에 ‘적정’ 또는 ‘부적정’…
+3. 2020년도_2020년 팀제 운영계획_최종 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-12-28 16:28:13   수정일: 2020-05-08 09:59:45 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+4. 2024년도_(붙임 1) 제출서류 양식 및 작성요령 #0  ▸  &lt;Document-Metadata&gt;   제목: 【서식 1】    작성자: KRA   마지막 수정자: KRA   작성일: 2022-12-03 16:20:03   수정일: 2024-03-08 16:26:59 &lt;/Document-Metadata&gt;  【참 고】    추천서식 …
+5. 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-Metadata&gt;  6) 추진일정    - 프로그램별 세…</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>0346542e0be2b2ab
+03e46e426c5e0a40
+0ac741faaa2da029
+0bffcf8f8dc55f5f
+0fdd2b845b06532f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>c006</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>내년도 경마 대회 일정은 어떻게 돼?</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['경마시행계획', '대회']</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_(요약)`22년 경마시행계획 #16  ▸  &lt;Document-Metadata&gt;   제목: 20년 잔여기간 목요경마 시행    작성자: KRA   마지막 수정자: KRA   작성일: 2020-05-22 17:24:33   수정일: 2021-12-26 14:14:00 &lt;/Document-Metadata&gt;  === …
+2. 2024년도_24년 11월 서울 부경 경마시행계획_v5_241012 #26  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-10-12 15:14:53 …
+3. 2024년도_(붙임) 제13회 국산 어린말 승마대회 개최계획 #10  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-20 16:38:53 &lt;/Document-Metadata&gt;  소요예산 : 66백만원    예…
+4. 2024년도_24년 5월 서울 부경 경마시행계획 v7 #24  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-04-17 17:46:10 …
+5. 2024년도_24년 12월 서울 부경 경마시행계획 v4 _ 241107 #26  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-11-10 12:21:03 …</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>068eb0be1021da16
+0ac3271720f05406
+140155f6377c6ed1
+1b3a2926650166e0
+294a5acf52548d54</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>c007</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>말 복지를 위해 어떤 프로그램을 운영하나요?</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['말복지', '승마']</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>1. 2023년도_2-1 812.승마지도사 자격 인정 등에 관한 규정_개정전문 #35  ▸  &lt;Document-Metadata&gt;   제목: 제1장  총    칙   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-04-28 09:00:57   수정일: 2024-03-23 13:41:22 &lt;/Document-Metadat…
+2. 2024년도_(붙임 1) 제1회 국산마 품평회 개최계획 #18  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-15 17:31:04   수정일: 2024-06-19 17:49:01 &lt;/Document-Metadata&gt;  소요예산 : 97,200천원  …
+3. 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-Metadata&gt;  (치료) 복지중심 의료서비스 지원 강…
+4. 2020년도_붙임_2_2020년 도심승마체험 시행계획(본문, 최종) #55  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2019-01-09 13:50:33   수정일: 2020-03-11 10:31:15 &lt;/Document-Metadata&gt;  === Extracted Images…
+5. 2022년도_제51회 한국마사회장배 전국승마대회 개최계획(안)-확정 #28  ▸  &lt;Document-Metadata&gt;   작성자: Letsrun   마지막 수정자: KRA   작성일: 2018-01-11 08:28:26   수정일: 2023-02-25 11:53:53 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; …</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>07c4de1cc000e7e8
+133dd2fda4f7c41d
+156fec294ba67ae4
+1dd7a41b6d49067a
+29c493103f7c509c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>c008</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>올해 예산은 어떻게 편성됐어요?</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['예산', '편성']</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>1. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+2. 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-Metadata&gt;  □ 추진기간 : 2021. 6월 ∼ …
+3. 2020년도_201020 지사 고객입장 및 방역관리 방안(최종) #25  ▸  &lt;Document-Metadata&gt;   제목: 2020   작성자: KRA   마지막 수정자: KRA   작성일: 2020-10-16 08:23:47   수정일: 2020-10-20 18:44:49 &lt;/Document-Metadata&gt;  [Image:temp/image…
+4. 2023년도_스마트 사무환경 구축(요약보고) #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2023-08-18 09:24:44 &lt;/Document-Metadata&gt;  전환에 대비한 시공간 제약 없는 원격…
+5. 2024년도_(별첨) 정부보조금 사업 무전표시스템 매뉴얼 #0  ▸  &lt;Document-Metadata&gt;   제목: ※ GL계정    작성자: user   마지막 수정자: KRA   작성일: 2015-09-10 17:14:26   수정일: 2024-05-04 16:17:22 &lt;/Document-Metadata&gt;  &lt;보조금사업 무전표시스템…</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>0f9e1947b0221b27
+2e907c84c2a15612
+36f5479362d3d864
+3d8c8292183997c8
+3dd0576c06bdadd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>c009</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>인권 경영 관련 자료 있어?</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['인권경영', '인권']</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>1. 2023년도_붙임3 2023년 기관운영 인권영향평가 체크리스트(최종) #104  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-09-20 01:25:07   수정일: 2023-12-21 06:47:49 &lt;/Document-Metadata&gt;  [Sheet: 11. 직장 내 인권보호] [Tabl…
+2. 2023년도_붙임4 2023년 주요사업 인권영향평가 체크리스트(최종) #29  ▸  &lt;Document-Metadata&gt;   작성자: USER   마지막 수정자: KRA   작성일: 2018-09-04 19:31:17   수정일: 2023-12-21 06:44:31 &lt;/Document-Metadata&gt;  [Sheet: 교육, 강습 및 기타 사업] [Ta…
+3. 2022년도_한국마사회 ESG경영부 2022년 인권경영 이행실적 보고서 견적서 #1  ▸  &lt;Document-Metadata&gt;   작성자: Administrator   마지막 수정자: 이주훈   작성일: 2012-01-19 08:40:24   수정일: 2023-06-18 09:36:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt;…
+4. 2022년도_(제23-11호) 인권경영 실행지침 일부 개정(안) #4  ▸  &lt;Document-Metadata&gt;   제목: 신명조 17 pt   작성자: KRA   마지막 수정자: KRA   작성일: 2017-03-04 09:10:19   수정일: 2023-04-23 10:51:13 &lt;/Document-Metadata&gt;  동과 아동노동도 허용하…
+5. 2024년도_(붙임) 2024년 인권경영 기본계획(안)_240414★ #2  ▸  &lt;Document-Metadata&gt;   제목: 추진배경   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-05 11:22:01   수정일: 2024-04-16 16:56:55 &lt;/Document-Metadata&gt;  &lt;table border='1'…</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>005599102a43b8f4
+0cf478ddca6e92d5
+1002c0855b631621
+2520e4f72ad580ae
+329af5c7de78350a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>c010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>경주마 국제 레이팅 현황을 알려줘</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['레이팅', '경주마']</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2020년도_1. 경주마위치추적시스템_운영관리용역_기본계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2020-05-24 16:03:22 &lt;/Document-Metadata&gt;  `2…
+3. 2022년도_첨부1_2022년 한국 대상경주 레이스 레이팅 총괄(연말최종) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-12-28 05:32:05   수정일: 2022-12-16 01:40:34 &lt;/Document-Metadata&gt;  [Sheet: Sheet1] [Table Chunk…
+4. 2023년도_(요약) 23년 국제경주(코리아컵 코리아스프린트) 시행계획 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-04-28 10:50:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+5. 2021년도_(2021) 제 99주년 경마의 날 기념식 시행계획(안)_요약보고 #0  ▸  &lt;Document-Metadata&gt;   작성자: Owner   마지막 수정자: KRA   작성일: 2008-04-15 17:25:03   수정일: 2021-05-08 14:10:03 &lt;/Document-Metadata&gt;  제 99주년 경마의 날 기념식 시행 (안) 보고…</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>012dcbe84f52c595
+05889d5822d0109f
+110f8ff7eb5dbdc1
+134ceaf0ae1ba751
+1ff851c7c3ee9eb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>c011</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>경마 운영과 복지 프로그램의 연관성</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>cross_document</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['경마운영', '복지']</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Document-Metadata&gt;  (단, 사업담당자의 재량으로 지…
+2. 2024년도_2024년 기부금 지원공모사업(안) #14  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2015-10-08 19:55:17   수정일: 2024-08-10 11:00:13 &lt;/Document-Metadata&gt;  6) 추진일정    - 프로그램별 세…
+3. 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-Metadata&gt;  (치료) 복지중심 의료서비스 지원 강…
+4. 2020년도_경주마 통합 건강관리시스템 추진계획(안) #19  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2020-05-27 10:31:20 &lt;/Document-Metadata&gt;  === Extracted Images…
+5. 2024년도_2. 2024년 경주마 토탈 케어시스템 운영 계획(안) 1부 #23  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-02-04 09:56:05 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr…</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>0346542e0be2b2ab
+0fdd2b845b06532f
+156fec294ba67ae4
+2d94f6c769030bda
+4f2b02c85a84bf0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>c012</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>마주 경제기준 변경과 경마시행의 관계</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>cross_document</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['마주', '경제', '경마시행']</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2024년도_(붙임 2) 2024 말용도 다각화 추진계획_본문 #12  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-01 17:42:54 &lt;/Document-Metadata&gt;  (단, 사업담당자의 재량으로 지…
+3. 2021년도_(붙임4)2021년 건전화 평가 실적 보고서 양식 #35  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-06-06 17:25:17   수정일: 2021-06-17 11:52:21 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp_BIN01…
+4. 2024년도_24년 11월 서울 부경 경마시행계획_v5_241012 #26  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-10-12 15:14:53 …
+5. 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-Metadata&gt;  (치료) 복지중심 의료서비스 지원 강…</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>012dcbe84f52c595
+0346542e0be2b2ab
+0a863b5949be411e
+0ac3271720f05406
+156fec294ba67ae4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>c013</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>교배 실적과 생산 현황의 관계</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>cross_document</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['교배', '생산']</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2020년도_1. 경주마위치추적시스템_운영관리용역_기본계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2020-05-24 16:03:22 &lt;/Document-Metadata&gt;  `2…
+3. 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:50:21 &lt;/Document-Metadata&gt;  20…
+4. 2020년도_2020년 팀제 운영계획_최종 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-12-28 16:28:13   수정일: 2020-05-08 09:59:45 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+5. 2024년도_(붙임 1) 제1회 국산마 품평회 개최계획 #18  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-15 17:31:04   수정일: 2024-06-19 17:49:01 &lt;/Document-Metadata&gt;  소요예산 : 97,200천원  …</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>012dcbe84f52c595
+05889d5822d0109f
+08dbb848822964aa
+0ac741faaa2da029
+133dd2fda4f7c41d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>c014</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>R&amp;D 연구 과제와 중장기 발전 계획 연계</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>cross_document</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['R&amp;D', '연구', '중장기']</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_(요약) 자율주행 트랙터 개발·도입 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-05-17 12:51:23   수정일: 2023-08-17 11:00:09 &lt;/Document-Metadata&gt;  비, 제석, 예취, 파종 등 제반 초지관리 작업 수…
+2. 2023년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-Metadata&gt;  * 산업형(100% NCS 적용) 채…
+3. 2024년도_★(본문) 2024년 이사회 운영 계획(안) #12  ▸  &lt;Document-Metadata&gt;   제목: 일자리 창출 중장기 계획   작성자: KRA   마지막 수정자: KRA   작성일: 2017-09-12 12:21:29   수정일: 2024-09-12 17:29:08 &lt;/Document-Metadata&gt;  &lt;table b…
+4. 2023년도_붙임 1. 2023년 학교체육 승마 시범사업 운영계획(안) #35  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2021-11-04 14:57:12   수정일: 2022-12-02 16:28:09 &lt;/Document-Metadata&gt;  * 학교별 전·출입 인원을 감안하여 5% 범위에서 …
+5. 2020년도_200828_언택트발매추진단 하반기 사업계획 및 예산 #4  ▸  &lt;Document-Metadata&gt;   제목: Ⅰ   작성자: KRA   마지막 수정자: KRA   작성일: 2020-07-21 12:13:34   수정일: 2020-08-28 13:15:23 &lt;/Document-Metadata&gt;  및 말산업 생태계 보존     (이용…</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>027e0c5f0f5686c0
+1c2e14b3e46641c4
+1da3f1fef69b9b0e
+230b3c89a0f6cfdc
+23f259fe9f9c25d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>c015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>승용마 번식 지원과 말산업 활성화</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>cross_document</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['승용마', '번식', '말산업']</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_(요약) 자율주행 트랙터 개발·도입 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-05-17 12:51:23   수정일: 2023-08-17 11:00:09 &lt;/Document-Metadata&gt;  비, 제석, 예취, 파종 등 제반 초지관리 작업 수…
+2. 2021년도_[붙임2] 2021년 일반말 등록업무 추진 계획(안) #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-31 13:09:52   수정일: 2021-03-13 11:35:26 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td …
+3. 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:50:21 &lt;/Document-Metadata&gt;  20…
+4. 2024년도_(붙임 1) 제1회 국산마 품평회 개최계획 #18  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-15 17:31:04   수정일: 2024-06-19 17:49:01 &lt;/Document-Metadata&gt;  소요예산 : 97,200천원  …
+5. 2024년도_(붙임) 제13회 국산 어린말 승마대회 개최계획 #10  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-20 16:38:53 &lt;/Document-Metadata&gt;  소요예산 : 66백만원    예…</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>027e0c5f0f5686c0
+048a00f4ea8e90a9
+08dbb848822964aa
+133dd2fda4f7c41d
+140155f6377c6ed1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>c016</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2023년에 수립된 추진 계획들</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['2023년', '추진계획']</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+3. 2023년도_(요약) 23년 국제경주(코리아컵 코리아스프린트) 시행계획 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-04-28 10:50:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+4. 2023년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp…
+5. 2023년도_도핑검사용 분석장비 도입 계획(안) #15  ▸  &lt;Document-Metadata&gt;   제목: 2023   작성자: KRA   마지막 수정자: KRA   작성일: 2023-04-26 11:12:59   수정일: 2024-04-21 16:47:10 &lt;/Document-Metadata&gt;  □ 준비 사항    ○ 배치 공…</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>012dcbe84f52c595
+0f9e1947b0221b27
+134ceaf0ae1ba751
+19fe4e04b9ae46af
+20ce77daff008e50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>c017</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2024년 경마 시행 관련 문서</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['2024년', '경마시행']</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_24년 11월 서울 부경 경마시행계획_v5_241012 #26  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-10-12 15:14:53 …
+2. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+3. 2024년도_★ (본문) 2024년 부경 경주마 보건복지 고도화 계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2024-05-04 14:09:56 &lt;/Document-Metadata&gt;  (치료) 복지중심 의료서비스 지원 강…
+4. 2023년도_붙임1.2024년 업무용 정보화기기 도입 계획(안) #0  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2024-05-26 17:28:25 &lt;/Document-Metadata&gt;  [Image:temp/images/hwp…
+5. 2024년도_(입찰공고문) 스마트 조교정보시스템 구축 #9  ▸  &lt;Document-Metadata&gt;   제목: 입찰공고문   마지막 수정자: KRA   작성일: 2007-05-20 11:05:36   수정일: 2024-05-10 17:36:20 &lt;/Document-Metadata&gt;  제출서류는 계약서에 특별히 명기하는 내용 외에는 …</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>0ac3271720f05406
+0f9e1947b0221b27
+156fec294ba67ae4
+19fe4e04b9ae46af
+1ab7e770624479a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>c018</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>농림부 관련 대회 계획</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['농림부', '대회']</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_(붙임) 제13회 국산 어린말 승마대회 개최계획 #10  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-06-20 16:38:53 &lt;/Document-Metadata&gt;  소요예산 : 66백만원    예…
+2. 2022년도_제51회 한국마사회장배 전국승마대회 개최계획(안)-확정 #28  ▸  &lt;Document-Metadata&gt;   작성자: Letsrun   마지막 수정자: KRA   작성일: 2018-01-11 08:28:26   수정일: 2023-02-25 11:53:53 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; …
+3. 2023년도_(붙임1) 2023년 어린말 승마대회 추진계획(요약) #2  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2022-04-28 13:07:00   수정일: 2023-04-27 14:10:13 &lt;/Document-Metadata&gt;  경우 참가가능   □ (위원위촉) 심판위원 5~6명…
+4. 2024년도_(붙임 1-2) 2024 어린말 승마대회 추진계획_본문 #38  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-04-19 11:25:07 &lt;/Document-Metadata&gt;  * 원활한 대회 운영을 위하여 …
+5. 2024년도_(붙임 1-2) 2024년 어린말 승마대회 추진계획_본문 #38  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-02-23 09:05:49   수정일: 2024-04-19 11:25:07 &lt;/Document-Metadata&gt;  * 원활한 대회 운영을 위하여 …</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>140155f6377c6ed1
+29c493103f7c509c
+3426f5fdd6c93022
+352b2e0ed9bd7c00
+45d800cab99cab86</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>c019</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>제주 지역 경마 운영 문서</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['제주', '경마']</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1. 2020년도_2020년 ICT인프라 도입 결과보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 전자정부지원   작성자: user   마지막 수정자: KRA   작성일: 2017-09-20 09:50:34   수정일: 2020-12-11 16:08:43 &lt;/Document-Metadata&gt;  &lt;table border=…
+2. 2022년도_(요약) 자율주행 트랙터 개발·도입 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-05-17 12:51:23   수정일: 2023-08-17 11:00:09 &lt;/Document-Metadata&gt;  비, 제석, 예취, 파종 등 제반 초지관리 작업 수…
+3. 2020년도_경마실황 무선중계시스템 도입 계획(안) #9  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-20 12:54:03   수정일: 2020-08-08 11:33:53 &lt;/Document-Metadata&gt;  나. 계약 방법 : 견적 최저가       LTE …
+4. 2024년도_붙임) `24년 8월 제주경마 시행계획(안)  ▸  2024년도_붙임) `24년 8월 제주경마 시행계획(안)
+5. 2024년도_붙임) `24년 7월 제주경마 시행계획(안)  ▸  2024년도_붙임) `24년 7월 제주경마 시행계획(안)</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>016e887719433e3b
+027e0c5f0f5686c0
+0370e8a4dce03ce3
+046a893e4b7fb53e
+0b64f19639d9e665</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>c020</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>불법 사설경마 대응 계획이 있나?</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['불법사설', '대응']</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_붙임 2. 승마 공교육 편입관련 성과자료 #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2022-12-02 16:24:52 &lt;/Document-Metadata&gt;  증명으로 정규교과 승마의 당위성을 확…
+2. 2020년도_경주마 통합 건강관리시스템 추진계획(안) #19  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: kra   마지막 수정자: KRA   작성일: 2017-09-16 17:23:25   수정일: 2020-05-27 10:31:20 &lt;/Document-Metadata&gt;  === Extracted Images…
+3. 2021년도_K-TOTE 클라우드 전환 구축 시행계획(요약)_최종 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2021-06-17 10:42:08 &lt;/Document-Metadata&gt;  □ 추진기간 : 2021. 6월 ∼ …
+4. 2023년도_[붙임 1] (요약) 말산업 R&amp;D 중장기 로드맵 구축 연구 #10  ▸  &lt;Document-Metadata&gt;   제목: 사업개요   작성자: KRA   마지막 수정자: KRA   작성일: 2022-01-19 15:06:14   수정일: 2024-03-03 16:48:29 &lt;/Document-Metadata&gt;  === Extracted Ima…
+5. 2024년도_[붙임1] (요약) 2024년 지사 건전화 운영계획(안) #1  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-07-28 15:36:01 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>2bd46b499bdcc01d
+2d94f6c769030bda
+2e907c84c2a15612
+38bd220368aba4ab
+512e17e7a4d429e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>c021</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>말산업 발전 계획 관련 문서 목록</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['말산업', '발전', '계획']</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_(요약) 자율주행 트랙터 개발·도입 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-05-17 12:51:23   수정일: 2023-08-17 11:00:09 &lt;/Document-Metadata&gt;  비, 제석, 예취, 파종 등 제반 초지관리 작업 수…
+2. 2020년도_경마실황 무선중계시스템 도입 계획(안) #9  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2016-07-20 12:54:03   수정일: 2020-08-08 11:33:53 &lt;/Document-Metadata&gt;  나. 계약 방법 : 견적 최저가       LTE …
+3. 2020년도_1. 경주마위치추적시스템_운영관리용역_기본계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2020-05-24 16:03:22 &lt;/Document-Metadata&gt;  `2…
+4. 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:50:21 &lt;/Document-Metadata&gt;  20…
+5. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>027e0c5f0f5686c0
+0370e8a4dce03ce3
+05889d5822d0109f
+08dbb848822964aa
+0f9e1947b0221b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>c022</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>공공혁신 추진 관련 자료 리스트</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['공공혁신', '추진']</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>1. 2020년도_2020년 ICT인프라 도입 결과보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 전자정부지원   작성자: user   마지막 수정자: KRA   작성일: 2017-09-20 09:50:34   수정일: 2020-12-11 16:08:43 &lt;/Document-Metadata&gt;  &lt;table border=…
+2. 2022년도_(요약) 자율주행 트랙터 개발·도입 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-05-17 12:51:23   수정일: 2023-08-17 11:00:09 &lt;/Document-Metadata&gt;  비, 제석, 예취, 파종 등 제반 초지관리 작업 수…
+3. 2021년도_(요약본)2021년 한국마사회 공공혁신 추진 계획(안)  ▸  2021년도_(요약본)2021년 한국마사회 공공혁신 추진 계획(안)
+4. 2020년도_1. 경주마위치추적시스템_운영관리용역_기본계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2020-05-24 16:03:22 &lt;/Document-Metadata&gt;  `2…
+5. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>016e887719433e3b
+027e0c5f0f5686c0
+02f450763e85d3da
+05889d5822d0109f
+0f9e1947b0221b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>c023</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>경마 시행 계획 + 경주마 생산 실적 통합 분석</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['경마시행', '경주마', '생산']</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2020년도_1. 경주마위치추적시스템_운영관리용역_기본계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2020-05-24 16:03:22 &lt;/Document-Metadata&gt;  `2…
+3. 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:50:21 &lt;/Document-Metadata&gt;  20…
+4. 2024년도_24년 11월 서울 부경 경마시행계획_v5_241012 #26  ▸  &lt;Document-Metadata&gt;   제목: ‘04년 10월 경마계획 회의자료   작성자: KRA   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-01-24 01:26:21   수정일: 2024-10-12 15:14:53 …
+5. 2020년도_2020년 팀제 운영계획_최종 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-12-28 16:28:13   수정일: 2020-05-08 09:59:45 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>012dcbe84f52c595
+05889d5822d0109f
+08dbb848822964aa
+0ac3271720f05406
+0ac741faaa2da029</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>c024</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>마주 기준 + 레이팅 + 경주마 생산의 종합 현황</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['마주', '레이팅', '생산']</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>1. 2022년도_첨부3_2023년 한국 경주마 국제 레이팅 현황(4등급 이상) #110  ▸  &lt;Document-Metadata&gt;   작성자: Apache POI   마지막 수정자: KRA   작성일: 2022-12-16 01:56:04   수정일: 2022-12-16 02:02:00 &lt;/Document-Metadata&gt;  [Sheet: Int. Rating L…
+2. 2020년도_1. 경주마위치추적시스템_운영관리용역_기본계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2020-05-24 16:03:22 &lt;/Document-Metadata&gt;  `2…
+3. 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:50:21 &lt;/Document-Metadata&gt;  20…
+4. 2020년도_2020년 팀제 운영계획_최종 #5  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2019-12-28 16:28:13   수정일: 2020-05-08 09:59:45 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+5. 2022년도_첨부1_2022년 한국 대상경주 레이스 레이팅 총괄(연말최종) #6  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2017-12-28 05:32:05   수정일: 2022-12-16 01:40:34 &lt;/Document-Metadata&gt;  [Sheet: Sheet1] [Table Chunk…</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>012dcbe84f52c595
+05889d5822d0109f
+08dbb848822964aa
+0ac741faaa2da029
+110f8ff7eb5dbdc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>c025</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>승마 복지 + 말 등록 + 발전 계획의 공통점</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>multi_hop</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['승마복지', '말등록', '발전']</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_붙임_2_말등록규정_개정 전문 #23  ▸  &lt;Document-Metadata&gt;   제목: 제1장  총칙   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-04 15:10:28   수정일: 2024-09-05 17:48:37 &lt;/Document-Metadata&gt;  &lt;table border=…
+2. 2021년도_[붙임2] 2021년 일반말 등록업무 추진 계획(안) #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-31 13:09:52   수정일: 2021-03-13 11:35:26 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td …
+3. 2024년도_(요약)2024년 승용마 번식 지원사업 추진계획(안) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2024-04-05 08:50:21 &lt;/Document-Metadata&gt;  20…
+4. 2023년도_(요약) 23년 국제경주(코리아컵 코리아스프린트) 시행계획 #2  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-04-28 10:50:47 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+5. 2020년도_[붙임2] 2020년 더러브렛 등록업무 추진 계획(안) #14  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2020-02-08 13:45:30 &lt;/Document-Metadata&gt;  협조사항    ❍ 말보건원 : 경주마 현…</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>031374f12370d483
+048a00f4ea8e90a9
+08dbb848822964aa
+134ceaf0ae1ba751
+1a38e229b370f559</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>c026</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>데이터 기반 행정 활성화는 어떻게 해?</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['데이터', '행정', '활성화']</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>1. 2021년도_[붙임2] 2021년 일반말 등록업무 추진 계획(안) #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-31 13:09:52   수정일: 2021-03-13 11:35:26 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td …
+2. 2024년도_2024 마권 용지 및 구매표 구매 계획 요약 #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-02-22 11:16:41 &lt;/Document-Metadata&gt;  : 현 재고량(4,754 BOX)에 …
+3. 2024년도_(붙임 1) 제1회 국산마 품평회 개최계획 #18  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: KRA   작성일: 2024-06-15 17:31:04   수정일: 2024-06-19 17:49:01 &lt;/Document-Metadata&gt;  소요예산 : 97,200천원  …
+4. 2023년도_붙임 1.  2023년 학교체육 승마 시범사업 운영계획(안) 요약 #2  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2022-12-02 16:36:59 &lt;/Document-Metadata&gt;  기초…
+5. 2023년도_(붙임1) 말산업 일학습병행제 도입 및 활성화 추진경과 #4  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2023-09-08 16:25:03 &lt;/Document-Metadata&gt;  * 산업형(100% NCS 적용) 채…</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>048a00f4ea8e90a9
+10f09627fe81dec0
+133dd2fda4f7c41d
+17701730bc960da9
+1c2e14b3e46641c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>c027</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>청춘 블루밍 페스티벌이 뭔가요?</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['청춘', '블루밍', '페스티벌']</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_2024년 블루밍 워터페스티벌 운영계획(안)240609 #11  ▸  &lt;Document-Metadata&gt;   작성자: kra   마지막 수정자: KRA   작성일: 2019-04-13 13:22:27   수정일: 2024-06-14 14:40:19 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+2. 2023년도_썸즈업 워터페스티벌 요약_최종 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023년 계묘년 신년 및 설맞이 고객사은 행사 시행    작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-04 10:42:29   수정일: 2023-06-08 16:26:23 &lt;/Document-Me…
+3. 2023년도_2023년 썸즈업 워터페스티벌 운영계획(안)230604_결재 #7  ▸  &lt;Document-Metadata&gt;   작성자: kra   마지막 수정자: KRA   작성일: 2019-04-13 13:22:27   수정일: 2023-06-08 16:27:03 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+4. 2024년도_붙임  (본문)야간경마 행사 추진계획(안) #38  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: 1930079   작성일: 2024-07-20 14:44:26   수정일: 2024-08-11 19:42:14 &lt;/Document-Metadata&gt;  === Extracted…
+5. 2024년도_붙임  (요약)야간경마 행사 추진계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-11 16:38:58 &lt;/Document-Metadata&gt;  문인증 이벤트 등 축제 방문객 경마참…</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>054f2c421357db5b
+06a77998947ddb80
+1a0e5539ca61da40
+21721806a5c11d88
+517703ddbb49e0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>c028</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>말 등록 규정이 어떻게 개정됐지?</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['말등록', '규정', '개정']</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_붙임_2_말등록규정_개정 전문 #23  ▸  &lt;Document-Metadata&gt;   제목: 제1장  총칙   작성자: KRA   마지막 수정자: KRA   작성일: 2012-07-04 15:10:28   수정일: 2024-09-05 17:48:37 &lt;/Document-Metadata&gt;  &lt;table border=…
+2. 2021년도_[붙임2] 2021년 일반말 등록업무 추진 계획(안) #15  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2020-01-31 13:09:52   수정일: 2021-03-13 11:35:26 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td …
+3. 2023년도_2-1 812.승마지도사 자격 인정 등에 관한 규정_개정전문 #35  ▸  &lt;Document-Metadata&gt;   제목: 제1장  총    칙   키워드: 
+    설명: 
+    마지막 수정자: KRA   작성일: 2006-04-28 09:00:57   수정일: 2024-03-23 13:41:22 &lt;/Document-Metadat…
+4. 2023년도_붙임 1.  2023년 학교체육 승마 시범사업 운영계획(안) 요약 #2  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2022-12-02 16:36:59 &lt;/Document-Metadata&gt;  기초…
+5. 2020년도_[붙임2] 2020년 더러브렛 등록업무 추진 계획(안) #14  ▸  &lt;Document-Metadata&gt;   작성자: (주)한글과컴퓨터   마지막 수정자: KRA   작성일: 2004-11-09 15:23:46   수정일: 2020-02-08 13:45:30 &lt;/Document-Metadata&gt;  협조사항    ❍ 말보건원 : 경주마 현…</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>031374f12370d483
+048a00f4ea8e90a9
+07c4de1cc000e7e8
+17701730bc960da9
+1a38e229b370f559</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>c029</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>워터 페스티벌 행사 계획 알려줘</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['워터', '페스티벌']</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>1. 2024년도_2024년 블루밍 워터페스티벌 운영계획(안)240609 #11  ▸  &lt;Document-Metadata&gt;   작성자: kra   마지막 수정자: KRA   작성일: 2019-04-13 13:22:27   수정일: 2024-06-14 14:40:19 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+2. 2023년도_썸즈업 워터페스티벌 요약_최종 #0  ▸  &lt;Document-Metadata&gt;   제목: 2023년 계묘년 신년 및 설맞이 고객사은 행사 시행    작성자: KRA   마지막 수정자: KRA   작성일: 2023-02-04 10:42:29   수정일: 2023-06-08 16:26:23 &lt;/Document-Me…
+3. 2023년도_2023년 썸즈업 워터페스티벌 운영계획(안)230604_결재 #7  ▸  &lt;Document-Metadata&gt;   작성자: kra   마지막 수정자: KRA   작성일: 2019-04-13 13:22:27   수정일: 2023-06-08 16:27:03 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…
+4. 2024년도_붙임  (본문)야간경마 행사 추진계획(안) #38  ▸  &lt;Document-Metadata&gt;   제목: 2024   작성자: KRA   마지막 수정자: 1930079   작성일: 2024-07-20 14:44:26   수정일: 2024-08-11 19:42:14 &lt;/Document-Metadata&gt;  === Extracted…
+5. 2024년도_붙임  (요약)야간경마 행사 추진계획(안) #3  ▸  &lt;Document-Metadata&gt;   제목: 1   작성자: KRA   마지막 수정자: KRA   작성일: 2022-02-27 09:21:34   수정일: 2024-08-11 16:38:58 &lt;/Document-Metadata&gt;  문인증 이벤트 등 축제 방문객 경마참…</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>054f2c421357db5b
+06a77998947ddb80
+1a0e5539ca61da40
+21721806a5c11d88
+517703ddbb49e0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>c030</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>건전화 추진 계획이 있으면 보여줘</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>conversational</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>keywords: ['건전화', '추진']</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1. 2020년도_2020년 ICT인프라 도입 결과보고 #3  ▸  &lt;Document-Metadata&gt;   제목: 전자정부지원   작성자: user   마지막 수정자: KRA   작성일: 2017-09-20 09:50:34   수정일: 2020-12-11 16:08:43 &lt;/Document-Metadata&gt;  &lt;table border=…
+2. 2022년도_(요약) 자율주행 트랙터 개발·도입 계획(안) #1  ▸  &lt;Document-Metadata&gt;   작성자: KRA   마지막 수정자: KRA   작성일: 2023-05-17 12:51:23   수정일: 2023-08-17 11:00:09 &lt;/Document-Metadata&gt;  비, 제석, 예취, 파종 등 제반 초지관리 작업 수…
+3. 2020년도_1. 경주마위치추적시스템_운영관리용역_기본계획(요약) #0  ▸  &lt;Document-Metadata&gt;   제목: CEO지시사항 추진과제 입력 매뉴얼   작성자: kra   마지막 수정자: KRA   작성일: 2014-03-29 09:25:36   수정일: 2020-05-24 16:03:22 &lt;/Document-Metadata&gt;  `2…
+4. 2023년도_(요약)2024년 업무용 정보화기기 도입 계획 #1  ▸  &lt;Document-Metadata&gt;   제목: 22008년도 추경예산   마지막 수정자: KRA   작성일: 2008-06-24 14:14:18   수정일: 2024-05-26 17:28:55 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;…
+5. 2024년도_별첨1-2_2024년도 사행산업사업자 건전화평가 편람 신구대조표_한국마사회ver. #0  ▸  &lt;Document-Metadata&gt;   작성자: 김지혜   마지막 수정자: KRA   작성일: 2022-05-12 10:45:42   수정일: 2024-05-17 09:46:41 &lt;/Document-Metadata&gt;  &lt;table border='1'&gt; &lt;tr&gt; &lt;td&gt;…</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>016e887719433e3b
+027e0c5f0f5686c0
+05889d5822d0109f
+0f9e1947b0221b27
+10fb01568d0a958f</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3735,7 +10056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5188,7 +11509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5652,1911 +11973,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>x2bee</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>X2BEE ai_lab_main 이커머스 데이터 검색 GT (6 tables, ~19,843 nodes). 상품/판매/피드백 정형 데이터.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>id_field</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>node_title</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Total queries</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Answer resolved?</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>YES — see relevant_answer column</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>qid</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>query</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>relevant_count</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>relevant_answer</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>relevant_docs</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>e001</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>iPhone 15 Pro 512GB</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>상품명 정확 검색</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>e002</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Shin Ramyun</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>상품명 정확 검색</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00005</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>e003</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Galaxy Book</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>상품명 정확 검색</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00003</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>e004</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Dried Beef</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>상품명 정확 검색 — 동명 상품 가능</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>e005</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CLA Mask</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>상품명 정확 검색</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>1. CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00002</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>e006</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Volume Lip plumper maxi</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>상품명 정확 검색 (화장품)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>1. Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00006</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>e007</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Cheese Boursin Garlic Herbs</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>상품명 부분 검색</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>1. Cheese - Boursin, Garlic / Herbs | G01006 | 2023-12-18 | Y | 9999.0 | 77000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G01006</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>e008</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Wine Niagara Reisling</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>와인 상품 검색</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>1. Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Wine - Niagara Peninsula Vqa | G00462 | 2023-12-18 | Y | 9999.0 | 22000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00010
-pr_goods_base:G00462</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="80" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>e009</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Chicken Soup Base</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>상품명 검색</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>1. Chicken - Soup Base | G01004 | 2023-12-18 | Y | 9999.0 | 52000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G01004</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="80" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>e010</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Pastry Banana Muffin</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>복합 상품명 검색</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>1. Pastry - Banana Muffin - Mini | G00992 | 2023-12-18 | Y | 9999.0 | 24000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00992</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>e011</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Jameson Irish Whiskey</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>주류 상품 검색 — 동명 상품 2개 (dash 유무 차이)</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>1. Jameson - Irish Whiskey | G00082 | 2023-12-18 | Y | 9999.0 | 58000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Jameson Irish Whiskey | G00968 | 2023-12-18 | Y | 9999.0 | 15000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00082
-pr_goods_base:G00968</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>e012</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Lamb Shoulder Boneless</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>식재료 검색 — 유사 상품 다수</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>1. Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00470
-pr_goods_base:G00736</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>e013</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>English Muffin</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>동명 상품 2개</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>1. English Muffin | G00467 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. English Muffin | G00569 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00467
-pr_goods_base:G00569</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="80" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>e014</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Beer Alexander Kieths Pale Ale</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>맥주 상품 검색</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>1. Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00974</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="80" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>e015</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Wiberg Super Cure</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>리뷰가 가장 많은 상품 (29건)</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00751</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="80" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>e016</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Ice Wine</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>아이스 와인 — 동명 2개 상품</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>1. Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Wine - Ice Wine | G00339 | 2023-12-18 | Y | 9999.0 | 39000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00106
-pr_goods_base:G00339</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="80" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>e017</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Cheese Feta</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>치즈 종류 검색 — 2개 상품</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>1. Cheese - Feta | G00315 | 2023-12-18 | Y | 9999.0 | 97000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Cheese - Feta | G00694 | 2023-12-18 | Y | 9999.0 | 55000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00315
-pr_goods_base:G00694</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="80" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>e018</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Cabernet Sauvignon wine</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>와인 품종 검색</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>1. Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00113</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="80" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>e019</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Bread 10 Grain</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>빵 상품 검색 — 동명 상품 3개</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>1. Bread - 10 Grain | G00563 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Bread - 10 Grain | G00817 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Bread - 10 Grain | G01005 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00563
-pr_goods_base:G00817
-pr_goods_base:G01005</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="80" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>e020</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Garlic Powder</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>향신료 검색 — 최저가 상품 중 하나 (1000원)</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>1. Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00711</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>x2bee_hard</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>X2BEE ai_lab_main 이커머스 고난이도 검색 GT — 패러프레이즈, FK조인, 필터, 집계, 멀티홉</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>id_field</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>node_title</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Total queries</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Answer resolved?</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>YES — see relevant_answer column</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>qid</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>query</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>relevant_count</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>relevant_answer</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>relevant_docs</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>h001</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>프리미엄 스마트폰 최신 모델</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>iPhone 15 Pro 512GB를 직접 언급하지 않고 의미로 검색</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>h002</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>한국 즉석 라면 제품</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Shin Ramyun을 한국어 설명으로 검색</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00005</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>h003</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>이탈리아 숙성 치즈 제품</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Provolone, Gorgonzola, Parmesan 등 이탈리아 치즈</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>1. Cheese - Provolone | G00040 | 2023-12-18 | Y | 9999.0 | 56000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Cheese - Gorgonzola | G00083 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Cheese - Parmesan Cubes | G00442 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-4. Cheese - Mozzarella | G00158 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00040
-pr_goods_base:G00083
-pr_goods_base:G00442
-pr_goods_base:G00158</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>h004</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>portable computing device</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Galaxy Book을 영어 패러프레이즈로 검색</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>1. Galaxy Book | 노트북 | G00003 | 2024-12-19 | Y | 150.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00003</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>h005</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Dried Beef 판매 이력</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>cross_table</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>상품(pr_goods_base) → 판매이력(pr_goods_sold_hist) FK 조인</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>h006</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Cheese Pont Couvert 리뷰</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>cross_table</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>상품 → 피드백 FK 조인. 27건의 리뷰 존재</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>1. Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00997</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>h007</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>iPhone 15 Pro 판매 기록은 몇 건인가?</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>cross_table</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>상품 → 판매이력 FK + 건수 확인 (65건)</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>h008</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>50만원 이상 고가 상품</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>price &gt;= 500000 필터. iPhone만 해당 (1,600,000원)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>1. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="80" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>h009</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>1000원짜리 최저가 상품</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>price = 1000 필터. 4개 상품</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>1. Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Garlic Powder | G00711 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-4. Plate Pie Foil | G00892 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00072
-pr_goods_base:G00302
-pr_goods_base:G00711
-pr_goods_base:G00892</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="80" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>h010</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>5000원 이하 저가 상품 목록</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>price &lt;= 5000 필터. 41개 상품</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Chips Potato Swt Chilli Sour | G00063 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Amarula Cream | G00068 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-4. Veal - Striploin | G00072 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-5. Quail - Jumbo | G00089 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-6. Fudge - Chocolate Fudge | G00098 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-7. Pepper - Green Thai | G00202 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-8. Jam - Raspberry,jar | G00203 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-9. Oysters - Smoked | G00204 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-10. Soda Water - Club Soda, 355 Ml | G00217 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-11. Juice - Apple Cider | G00258 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-12. Scotch - Queen Anne | G00261 | 2023-12-18 | Y | 9999.0 | 3000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-13. Soup - Campbells - Tomato | G00267 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-14. Chinese Foods - Chicken Wing | G00283 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-15. Oil - Olive | G00302 | 2023-12-18 | Y | 9999.0 | 1000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-16. Fondant - Icing | G00314 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-17. Nut - Walnut, Chopped | G00332 | 2023-12-18 | Y | 9999.0 | 4000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-18. Otomegusa Dashi Konbu | G00376 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-19. Lettuce - Iceberg | G00388 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-20. Doilies - 8, Paper | G00438 | 2023-12-18 | Y | 9999.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-... +21 more</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00005
-pr_goods_base:G00063
-pr_goods_base:G00068
-pr_goods_base:G00072
-pr_goods_base:G00089
-pr_goods_base:G00098
-pr_goods_base:G00202
-pr_goods_base:G00203
-pr_goods_base:G00204
-pr_goods_base:G00217
-pr_goods_base:G00258
-pr_goods_base:G00261
-pr_goods_base:G00267
-pr_goods_base:G00283
-pr_goods_base:G00302
-pr_goods_base:G00314
-pr_goods_base:G00332
-pr_goods_base:G00376
-pr_goods_base:G00388
-pr_goods_base:G00438
-pr_goods_base:G00444
-pr_goods_base:G00492
-pr_goods_base:G00529
-pr_goods_base:G00554
-pr_goods_base:G00557
-pr_goods_base:G00583
-pr_goods_base:G00634
-pr_goods_base:G00635
-pr_goods_base:G00667
-pr_goods_base:G00688
-pr_goods_base:G00711
-pr_goods_base:G00738
-pr_goods_base:G00754
-pr_goods_base:G00768
-pr_goods_base:G00769
-pr_goods_base:G00778
-pr_goods_base:G00783
-pr_goods_base:G00787
-pr_goods_base:G00892
-pr_goods_base:G00965
-pr_goods_base:G01009</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>h011</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>가장 많이 팔린 상품 TOP 3</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>aggregation</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>sold_qunt SUM GROUP BY goods_no. Dried Beef(83), Jacket(74), iPhone(69)</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Jacket | 남성 의류 | G00004 | 2024-12-19 | Y | 200.0 | 18500.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. iPhone 15 Pro 512GB | 아이폰 15 프로 | G00007 | 2024-12-19 | Y | 200.0 | 1600000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00001
-pr_goods_base:G00004
-pr_goods_base:G00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>h012</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>리뷰가 가장 많은 상품 TOP 5</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>aggregation</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>feedback COUNT GROUP BY goods_no. Wiberg(29), Bread Kimel(28), Pork Ham(28), Sauce Ranch(27), Cheese Pont(27)</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>1. Wiberg Super Cure | G00751 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Bread - Kimel Stick Poly | G00472 | 2023-12-18 | Y | 9999.0 | 42000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Pork Ham Prager | G00389 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-4. Sauce - Ranch Dressing | G00329 | 2023-12-18 | Y | 9999.0 | 88000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-5. Cheese - Pont Couvert | G00997 | 2023-12-18 | Y | 9999.0 | 66000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00751
-pr_goods_base:G00472
-pr_goods_base:G00389
-pr_goods_base:G00329
-pr_goods_base:G00997</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>h013</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>맥주 종류가 총 몇 개인가?</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>aggregation</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Beer 포함 상품 COUNT = 11개</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>1. Beer - Mill St Organic | G00270 | 2023-12-18 | Y | 9999.0 | 59000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Beer - Sleemans Honey Brown | G00466 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Beer - Original Organic Lager | G00645 | 2023-12-18 | Y | 9999.0 | 73000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-4. Beer - Moosehead | G00700 | 2023-12-18 | Y | 9999.0 | 87000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-5. Beer - Original Organic Lager | G00719 | 2023-12-18 | Y | 9999.0 | 74000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-6. Beer - Steamwhistle | G00793 | 2023-12-18 | Y | 9999.0 | 33000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-7. Beer - Original Organic Lager | G00798 | 2023-12-18 | Y | 9999.0 | 90000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-8. Beer - Rickards Red | G00928 | 2023-12-18 | Y | 9999.0 | 36000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-9. Beer - Mcauslan Apricot | G00937 | 2023-12-18 | Y | 9999.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-10. Beer - Steamwhistle | G00938 | 2023-12-18 | Y | 9999.0 | 63000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-11. Beer - Alexander Kieths, Pale Ale | G00974 | 2023-12-18 | Y | 9999.0 | 31000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00270
-pr_goods_base:G00466
-pr_goods_base:G00645
-pr_goods_base:G00700
-pr_goods_base:G00719
-pr_goods_base:G00793
-pr_goods_base:G00798
-pr_goods_base:G00928
-pr_goods_base:G00937
-pr_goods_base:G00938
-pr_goods_base:G00974</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="80" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>h014</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>5점 리뷰를 가장 많이 받은 상품의 가격은?</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>multi_hop</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>feedback(score=5) 집계 → 상품 조회 → 가격 확인. Flour Masa De Harina(11건 5점, 가격 확인 필요)</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>1. Flour - Masa De Harina Mexican | G00857 | 2023-12-18 | Y | 9999.0 | 86000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00857</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="80" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>h015</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>판매량 1위 상품의 리뷰 평점은?</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>multi_hop</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>L6</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>sold_hist 집계(G00001 Dried Beef=83개) → feedback 평점 확인</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>1. Dried Beef | 소고기육포 | G00001 | 2024-12-19 | Y | 100.0 | 40000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="80" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>h016</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>이 쇼핑몰에서 와인이 몇 종류나 있어?</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>conversational</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Wine 포함 상품 COUNT. 80+ 종류</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>1. Wine - Niagara,vqa Reisling | A | G00010 | 2023-12-18 | Y | 9999.0 | 78000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Wine - Piper Heidsieck Brut | G00034 | 2023-12-18 | Y | 9999.0 | 47000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Wine - Sicilia Igt Nero Avola | G00048 | 2023-12-18 | Y | 9999.0 | 18000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-4. Wine - Champagne Brut Veuve | G00055 | 2023-12-18 | Y | 9999.0 | 10000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-5. Wine - Magnotta, White | G00077 | 2023-12-18 | Y | 9999.0 | 26000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-6. Wine - Winzer Krems Gruner | G00086 | 2023-12-18 | Y | 9999.0 | 75000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-7. Wine - Ice Wine | G00106 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-8. Wine - Red, Cabernet Merlot | G00112 | 2023-12-18 | Y | 9999.0 | 14000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-9. Wine - Cabernet Sauvignon | G00113 | 2023-12-18 | Y | 9999.0 | 41000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-10. Wine - Fino Tio Pepe Gonzalez | G00138 | 2023-12-18 | Y | 9999.0 | 64000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-11. Wine - Tribal Sauvignon | G00144 | 2023-12-18 | Y | 9999.0 | 38000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-12. Wine - Delicato Merlot | G00148 | 2023-12-18 | Y | 9999.0 | 17000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-13. Wine - Pinot Grigio Collavini | G00164 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-14. Wine - Red, Pinot Noir, Chateau | G00172 | 2023-12-18 | Y | 9999.0 | 48000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-15. Wine La Vielle Ferme Cote Du | G00174 | 2023-12-18 | Y | 9999.0 | 85000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-16. Wine - Rubyport | G00207 | 2023-12-18 | Y | 9999.0 | 65000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-17. Wine - Rosso Del Veronese Igt | G00264 | 2023-12-18 | Y | 9999.0 | 54000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-18. Wine - Wyndham Estate Bin 777 | G00277 | 2023-12-18 | Y | 9999.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-19. Wine - Chateauneuf Du Pape | G00282 | 2023-12-18 | Y | 9999.0 | 29000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-20. Wine - Casablanca Valley | G00293 | 2023-12-18 | Y | 9999.0 | 12000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-... +10 more</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00010
-pr_goods_base:G00034
-pr_goods_base:G00048
-pr_goods_base:G00055
-pr_goods_base:G00077
-pr_goods_base:G00086
-pr_goods_base:G00106
-pr_goods_base:G00112
-pr_goods_base:G00113
-pr_goods_base:G00138
-pr_goods_base:G00144
-pr_goods_base:G00148
-pr_goods_base:G00164
-pr_goods_base:G00172
-pr_goods_base:G00174
-pr_goods_base:G00207
-pr_goods_base:G00264
-pr_goods_base:G00277
-pr_goods_base:G00282
-pr_goods_base:G00293
-pr_goods_base:G00306
-pr_goods_base:G00330
-pr_goods_base:G00333
-pr_goods_base:G00339
-pr_goods_base:G00379
-pr_goods_base:G00402
-pr_goods_base:G00405
-pr_goods_base:G00424
-pr_goods_base:G00449
-pr_goods_base:G00462</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="80" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>h017</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>신라면이 잘 팔리나요?</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>conversational</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Shin Ramyun(G00005) 판매이력 확인. 45개 판매로 5위</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>1. Shin Ramyun | 신라면 | G00005 | 2024-12-19 | Y | 150.0 | 5000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00005</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="80" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>h018</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>양고기 제품 중 뼈 없는 것</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Lamb + Boneless 필터</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>1. Lamb Shoulder Boneless Nz | G00470 | 2023-12-18 | Y | 9999.0 | 61000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Lamb - Loin, Trimmed, Boneless | G00492 | 2023-12-18 | Y | 9999.0 | 2000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-3. Lamb - Shoulder, Boneless | G00736 | 2023-12-18 | Y | 9999.0 | 25000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00470
-pr_goods_base:G00492
-pr_goods_base:G00736</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="80" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>h019</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>facial skincare product</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>paraphrase</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>CLA Mask를 영어 카테고리로 검색</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>1. CLA Mask | 일회용 마스크 | G00002 | 2024-12-19 | Y | 200.0 | 72000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00
-2. Volume Lip plumper maxi | 립밤 | G00006 | 2024-12-19 | Y | 200.0 | 16000.0 | 2023-12-19 00:00:00 | 2024-12-18 00:00:00 | 2023-12-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>pr_goods_base:G00002
-pr_goods_base:G00006</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="80" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>h020</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>유저 한 명이 작성한 리뷰 수는 최대 몇 건?</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>aggregation</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>user_id GROUP BY COUNT MAX = 23건</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>